--- a/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -908,50 +908,64 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PROVENANCE LIMIT, STATED PLAINLY. The company's audited statements could not be retrieved when this was</t>
+          <t>PROVENANCE LIMIT, STATED PLAINLY. NO SOURCE DOCUMENT WAS OPENED. Not the audited statements, not the annual</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>built: the environment's egress policy refused every external financial host. Revenue, profit, operating</t>
+          <t>report, not the investor presentation, not the exchange filing, and not the press articles reporting them:</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>income, the balance-sheet totals and both dividend distributions are carried as disclosed via reporting of</t>
+          <t>the environment's egress policy refused every external financial host at the connection stage. Revenue,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>the EGX filings and via aggregations of S&amp;P Global Market Intelligence data. Where two aggregations disagree</t>
+          <t>profit, operating income, the balance-sheet totals and both dividend distributions are carried as RELAYED in</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>— they do, on total liabilities — the disagreement is shown on the Balance Sheet sheet rather than averaged</t>
+          <t>web-search summaries of EGX-filing coverage and of aggregations of S&amp;P Global Market Intelligence data —</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>away, and the figure that closes against total assets is the one carried.</t>
+          <t>two steps from the audited print, not one. Where two aggregations disagree</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr"/>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>— they do, on total liabilities — the disagreement is shown on the Balance Sheet sheet rather than averaged</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>away, and the figure that closes against total assets is the one carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>No rating and no price target. Fair-value ranges and distributions only.</t>
         </is>

--- a/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Testahil — Arabian Cement Company S.A.E. (EGX: ARCC) — revision 2</t>
+          <t>Testahil — Arabian Cement Company S.A.E. (EGX: ARCC) — revision 3</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -580,359 +580,467 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>REVISION 2 IS BUILT ON THE AUDITED ACCOUNTS. Revision 1 of this model was built without opening a single</t>
+          <t>REVISION 3 CORRECTS THE PRICE PATH, WHICH THE AUDITED RECORD DISPROVED. Revision 2 rebuilt every company</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>source document: every outbound request was refused by the network policy in force, so every company figure</t>
+          <t>figure on the statements but left one forecast driver where revision 1 had put it: local realised price</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>reached it as relayed in a web-search summary. The audited consolidated financial statements for FY2023,</t>
+          <t>growing 3.0% in FY2026 against 11.5% cost inflation, and about 4% a year after that. The statements that had</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FY2024 and FY2025 — Deloitte, signed 25 February 2026 — and the reviewed Q1-2026 interim accounts are now in</t>
+          <t>just been read contradict it. FY2024: revenue +44.5% against total cash cost +41.8%. FY2025: revenue +42.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>hand, and every historical cell in this workbook is a disclosed figure read from them.</t>
+          <t>against cash cost +12.5%, which is why the audited gross margin went 21.2% to 23.9% to 40.6%. Q1-2026 then</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>printed revenue +17.3% at a 42.9% gross margin against 40.6% for the full prior year — still WIDENING. In</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>WHAT THE STATEMENTS CHANGED, and it is not cosmetic:</t>
+          <t>every period the accounts cover, price outran cost. The old path also implied a producer unable to raise</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Non-controlling interests are EGP 158,005 — one hundred and fifty-eight THOUSAND pounds. Revision 1</t>
+          <t>price even at the central bank's own 7% medium-term target, while the same model had utilisation RISING</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    deducted EGP 150 MILLION on inference, 950 times too much.</t>
+          <t>from 69.7% to 78.2% — volume gained and real price lost at once, two conservatisms stacked rather than one</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * The effective tax rate is 23.82%, not the 29.43% revision 1 inferred. Every forecast year was over-taxed.</t>
+          <t>judgement made. The path is recalibrated to 8.0% / 9.0% / 8.0% / 7.0% / 6.5%, still below the cost path in</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * The cost of debt is about 7.5%, not 21.5%: 91% of the book is EURO-denominated, at Euribor plus 4.35%</t>
+          <t>every year, and still producing FY2026 group revenue growth of about 10.7% against the 17.3% the first</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (a EUR 25mn EBRD decarbonisation facility) and Euribor plus 3% (a EUR 3.09mn NBE/KfW facility).</t>
+          <t>quarter actually ran. The cost path is UNCHANGED at headline inflation: the company's realised cost</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Kiln capacity is 4.2Mt of clinker against 5.0Mt of cement, so the clinker factor is 0.84, not 0.72.</t>
+          <t>inflation ran below the national rate, but crediting that here would double-count the alternative-fuel</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Exports are 30.7% of revenue, not 12%. The revenue note splits local from export and goods from services.</t>
+          <t>saving already carried as its own driver. The EBITDA margin now glides from the audited 39.3% to about</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * The cost stack is DISCLOSED. The invented five-line stack of revision 1 is retired for the printed one.</t>
+          <t>34.3% by FY2030 rather than to 24.5% — still erosion, but erosion the record can support.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  What survived: the share count of 374,867,445, FY2025 operating income of EGP 4,595.82mn to the pound, and</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total liabilities of EGP 4,140.99mn — which revision 1 derived, against an aggregator print of EGP 2,894mn</t>
+          <t>REVISION 2 BUILT THE STUDY ON THE AUDITED ACCOUNTS. Revision 1 was built without opening a single</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that it rejected. That figure turns out to be total CURRENT liabilities. The derivation was right.</t>
+          <t>source document: every outbound request was refused by the network policy in force, so every company figure</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>reached it as relayed in a web-search summary. The audited consolidated financial statements for FY2023,</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>IT IS FORMULA-DRIVEN, AND THAT CLAIM IS TESTED. Change a blue cell on Assumptions and the model reprices. The</t>
+          <t>FY2024 and FY2025 — Deloitte, signed 25 February 2026 — and the reviewed Q1-2026 interim accounts are now in</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>cost of equity is built from the risk-free rate NET of the sovereign default spread, beta and the premium;</t>
+          <t>hand, and every historical cell in this workbook is a disclosed figure read from them.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>the cost of debt is built FACILITY BY FACILITY from the audited debt note and blended by currency; the</t>
-        </is>
-      </c>
+      <c r="A27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>weights come from debt and market capitalisation; the terminal rate is built from its own components; the</t>
+          <t>WHAT THE STATEMENTS CHANGED, and it is not cosmetic:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>glide fractions are derived from the pound cost-of-debt path; the discount factors compound through it; the</t>
+          <t xml:space="preserve">  * Non-controlling interests are EGP 158,005 — one hundred and fifty-eight THOUSAND pounds. Revision 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>waterfall chains from margin through EBITDA, D&amp;A, EBIT, NOPAT, capex and working capital to free cash flow</t>
+          <t xml:space="preserve">    deducted EGP 150 MILLION on inference, 950 times too much.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>and present value; the terminal block chains from reinvestment = growth / return on capital; the statements</t>
+          <t xml:space="preserve">  * The effective tax rate is 23.82%, not the 29.43% revision 1 inferred. Every forecast year was over-taxed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>roll forward; and every ratio and per-share figure is a formula. A driver test perturbs every input in place,</t>
+          <t xml:space="preserve">  * The cost of debt is about 7.5%, not 21.5%: 91% of the book is EURO-denominated, at Euribor plus 4.35%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>re-evaluates the whole workbook and confirms the headline moves in the right direction.</t>
+          <t xml:space="preserve">    (a EUR 25mn EBRD decarbonisation facility) and Euribor plus 3% (a EUR 3.09mn NBE/KfW facility).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Kiln capacity is 4.2Mt of clinker against 5.0Mt of cement, so the clinker factor is 0.84, not 0.72.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>THREE CLASSES OF CELL ARE PASTED, and it is worth knowing exactly which.</t>
+          <t xml:space="preserve">  * Exports are 30.7% of revenue, not 12%. The revenue note splits local from export and goods from services.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Audited and disclosed history — the primary record, not a calculation. Where a line is both disclosed</t>
+          <t xml:space="preserve">  * The cost stack is DISCLOSED. The invented five-line stack of revision 1 is retired for the printed one.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     and derivable, the DISCLOSED figure is carried. These sit on Assumptions and are labelled there.</t>
+          <t xml:space="preserve">  What survived: the share count of 374,867,445, FY2025 operating income of EGP 4,595.82mn to the pound, and</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. The output of a unit build that cannot survive being flattened into a grid: the percentile ladder of the</t>
+          <t xml:space="preserve">  total liabilities of EGP 4,140.99mn — which revision 1 derived, against an aggregator print of EGP 2,894mn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     probabilistic price map on the Monte Carlo sheet, the output of a 50,000-path simulation.</t>
+          <t xml:space="preserve">  that it rejected. That figure turns out to be total CURRENT liabilities. The derivation was right.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Whole-model re-runs — the sensitivity grids, and the alternative fair values in the contested-choices</t>
-        </is>
-      </c>
+      <c r="A40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     table. Each of those cells is a COMPLETE revaluation at a different assumption. THESE DO NOT REDRAW</t>
+          <t>IT IS FORMULA-DRIVEN, AND THAT CLAIM IS TESTED. Change a blue cell on Assumptions and the model reprices. The</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     WHEN A DRIVER CHANGES. Edit an input and the unit build, waterfall, statements, ratios and all four</t>
+          <t>cost of equity is built from the risk-free rate NET of the sovereign default spread, beta and the premium;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     lenses reprice; the sensitivity tables and the price map keep the values printed here.</t>
+          <t>the cost of debt is built FACILITY BY FACILITY from the audited debt note and blended by currency; the</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Anything else pasted would be a defect.</t>
+          <t>weights come from debt and market capitalisation; the terminal rate is built from its own components; the</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>glide fractions are derived from the pound cost-of-debt path; the discount factors compound through it; the</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>HOW THE COMPANY IS VALUED. A single-segment cement operating company: two lines in Suez governorate, 4.2Mt of</t>
+          <t>waterfall chains from margin through EBITDA, D&amp;A, EBIT, NOPAT, capex and working capital to free cash flow</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>clinker capacity and 5.0Mt of cement, 60% owned by Aridos Jativa of Spain. No property leg, no lending book,</t>
+          <t>and present value; the terminal block chains from reinvestment = growth / return on capital; the statements</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>no concession. One operating-company lens, cross-read against relative multiples, normalised earnings power</t>
+          <t>roll forward; and every ratio and per-share figure is a formula. A driver test perturbs every input in place,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>and replacement cost. Cash of EGP 3,459mn against interest-bearing debt of EGP 1,135mn makes it net cash;</t>
+          <t>re-evaluates the whole workbook and confirms the headline moves in the right direction.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>that cash is stripped out of the discount rate and added back in the bridge, so it is priced once at face —</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>less the EGP 2,002mn FY2025 dividend that was declared and still unpaid at 31 March 2026.</t>
+          <t>THREE CLASSES OF CELL ARE PASTED, and it is worth knowing exactly which.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Audited and disclosed history — the primary record, not a calculation. Where a line is both disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>TWO THINGS TO KNOW BEFORE READING ANY NUMBER.</t>
+          <t xml:space="preserve">     and derivable, the DISCLOSED figure is carried. These sit on Assumptions and are labelled there.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * FY2025 is a cyclical peak. The audited EBITDA margin went 22.0% to 23.1% to 39.2% across the three years,</t>
+          <t xml:space="preserve">  2. The output of a unit build that cannot survive being flattened into a grid: the percentile ladder of the</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    on the abolition of the production quota in May 2025. The forecast glides it down every year from there.</t>
+          <t xml:space="preserve">     probabilistic price map on the Monte Carlo sheet, the output of a 50,000-path simulation.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Book return on capital is 60.6% and replacement-cost return is 8.6%. The terminal block is struck on the</t>
+          <t xml:space="preserve">  3. Whole-model re-runs — the sensitivity grids, and the alternative fair values in the contested-choices</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    REPLACEMENT figure. On the book number, growth would be free; it is not, and the difference is the single</t>
+          <t xml:space="preserve">     table. Each of those cells is a COMPLETE revaluation at a different assumption. THESE DO NOT REDRAW</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    most consequential judgement in this model.</t>
+          <t xml:space="preserve">     WHEN A DRIVER CHANGES. Edit an input and the unit build, waterfall, statements, ratios and all four</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     lenses reprice; the sensitivity tables and the price map keep the values printed here.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Anything else pasted would be a defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>HOW THE COMPANY IS VALUED. A single-segment cement operating company: two lines in Suez governorate, 4.2Mt of</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>clinker capacity and 5.0Mt of cement, 60% owned by Aridos Jativa of Spain. No property leg, no lending book,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>no concession. One operating-company lens, cross-read against relative multiples, normalised earnings power</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>and replacement cost. Cash of EGP 3,459mn against interest-bearing debt of EGP 1,135mn makes it net cash;</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>that cash is stripped out of the discount rate and added back in the bridge, so it is priced once at face —</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>less the EGP 2,002mn FY2025 dividend that was declared and still unpaid at 31 March 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>TWO THINGS TO KNOW BEFORE READING ANY NUMBER.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * FY2025 is a cyclical peak. The audited EBITDA margin went 22.0% to 23.1% to 39.2% across the three years,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    on the abolition of the production quota in May 2025. The forecast glides it down every year from there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Book return on capital is 60.6% and replacement-cost return is 8.6%. The terminal block is struck on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REPLACEMENT figure. On the book number, growth would be free; it is not, and the difference is the single</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    most consequential judgement in this model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>No rating and no price target. Fair-value ranges and distributions only.</t>
         </is>
@@ -2102,7 +2210,7 @@
         <v/>
       </c>
       <c r="E20" s="7" t="n">
-        <v>36.25531474459756</v>
+        <v>68.51141773004619</v>
       </c>
       <c r="F20" s="23">
         <f>E20/D20-1</f>
@@ -2130,7 +2238,7 @@
         <v/>
       </c>
       <c r="E21" s="7" t="n">
-        <v>32.66153709598022</v>
+        <v>59.63546849895328</v>
       </c>
       <c r="F21" s="23">
         <f>E21/D21-1</f>
@@ -2158,7 +2266,7 @@
         <v/>
       </c>
       <c r="E22" s="7" t="n">
-        <v>41.70143691039763</v>
+        <v>73.70516700786516</v>
       </c>
       <c r="F22" s="23">
         <f>E22/D22-1</f>
@@ -2760,13 +2868,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>58.34234480539681</v>
+        <v>58.81442632306862</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>68.40590207161927</v>
+        <v>68.87798358929108</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>78.46945933784173</v>
+        <v>78.94154085551355</v>
       </c>
       <c r="E17" s="23">
         <f>C17/Assumptions!$B$5-1</f>
@@ -2780,13 +2888,13 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>45.64838429697266</v>
+        <v>46.12046581464448</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>52.47810844887751</v>
+        <v>52.95018996654932</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>59.30783260078233</v>
+        <v>59.77991411845415</v>
       </c>
       <c r="E18" s="23">
         <f>C18/Assumptions!$B$5-1</f>
@@ -2800,13 +2908,13 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>32.89299564012248</v>
+        <v>50.51763698507147</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>36.92484653363374</v>
+        <v>56.99985356819377</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>42.30064772498208</v>
+        <v>65.64280901235682</v>
       </c>
       <c r="E19" s="23">
         <f>C19/Assumptions!$B$5-1</f>
@@ -3251,19 +3359,19 @@
         <v>0.2089372422775459</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>41.76342837826929</v>
+        <v>71.4593442293817</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>39.89173337926264</v>
+        <v>71.53145985731972</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>37.67177438102595</v>
+        <v>71.61699395194488</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>34.99637909021594</v>
+        <v>71.72007581703591</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>31.70937496143734</v>
+        <v>71.84672271565323</v>
       </c>
     </row>
     <row r="7">
@@ -3271,19 +3379,19 @@
         <v>0.2239372422775459</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>40.98429516066264</v>
+        <v>69.98304441235413</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>39.16027531261984</v>
+        <v>70.05332313660291</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36.99686232237625</v>
+        <v>70.13667853711605</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>34.38961375122143</v>
+        <v>70.23713473751145</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>31.18633502542862</v>
+        <v>70.36055573125974</v>
       </c>
     </row>
     <row r="8">
@@ -3291,19 +3399,19 @@
         <v>0.2389372422775459</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>40.23046167443645</v>
+        <v>68.55531419214742</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>38.45249399426929</v>
+        <v>68.62381854556868</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>36.34370204245242</v>
+        <v>68.70506942024463</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>33.80228030373102</v>
+        <v>68.80298934023183</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>30.67987675579933</v>
+        <v>68.92329424709673</v>
       </c>
     </row>
     <row r="9">
@@ -3311,19 +3419,19 @@
         <v>0.2539372422775459</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>39.50085951822804</v>
+        <v>67.1740906523508</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>37.76739102745903</v>
+        <v>67.24088047055777</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>35.71137817478549</v>
+        <v>67.32009778854915</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>33.23356344565906</v>
+        <v>67.4155669569766</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>30.18930779006914</v>
+        <v>67.53286085813211</v>
       </c>
     </row>
     <row r="10">
@@ -3331,19 +3439,19 @@
         <v>0.2689372422775459</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>38.79447584600187</v>
+        <v>65.83741847106668</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>37.10401988952282</v>
+        <v>65.90255103426088</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>35.09902286078677</v>
+        <v>65.97980273382618</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>32.6826901208446</v>
+        <v>66.0729030268443</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>29.71397154681731</v>
+        <v>66.18728651574119</v>
       </c>
     </row>
     <row r="12">
@@ -3386,19 +3494,19 @@
         <v>0.2089372422775459</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>41.90480800166688</v>
+        <v>82.57728288508706</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>39.57602658912257</v>
+        <v>76.54139078979419</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>37.67177438102595</v>
+        <v>71.61699395194488</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>36.08383305553142</v>
+        <v>67.5205187341991</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>34.73793336462717</v>
+        <v>64.05735786089986</v>
       </c>
     </row>
     <row r="15">
@@ -3406,19 +3514,19 @@
         <v>0.2239372422775459</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>41.11924005323293</v>
+        <v>80.81079131273962</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>38.85133672264659</v>
+        <v>74.93251493373815</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>36.99686232237625</v>
+        <v>70.13667853711605</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>35.45042732963532</v>
+        <v>66.14712077749493</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>34.13970391702797</v>
+        <v>62.77432123211368</v>
       </c>
     </row>
     <row r="16">
@@ -3426,19 +3534,19 @@
         <v>0.2389372422775459</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>40.35926703770503</v>
+        <v>79.10293545539865</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>38.1501273709972</v>
+        <v>73.37680543026032</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>36.34370204245242</v>
+        <v>68.70506942024463</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>34.83733206214591</v>
+        <v>64.81872089392061</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>33.56056358137754</v>
+        <v>61.53314958028578</v>
       </c>
     </row>
     <row r="17">
@@ -3446,19 +3554,19 @@
         <v>0.2539372422775459</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>39.62380526879407</v>
+        <v>77.45121195721818</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>37.47140745795001</v>
+        <v>71.8719983043673</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>35.71137817478549</v>
+        <v>67.32009778854915</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>34.24369500131927</v>
+        <v>63.53341249464879</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>32.99971358046732</v>
+        <v>60.33207334377854</v>
       </c>
     </row>
     <row r="18">
@@ -3466,19 +3574,19 @@
         <v>0.2689372422775459</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>38.9118275222316</v>
+        <v>75.85324846929772</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>36.8142374424753</v>
+        <v>70.41594786025824</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>35.09902286078677</v>
+        <v>65.97980273382618</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>33.6687080463679</v>
+        <v>62.28938827364372</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>32.45639644425723</v>
+        <v>59.1694149628063</v>
       </c>
     </row>
     <row r="20">
@@ -3523,19 +3631,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>36.7666901891904</v>
+        <v>69.75553445865843</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>34.0301794456266</v>
+        <v>62.98956762602439</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>31.81696973523281</v>
+        <v>57.57727443120589</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>30.41291717923679</v>
+        <v>54.17757888983147</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>29.18082945093426</v>
+        <v>51.21959885377272</v>
       </c>
     </row>
     <row r="24">
@@ -3580,19 +3688,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>26.26605136147024</v>
+        <v>57.30429677534273</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>31.30487670196132</v>
+        <v>63.00468309779369</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>36.34370204245242</v>
+        <v>68.70506942024463</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>41.38252738294353</v>
+        <v>74.40545574269558</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>46.42135272343462</v>
+        <v>80.10584206514655</v>
       </c>
     </row>
     <row r="28">
@@ -3606,27 +3714,27 @@
       <c r="A29" s="15" t="inlineStr"/>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>428</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>1,001</t>
+          <t>1,178</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>1,751</t>
+          <t>1,928</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>2,501</t>
+          <t>2,678</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>3,251</t>
+          <t>3,428</t>
         </is>
       </c>
     </row>
@@ -3637,19 +3745,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>32.34228762248325</v>
+        <v>64.70365500027546</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>34.34299483246784</v>
+        <v>66.70436221026004</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>36.34370204245242</v>
+        <v>68.70506942024463</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>38.344409252437</v>
+        <v>70.70577663022921</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>40.34511646242159</v>
+        <v>72.70648384021381</v>
       </c>
     </row>
     <row r="32">
@@ -4377,19 +4485,19 @@
         <v>1</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1.075</v>
+        <v>1.1772</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1.12</v>
+        <v>1.2714</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1.165</v>
+        <v>1.3604</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>1.21</v>
+        <v>1.4488</v>
       </c>
     </row>
     <row r="26">

--- a/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
@@ -137,31 +137,30 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,6 +172,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1089,43 +1089,43 @@
       <c r="J1" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -1137,35 +1137,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="36">
         <f>'Income Statement'!B21</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="36">
         <f>'Income Statement'!C21</f>
         <v/>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="36">
         <f>'Income Statement'!D21</f>
         <v/>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="36">
         <f>'Income Statement'!E21</f>
         <v/>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="36">
         <f>'Income Statement'!F21</f>
         <v/>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="36">
         <f>'Income Statement'!G21</f>
         <v/>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="36">
         <f>'Income Statement'!H21</f>
         <v/>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="36">
         <f>'Income Statement'!I21</f>
         <v/>
       </c>
@@ -1176,35 +1176,35 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="36">
         <f>'Balance Sheet'!B17</f>
         <v/>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="36">
         <f>'Balance Sheet'!C17</f>
         <v/>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="36">
         <f>'Balance Sheet'!D17</f>
         <v/>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="36">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="36">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="36">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="36">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="36">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -1215,35 +1215,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="39">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="39">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="39">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="39">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="39">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -1254,35 +1254,35 @@
           <t>Price / book (at spot)</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="39">
         <f>Assumptions!$B$5/B6</f>
         <v/>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="39">
         <f>Assumptions!$B$5/C6</f>
         <v/>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <f>Assumptions!$B$5/D6</f>
         <v/>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="39">
         <f>Assumptions!$B$5/E6</f>
         <v/>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="39">
         <f>Assumptions!$B$5/F6</f>
         <v/>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="39">
         <f>Assumptions!$B$5/G6</f>
         <v/>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="39">
         <f>Assumptions!$B$5/H6</f>
         <v/>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="39">
         <f>Assumptions!$B$5/I6</f>
         <v/>
       </c>
@@ -1293,28 +1293,28 @@
           <t>EBITDA per tonne (EGP)</t>
         </is>
       </c>
-      <c r="D9" s="24">
-        <f>'Income Statement'!D14/'Unit Build'!B32</f>
-        <v/>
-      </c>
-      <c r="E9" s="24">
-        <f>'Income Statement'!E14/'Unit Build'!C32</f>
-        <v/>
-      </c>
-      <c r="F9" s="24">
-        <f>'Income Statement'!F14/'Unit Build'!D32</f>
-        <v/>
-      </c>
-      <c r="G9" s="24">
-        <f>'Income Statement'!G14/'Unit Build'!E32</f>
-        <v/>
-      </c>
-      <c r="H9" s="24">
-        <f>'Income Statement'!H14/'Unit Build'!F32</f>
-        <v/>
-      </c>
-      <c r="I9" s="24">
-        <f>'Income Statement'!I14/'Unit Build'!G32</f>
+      <c r="D9" s="26">
+        <f>'Income Statement'!D14/'Unit Build'!B55</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>'Income Statement'!E14/'Unit Build'!C55</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>'Income Statement'!F14/'Unit Build'!D55</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>'Income Statement'!G14/'Unit Build'!E55</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>'Income Statement'!H14/'Unit Build'!F55</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>'Income Statement'!I14/'Unit Build'!G55</f>
         <v/>
       </c>
     </row>
@@ -1324,35 +1324,35 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="18">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="18">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="18">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="18">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="18">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="18">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="18">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="18">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -1363,35 +1363,35 @@
           <t>Net (cash) / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="39">
         <f>'Balance Sheet'!B16/'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="39">
         <f>'Balance Sheet'!C16/'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="39">
         <f>'Balance Sheet'!D16/'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="39">
         <f>'Balance Sheet'!E16/'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="39">
         <f>'Balance Sheet'!F16/'Income Statement'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="39">
         <f>'Balance Sheet'!G16/'Income Statement'!G14</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="39">
         <f>'Balance Sheet'!H16/'Income Statement'!H14</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="39">
         <f>'Balance Sheet'!I16/'Income Statement'!I14</f>
         <v/>
       </c>
@@ -1418,7 +1418,7 @@
           <t>Shares issued (audited note 20)</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="31">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -1429,7 +1429,7 @@
           <t>Less treasury shares (audited note 21)</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="31">
         <f>-Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1440,7 +1440,7 @@
           <t>Shares outstanding — ADOPTED</t>
         </is>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="38">
         <f>B14+B15</f>
         <v/>
       </c>
@@ -1451,7 +1451,7 @@
           <t>Shares implied by the FY2025 dividend at EGP 5.34 per share</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="31">
         <f>Assumptions!$B$130/5.34</f>
         <v/>
       </c>
@@ -1462,7 +1462,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="40">
         <f>B17/B16-1</f>
         <v/>
       </c>
@@ -1473,7 +1473,7 @@
           <t>Issued capital implied at EGP 2 par (EGP mn)</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="26">
         <f>Assumptions!$B$6*2</f>
         <v/>
       </c>
@@ -1484,7 +1484,7 @@
           <t>Q1-2026 revenue growth on Q1-2025</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <f>Assumptions!$B$132/Assumptions!$B$133-1</f>
         <v/>
       </c>
@@ -1495,7 +1495,7 @@
           <t>FY2026 revenue implied by holding that growth</t>
         </is>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="26">
         <f>Assumptions!$B$54*Assumptions!$B$132/Assumptions!$B$133</f>
         <v/>
       </c>
@@ -1506,7 +1506,7 @@
           <t>FY2026 revenue this model forecasts</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="23">
         <f>DCF!B5</f>
         <v/>
       </c>
@@ -1517,7 +1517,7 @@
           <t>The forecast against the run rate</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="22">
         <f>B22/B21-1</f>
         <v/>
       </c>
@@ -1528,7 +1528,7 @@
           <t>Q1-2026 gross margin</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="22">
         <f>Assumptions!$B$134/Assumptions!$B$132</f>
         <v/>
       </c>
@@ -1539,7 +1539,7 @@
           <t>FY2025 gross margin</t>
         </is>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="18">
         <f>'Income Statement'!D8</f>
         <v/>
       </c>
@@ -1550,7 +1550,7 @@
           <t>Q1-2026 attributable profit annualised at four times</t>
         </is>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="26">
         <f>4*Assumptions!$B$135</f>
         <v/>
       </c>
@@ -1561,7 +1561,7 @@
           <t>FY2026 profit this model forecasts</t>
         </is>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="23">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
@@ -1572,7 +1572,7 @@
           <t>The forecast against the annualised first quarter</t>
         </is>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <f>B27/B26-1</f>
         <v/>
       </c>
@@ -1583,7 +1583,7 @@
           <t>Q1-2026 net cash, free of the declared dividend</t>
         </is>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="26">
         <f>Assumptions!$B$136-Assumptions!$B$137-Assumptions!$B$138</f>
         <v/>
       </c>
@@ -1594,7 +1594,7 @@
           <t>Net cash at the valuation date in this model</t>
         </is>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="23">
         <f>DCF!B40</f>
         <v/>
       </c>
@@ -1680,7 +1680,7 @@
           <t>FY2025 revenue, audited (the cyclical peak)</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>Assumptions!$B$54</f>
         <v/>
       </c>
@@ -1691,7 +1691,7 @@
           <t>Haircut to the revenue base</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="22">
         <f>Assumptions!$B$146</f>
         <v/>
       </c>
@@ -1702,7 +1702,7 @@
           <t>Normalised revenue</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -1713,7 +1713,7 @@
           <t>Mid-cycle EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <f>Assumptions!$B$145</f>
         <v/>
       </c>
@@ -1724,7 +1724,7 @@
           <t>Normalised EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -1735,7 +1735,7 @@
           <t>Less audited depreciation</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="26">
         <f>-Assumptions!$B$81</f>
         <v/>
       </c>
@@ -1746,7 +1746,7 @@
           <t>Normalised EBIT</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <f>B9+B10</f>
         <v/>
       </c>
@@ -1757,7 +1757,7 @@
           <t>Normalised NOPAT</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="24">
         <f>B11*(1-Assumptions!$B$9)</f>
         <v/>
       </c>
@@ -1768,7 +1768,7 @@
           <t>Memo: audited FY2023 EBITDA margin</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="18">
         <f>'Income Statement'!B15</f>
         <v/>
       </c>
@@ -1779,7 +1779,7 @@
           <t>Memo: audited FY2024 EBITDA margin</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="18">
         <f>'Income Statement'!C15</f>
         <v/>
       </c>
@@ -1790,7 +1790,7 @@
           <t>Memo: audited FY2025 EBITDA margin</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="18">
         <f>'Income Statement'!D15</f>
         <v/>
       </c>
@@ -1814,7 +1814,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="39">
         <f>Assumptions!$B$143</f>
         <v/>
       </c>
@@ -1825,7 +1825,7 @@
           <t>Implied enterprise value</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="26">
         <f>B9*B18</f>
         <v/>
       </c>
@@ -1836,7 +1836,7 @@
           <t>Plus net cash</t>
         </is>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="23">
         <f>DCF!B40</f>
         <v/>
       </c>
@@ -1847,7 +1847,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -1858,7 +1858,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="26">
         <f>B19+B20+B21</f>
         <v/>
       </c>
@@ -1869,7 +1869,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="32">
         <f>B22/DCF!$B$43</f>
         <v/>
       </c>
@@ -1893,7 +1893,7 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="39">
         <f>Assumptions!$B$144</f>
         <v/>
       </c>
@@ -1904,7 +1904,7 @@
           <t>Capitalised operating earnings</t>
         </is>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="26">
         <f>B12*B26</f>
         <v/>
       </c>
@@ -1915,7 +1915,7 @@
           <t>Plus net cash, at FACE</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="23">
         <f>DCF!B40</f>
         <v/>
       </c>
@@ -1926,7 +1926,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="41">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -1937,7 +1937,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="26">
         <f>B27+B28+B29</f>
         <v/>
       </c>
@@ -1948,7 +1948,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="32">
         <f>B30/DCF!$B$43</f>
         <v/>
       </c>
@@ -2018,7 +2018,7 @@
           <t>Cement capacity (Mt/yr, audited note 1)</t>
         </is>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="42">
         <f>Assumptions!$B$13</f>
         <v/>
       </c>
@@ -2029,7 +2029,7 @@
           <t>Replacement cost per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <f>Assumptions!$B$141</f>
         <v/>
       </c>
@@ -2040,7 +2040,7 @@
           <t>Justified enterprise value per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <f>Assumptions!$B$142</f>
         <v/>
       </c>
@@ -2051,7 +2051,7 @@
           <t>Discount to replacement cost</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <f>B7/B6-1</f>
         <v/>
       </c>
@@ -2062,7 +2062,7 @@
           <t>Implied enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <f>B7*B5*Assumptions!$B$11</f>
         <v/>
       </c>
@@ -2073,7 +2073,7 @@
           <t>Plus net cash</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="23">
         <f>DCF!B40</f>
         <v/>
       </c>
@@ -2084,7 +2084,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="41">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -2095,7 +2095,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="26">
         <f>B9+B10+B11</f>
         <v/>
       </c>
@@ -2106,7 +2106,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="32">
         <f>B12/DCF!$B$43</f>
         <v/>
       </c>
@@ -2117,7 +2117,7 @@
           <t>Memo: what the MARKET is paying per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="37">
         <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$117)/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
@@ -2128,7 +2128,7 @@
           <t>Memo: audited net book value of property and construction (EGP mn)</t>
         </is>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="26">
         <f>Assumptions!$B$105+Assumptions!$B$106</f>
         <v/>
       </c>
@@ -2139,7 +2139,7 @@
           <t>Memo: that book value per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="37">
         <f>B15/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
@@ -2158,67 +2158,67 @@
       <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Choice</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Adopted</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Fair value adopted</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Fair value alternative</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Cost of debt: currency composition as contracted (adopted) vs the pound-equivalent under uncovered interest parity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.89%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13.00%</t>
-        </is>
-      </c>
-      <c r="D20" s="38">
+          <t>13.36%</t>
+        </is>
+      </c>
+      <c r="D20" s="36">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E20" s="7" t="n">
-        <v>68.51141773004619</v>
-      </c>
-      <c r="F20" s="23">
+        <v>61.80028530387204</v>
+      </c>
+      <c r="F20" s="22">
         <f>E20/D20-1</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>Beta: contemporaneous regression (adopted) vs lead-lag sum-beta</t>
         </is>
@@ -2233,20 +2233,20 @@
           <t>0.919</t>
         </is>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="36">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E21" s="7" t="n">
-        <v>59.63546849895328</v>
-      </c>
-      <c r="F21" s="23">
+        <v>53.48004877782317</v>
+      </c>
+      <c r="F21" s="22">
         <f>E21/D21-1</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>Capex: economic maintenance in dollars per tonne (adopted) vs book depreciation</t>
         </is>
@@ -2261,14 +2261,14 @@
           <t>book depreciation</t>
         </is>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="36">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E22" s="7" t="n">
-        <v>73.70516700786516</v>
-      </c>
-      <c r="F22" s="23">
+        <v>67.29433644504972</v>
+      </c>
+      <c r="F22" s="22">
         <f>E22/D22-1</f>
         <v/>
       </c>
@@ -2294,18 +2294,18 @@
       <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr"/>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr"/>
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2317,15 +2317,15 @@
           <t>Capital expenditure (audited)</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="23">
         <f>Assumptions!$B$82</f>
         <v/>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="23">
         <f>Assumptions!$B$83</f>
         <v/>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="23">
         <f>Assumptions!$B$84</f>
         <v/>
       </c>
@@ -2336,15 +2336,15 @@
           <t>Capex / EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="22">
         <f>B28/'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="22">
         <f>C28/'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <f>D28/'Income Statement'!D14</f>
         <v/>
       </c>
@@ -2355,15 +2355,15 @@
           <t>Depreciation (audited)</t>
         </is>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="23">
         <f>Assumptions!$B$79</f>
         <v/>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="23">
         <f>Assumptions!$B$80</f>
         <v/>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="23">
         <f>Assumptions!$B$81</f>
         <v/>
       </c>
@@ -2374,15 +2374,15 @@
           <t>Net reinvestment (capex less depreciation)</t>
         </is>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="26">
         <f>B28-B30</f>
         <v/>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="26">
         <f>C28-C30</f>
         <v/>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="26">
         <f>D28-D30</f>
         <v/>
       </c>
@@ -2393,15 +2393,15 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="26">
         <f>'Income Statement'!B11*(1-'Income Statement'!B19)</f>
         <v/>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="26">
         <f>'Income Statement'!C11*(1-'Income Statement'!C19)</f>
         <v/>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="26">
         <f>'Income Statement'!D11*(1-'Income Statement'!D19)</f>
         <v/>
       </c>
@@ -2412,15 +2412,15 @@
           <t>Reinvestment rate</t>
         </is>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="22">
         <f>B31/B32</f>
         <v/>
       </c>
-      <c r="C33" s="23">
+      <c r="C33" s="22">
         <f>C31/C32</f>
         <v/>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="22">
         <f>D31/D32</f>
         <v/>
       </c>
@@ -2431,15 +2431,15 @@
           <t>Return on BOOK invested capital</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="22">
         <f>B32/(Assumptions!$B$116+Assumptions!$B$124)</f>
         <v/>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="22">
         <f>C32/(Assumptions!$B$115+Assumptions!$B$123)</f>
         <v/>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <f>D32/(Assumptions!$B$114+DCF!$C$44)</f>
         <v/>
       </c>
@@ -2450,15 +2450,15 @@
           <t>Implied growth (return x reinvestment)</t>
         </is>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <f>B34*B33</f>
         <v/>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="22">
         <f>C34*C33</f>
         <v/>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <f>D34*D33</f>
         <v/>
       </c>
@@ -2491,7 +2491,7 @@
           <t>Terminal return on capital, REPLACEMENT-COST basis</t>
         </is>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="18">
         <f>DCF!B24</f>
         <v/>
       </c>
@@ -2502,7 +2502,7 @@
           <t>Terminal return on capital, BOOK basis (FY2025)</t>
         </is>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="18">
         <f>DCF!B25</f>
         <v/>
       </c>
@@ -2513,7 +2513,7 @@
           <t>Terminal rate</t>
         </is>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="18">
         <f>DCF!$C$50</f>
         <v/>
       </c>
@@ -2524,7 +2524,7 @@
           <t>Terminal growth adopted</t>
         </is>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="22">
         <f>Assumptions!$B$49</f>
         <v/>
       </c>
@@ -2608,32 +2608,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Weighted contribution</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Versus spot</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Terminal value % of EV</t>
         </is>
@@ -2645,23 +2645,23 @@
           <t>DCF (cash flow)</t>
         </is>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="44">
         <f>DCF!B44</f>
         <v/>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="18">
         <f>Assumptions!$B$147</f>
         <v/>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <f>B5/Assumptions!$B$5-1</f>
         <v/>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="35">
         <f>DCF!B34</f>
         <v/>
       </c>
@@ -2672,19 +2672,19 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="44">
         <f>'Relative &amp; Normalized'!B23</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="18">
         <f>Assumptions!$B$148</f>
         <v/>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="33">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <f>B6/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2700,19 +2700,19 @@
           <t>Normalised earnings</t>
         </is>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="44">
         <f>'Relative &amp; Normalized'!B31</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="18">
         <f>Assumptions!$B$149</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="33">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <f>B7/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2728,19 +2728,19 @@
           <t>Asset / replacement cost</t>
         </is>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="44">
         <f>'Fundamental Valuation'!B13</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="18">
         <f>Assumptions!$B$150</f>
         <v/>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="33">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <f>B8/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2756,19 +2756,19 @@
           <t>WEIGHTED CENTRAL FAIR VALUE</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>SUMPRODUCT(B5:B8,C5:C8)</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="27">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="27">
         <f>B9/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2779,11 +2779,11 @@
           <t>Lowest lens</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="33">
         <f>MIN(B5:B8)</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f>B10/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2794,11 +2794,11 @@
           <t>Highest lens</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="33">
         <f>MAX(B5:B8)</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="22">
         <f>B11/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2809,7 +2809,7 @@
           <t>Market price, 6 August 2026</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="36">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -2820,7 +2820,7 @@
           <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="23">
         <f>DCF!C45</f>
         <v/>
       </c>
@@ -2839,23 +2839,23 @@
       <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Low (EGP)</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Central (EGP)</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>High (EGP)</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Versus spot</t>
         </is>
@@ -2868,15 +2868,15 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>58.81442632306862</v>
+        <v>59.0043470762966</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>68.87798358929108</v>
+        <v>69.06790434251907</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>78.94154085551355</v>
-      </c>
-      <c r="E17" s="23">
+        <v>79.13146160874153</v>
+      </c>
+      <c r="E17" s="22">
         <f>C17/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2888,15 +2888,15 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46.12046581464448</v>
+        <v>46.31038656787247</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>52.95018996654932</v>
+        <v>53.1401107197773</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>59.77991411845415</v>
-      </c>
-      <c r="E18" s="23">
+        <v>59.96983487168214</v>
+      </c>
+      <c r="E18" s="22">
         <f>C18/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2908,15 +2908,15 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>50.51763698507147</v>
+        <v>49.13650867854979</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>56.99985356819377</v>
+        <v>55.39428968170785</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>65.64280901235682</v>
-      </c>
-      <c r="E19" s="23">
+        <v>63.73799768591857</v>
+      </c>
+      <c r="E19" s="22">
         <f>C19/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2927,11 +2927,11 @@
           <t>Panel median</t>
         </is>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <f>MEDIAN(C17:C19)</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="22">
         <f>C20/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -3005,13 +3005,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr"/>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>One month</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Three months</t>
         </is>
@@ -3088,11 +3088,11 @@
           <t>Spot</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="36">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="36">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -3168,11 +3168,11 @@
           <t>Median versus spot</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <f>B9/B12-1</f>
         <v/>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="22">
         <f>C9/C12-1</f>
         <v/>
       </c>
@@ -3183,11 +3183,11 @@
           <t>Width of the 5th-95th band, as % of spot</t>
         </is>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <f>(B11-B7)/B12</f>
         <v/>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="22">
         <f>(C11-C7)/C12</f>
         <v/>
       </c>
@@ -3211,7 +3211,7 @@
           <t>Windows scored</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3320,35 +3320,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window cost of capital against terminal growth</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr"/>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>g = 3%</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>g = 4%</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>g = 5%</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>g = 6%</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>g = 7%</t>
         </is>
@@ -3356,269 +3356,269 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
-        <v>0.2089372422775459</v>
+        <v>0.2151592218162085</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>71.4593442293817</v>
+        <v>69.68480446917765</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>71.53145985731972</v>
+        <v>67.02354639938432</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>71.61699395194488</v>
+        <v>63.80382223673868</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>71.72007581703591</v>
+        <v>59.82923330334724</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>71.84672271565323</v>
+        <v>54.79906056677138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
-        <v>0.2239372422775459</v>
+        <v>0.2301592218162085</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>69.98304441235413</v>
+        <v>68.62467545844318</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>70.05332313660291</v>
+        <v>66.01291262285645</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70.13667853711605</v>
+        <v>62.85307028953042</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>70.23713473751145</v>
+        <v>58.95240248854102</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>70.36055573125974</v>
+        <v>54.01578309071213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
-        <v>0.2389372422775459</v>
+        <v>0.2451592218162085</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>68.55531419214742</v>
+        <v>67.59129378051799</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>68.62381854556868</v>
+        <v>65.02774111983067</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>68.70506942024463</v>
+        <v>61.9262258862966</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>68.80298934023183</v>
+        <v>58.09755998163097</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>68.92329424709673</v>
+        <v>53.2520649697296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
-        <v>0.2539372422775459</v>
+        <v>0.2601592218162085</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>67.1740906523508</v>
+        <v>66.58375921938828</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>67.24088047055777</v>
+        <v>64.0671754246041</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>67.32009778854915</v>
+        <v>61.0224854926659</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>67.4155669569766</v>
+        <v>57.26396758933526</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>67.53286085813211</v>
+        <v>52.50725070512303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
-        <v>0.2689372422775459</v>
+        <v>0.2751592218162085</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>65.83741847106668</v>
+        <v>65.60120983131745</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>65.90255103426088</v>
+        <v>63.13039547455369</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>65.97980273382618</v>
+        <v>60.14107971589755</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>66.0729030268443</v>
+        <v>56.45091846835627</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>66.18728651574119</v>
+        <v>51.78071261511543</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window rate against TERMINAL rate</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>terminal 13.7%</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>terminal 14.7%</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>terminal 15.7%</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>terminal 16.7%</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>terminal 17.7%</t>
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>terminal 12.5%</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>terminal 13.5%</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>terminal 14.5%</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>terminal 15.5%</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>terminal 16.5%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
-        <v>0.2089372422775459</v>
+        <v>0.2151592218162085</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>82.57728288508706</v>
+        <v>74.54479265991846</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>76.54139078979419</v>
+        <v>68.55901969603394</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>71.61699395194488</v>
+        <v>63.80382223673868</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>67.5205187341991</v>
+        <v>59.92930060886857</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>64.05735786089986</v>
+        <v>56.70691323937821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
-        <v>0.2239372422775459</v>
+        <v>0.2301592218162085</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>80.81079131273962</v>
+        <v>73.38777996625358</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.93251493373815</v>
+        <v>67.5169597654033</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>70.13667853711605</v>
+        <v>62.85307028953042</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>66.14712077749493</v>
+        <v>59.05293251959468</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>62.77432123211368</v>
+        <v>55.89239471828357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>0.2389372422775459</v>
+        <v>0.2451592218162085</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>79.10293545539865</v>
+        <v>72.26016858976557</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>73.37680543026032</v>
+        <v>66.50123914144211</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>68.70506942024463</v>
+        <v>61.9262258862966</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>64.81872089392061</v>
+        <v>58.19849137161848</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>61.53314958028578</v>
+        <v>55.09815671448623</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
-        <v>0.2539372422775459</v>
+        <v>0.2601592218162085</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>77.45121195721818</v>
+        <v>71.16096421323304</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>71.8719983043673</v>
+        <v>65.51096985080824</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>67.32009778854915</v>
+        <v>61.0224854926659</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>63.53341249464879</v>
+        <v>57.36524238774131</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>60.33207334377854</v>
+        <v>54.32352159125278</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>0.2689372422775459</v>
+        <v>0.2751592218162085</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>75.85324846929772</v>
+        <v>70.08921493439811</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>70.41594786025824</v>
+        <v>64.54530172310298</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>65.97980273382618</v>
+        <v>60.14107971589755</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>62.28938827364372</v>
+        <v>56.55248195173446</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>59.1694149628063</v>
+        <v>53.56784039640031</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): beta</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr"/>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr"/>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
@@ -3631,51 +3631,51 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>69.75553445865843</v>
+        <v>62.1918530339136</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>62.98956762602439</v>
+        <v>56.34393307051827</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>57.57727443120589</v>
+        <v>51.73278769457785</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>54.17757888983147</v>
+        <v>48.86156459044297</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>51.21959885377272</v>
+        <v>46.37628177687942</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): margin shift</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr"/>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr"/>
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>-4%</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>-2%</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>+0%</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>+2%</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>+4%</t>
         </is>
@@ -3688,53 +3688,53 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>57.30429677534273</v>
+        <v>49.80257797286092</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>63.00468309779369</v>
+        <v>55.86440192957877</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>68.70506942024463</v>
+        <v>61.9262258862966</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>74.40545574269558</v>
+        <v>67.98804984301447</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>80.10584206514655</v>
+        <v>74.04987379973232</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="46" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): net cash (EGP mn)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr"/>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>1,178</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>1,928</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>2,678</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>3,428</t>
+      <c r="A29" s="14" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>1,249</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>1,999</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>2,749</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>3,499</t>
         </is>
       </c>
     </row>
@@ -3745,19 +3745,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>64.70365500027546</v>
+        <v>57.92481146632743</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>66.70436221026004</v>
+        <v>59.92551867631202</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>68.70506942024463</v>
+        <v>61.9262258862966</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>70.70577663022921</v>
+        <v>63.92693309628118</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>72.70648384021381</v>
+        <v>65.92764030626577</v>
       </c>
     </row>
     <row r="32">
@@ -3770,12 +3770,20 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>terminal return on capital sits below the terminal rate. That is the model being consistent.</t>
+          <t>terminal return on replacement-cost capital sits below the hurdle. Read off the grid, never typed:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>revision 3 carried this note unchanged after its own grid had reversed, and it contradicted itself.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
@@ -3817,33 +3825,33 @@
       <c r="H1" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Profit (EGP mn)</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Market cap (EGP mn)</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Price / earnings</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Price / sales</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Net margin</t>
         </is>
@@ -3855,27 +3863,27 @@
           <t>Arabian Cement (ARCC)</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>Assumptions!$B$54</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="23">
         <f>Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>DCF!C45</f>
         <v/>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="39">
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="39">
         <f>D5/B5</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <f>C5/B5</f>
         <v/>
       </c>
@@ -3886,27 +3894,27 @@
           <t>Sinai Cement (SCEM)</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>Assumptions!$B$157</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>Assumptions!$B$158</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f>Assumptions!$B$159</f>
         <v/>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="39">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="39">
         <f>D6/B6</f>
         <v/>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <f>C6/B6</f>
         <v/>
       </c>
@@ -3917,27 +3925,27 @@
           <t>Misr Beni Suef Cement (MBSC)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="23">
         <f>Assumptions!$B$160</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>Assumptions!$B$161</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="23">
         <f>Assumptions!$B$162</f>
         <v/>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="39">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <f>D7/B7</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <f>C7/B7</f>
         <v/>
       </c>
@@ -3948,7 +3956,7 @@
           <t>Peer average price / earnings (excluding the subject)</t>
         </is>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="46">
         <f>AVERAGE(E6:E7)</f>
         <v/>
       </c>
@@ -3959,7 +3967,7 @@
           <t>Subject premium / (discount) to the peer average</t>
         </is>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f>E5/E9-1</f>
         <v/>
       </c>
@@ -3984,7 +3992,7 @@
           <t>Nameplate capacity (Mt)</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="47">
         <f>Assumptions!$B$152</f>
         <v/>
       </c>
@@ -3995,7 +4003,7 @@
           <t>Production 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="47">
         <f>Assumptions!$B$153</f>
         <v/>
       </c>
@@ -4006,7 +4014,7 @@
           <t>Domestic consumption 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="47">
         <f>Assumptions!$B$154</f>
         <v/>
       </c>
@@ -4017,7 +4025,7 @@
           <t>Exports 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="47">
         <f>Assumptions!$B$155</f>
         <v/>
       </c>
@@ -4028,7 +4036,7 @@
           <t>Dormant capacity under revival (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="47">
         <f>Assumptions!$B$156</f>
         <v/>
       </c>
@@ -4039,7 +4047,7 @@
           <t>Sector utilisation</t>
         </is>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="22">
         <f>B14/B13</f>
         <v/>
       </c>
@@ -4050,7 +4058,7 @@
           <t>The subject as a share of national capacity</t>
         </is>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="22">
         <f>Assumptions!$B$13/B13</f>
         <v/>
       </c>
@@ -4061,7 +4069,7 @@
           <t>Revival capacity as a share of consumption</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="22">
         <f>B17/B15</f>
         <v/>
       </c>
@@ -4072,8 +4080,8 @@
           <t>The subject's own volume as a share of national production</t>
         </is>
       </c>
-      <c r="B21" s="23">
-        <f>'Unit Build'!B12/B14</f>
+      <c r="B21" s="22">
+        <f>'Unit Build'!B18/B14</f>
         <v/>
       </c>
     </row>
@@ -4299,7 +4307,7 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>0.84</v>
+        <v>0.733</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -4310,7 +4318,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>PRICE CALIBRATION — the volume build is anchored on these</t>
+          <t>EXPORT SPLIT — the one ratio the export leg needs; both prices come OUT</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -4325,154 +4333,159 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Local realised price</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>EGP/t</t>
-        </is>
+          <t>Export clinker price as a fraction of export cement</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Export price</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>62</v>
+          <t>Average USD/EGP FY2025</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>49.26</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>USD/t</t>
+          <t>audited note 2.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Average USD/EGP FY2025</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>audited note 2.5</t>
-        </is>
+          <t>Services revenue as a share of goods revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.06325</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Services revenue as a share of goods revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>0.06325</v>
-      </c>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>PATHS — FY2025A then FY2026E to FY2030E</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>PATHS — FY2025A then FY2026E to FY2030E</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
+      <c r="A21" s="14" t="inlineStr"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr"/>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>FY2025A</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kiln utilisation  (THE volume driver)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capacity utilisation</t>
+          <t>Clinker sold as clinker, share of clinker made</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.697</v>
+        <v>0.3377</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>0.73</v>
+        <v>0.33</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0.765</v>
+        <v>0.31</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.775</v>
+        <v>0.305</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.782</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Export share of volume</t>
+          <t>Cement exported, share of cement made</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.3153</v>
+        <v>0.1772</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.295</v>
+        <v>0.175</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="25">
@@ -4616,28 +4629,28 @@
       <c r="I30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr"/>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr"/>
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -4766,7 +4779,7 @@
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>0.2231</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="40">
@@ -4796,7 +4809,7 @@
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>0.021</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="43">
@@ -4826,7 +4839,7 @@
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>0.1</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="46">
@@ -4836,7 +4849,7 @@
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="47">
@@ -4900,7 +4913,7 @@
           <t>FY2023 sales (net)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
+      <c r="B52" s="15" t="n">
         <v>6042.831338</v>
       </c>
     </row>
@@ -4910,7 +4923,7 @@
           <t>FY2024 sales (net)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="n">
+      <c r="B53" s="15" t="n">
         <v>8729.782821000001</v>
       </c>
     </row>
@@ -4920,7 +4933,7 @@
           <t>FY2025 sales (net)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="n">
+      <c r="B54" s="15" t="n">
         <v>12447.320081</v>
       </c>
     </row>
@@ -4930,7 +4943,7 @@
           <t>FY2023 cost of sales</t>
         </is>
       </c>
-      <c r="B55" s="14" t="n">
+      <c r="B55" s="15" t="n">
         <v>4759.815212</v>
       </c>
     </row>
@@ -4940,7 +4953,7 @@
           <t>FY2024 cost of sales</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="15" t="n">
         <v>6642.972487</v>
       </c>
     </row>
@@ -4950,7 +4963,7 @@
           <t>FY2025 cost of sales</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="15" t="n">
         <v>7389.054416</v>
       </c>
     </row>
@@ -4960,7 +4973,7 @@
           <t>FY2023 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B58" s="14" t="n">
+      <c r="B58" s="15" t="n">
         <v>183.940276</v>
       </c>
     </row>
@@ -4970,7 +4983,7 @@
           <t>FY2024 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B59" s="14" t="n">
+      <c r="B59" s="15" t="n">
         <v>267.798104</v>
       </c>
     </row>
@@ -4980,7 +4993,7 @@
           <t>FY2025 general and administrative expenses</t>
         </is>
       </c>
-      <c r="B60" s="14" t="n">
+      <c r="B60" s="15" t="n">
         <v>384.332833</v>
       </c>
     </row>
@@ -4990,7 +5003,7 @@
           <t>FY2023 provisions charged</t>
         </is>
       </c>
-      <c r="B61" s="14" t="n">
+      <c r="B61" s="15" t="n">
         <v>15.220195</v>
       </c>
     </row>
@@ -5000,7 +5013,7 @@
           <t>FY2024 provisions charged</t>
         </is>
       </c>
-      <c r="B62" s="14" t="n">
+      <c r="B62" s="15" t="n">
         <v>56.05295</v>
       </c>
     </row>
@@ -5010,7 +5023,7 @@
           <t>FY2025 provisions charged</t>
         </is>
       </c>
-      <c r="B63" s="14" t="n">
+      <c r="B63" s="15" t="n">
         <v>74.505707</v>
       </c>
     </row>
@@ -5020,7 +5033,7 @@
           <t>FY2023 expected credit losses</t>
         </is>
       </c>
-      <c r="B64" s="14" t="n">
+      <c r="B64" s="15" t="n">
         <v>4.745753</v>
       </c>
     </row>
@@ -5030,7 +5043,7 @@
           <t>FY2024 expected credit losses</t>
         </is>
       </c>
-      <c r="B65" s="14" t="n">
+      <c r="B65" s="15" t="n">
         <v>-1.106452</v>
       </c>
     </row>
@@ -5040,7 +5053,7 @@
           <t>FY2025 expected credit losses</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
+      <c r="B66" s="15" t="n">
         <v>3.603563</v>
       </c>
     </row>
@@ -5050,7 +5063,7 @@
           <t>FY2023 profit before tax</t>
         </is>
       </c>
-      <c r="B67" s="14" t="n">
+      <c r="B67" s="15" t="n">
         <v>930.231432</v>
       </c>
     </row>
@@ -5060,7 +5073,7 @@
           <t>FY2024 profit before tax</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
+      <c r="B68" s="15" t="n">
         <v>1505.866118</v>
       </c>
     </row>
@@ -5070,7 +5083,7 @@
           <t>FY2025 profit before tax</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="15" t="n">
         <v>4725.157878</v>
       </c>
     </row>
@@ -5080,7 +5093,7 @@
           <t>FY2023 income tax</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n">
+      <c r="B70" s="15" t="n">
         <v>232.732802</v>
       </c>
     </row>
@@ -5090,7 +5103,7 @@
           <t>FY2024 income tax</t>
         </is>
       </c>
-      <c r="B71" s="14" t="n">
+      <c r="B71" s="15" t="n">
         <v>345.730996</v>
       </c>
     </row>
@@ -5100,7 +5113,7 @@
           <t>FY2025 income tax</t>
         </is>
       </c>
-      <c r="B72" s="14" t="n">
+      <c r="B72" s="15" t="n">
         <v>1125.467657</v>
       </c>
     </row>
@@ -5110,7 +5123,7 @@
           <t>FY2023 attributable profit</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n">
+      <c r="B73" s="15" t="n">
         <v>697.488741</v>
       </c>
     </row>
@@ -5120,7 +5133,7 @@
           <t>FY2024 attributable profit</t>
         </is>
       </c>
-      <c r="B74" s="14" t="n">
+      <c r="B74" s="15" t="n">
         <v>1160.129411</v>
       </c>
     </row>
@@ -5130,7 +5143,7 @@
           <t>FY2025 attributable profit</t>
         </is>
       </c>
-      <c r="B75" s="14" t="n">
+      <c r="B75" s="15" t="n">
         <v>3599.585937</v>
       </c>
     </row>
@@ -5185,7 +5198,7 @@
           <t>FY2023 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B79" s="14" t="n">
+      <c r="B79" s="15" t="n">
         <v>250.424521</v>
       </c>
     </row>
@@ -5195,7 +5208,7 @@
           <t>FY2024 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B80" s="14" t="n">
+      <c r="B80" s="15" t="n">
         <v>256.801527</v>
       </c>
     </row>
@@ -5205,7 +5218,7 @@
           <t>FY2025 depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B81" s="14" t="n">
+      <c r="B81" s="15" t="n">
         <v>289.771295</v>
       </c>
     </row>
@@ -5215,7 +5228,7 @@
           <t>FY2023 capital expenditure</t>
         </is>
       </c>
-      <c r="B82" s="14" t="n">
+      <c r="B82" s="15" t="n">
         <v>58.543963</v>
       </c>
     </row>
@@ -5225,7 +5238,7 @@
           <t>FY2024 capital expenditure</t>
         </is>
       </c>
-      <c r="B83" s="14" t="n">
+      <c r="B83" s="15" t="n">
         <v>912.0154</v>
       </c>
     </row>
@@ -5235,7 +5248,7 @@
           <t>FY2025 capital expenditure</t>
         </is>
       </c>
-      <c r="B84" s="14" t="n">
+      <c r="B84" s="15" t="n">
         <v>796.47076</v>
       </c>
     </row>
@@ -5245,7 +5258,7 @@
           <t>FY2025 interest income</t>
         </is>
       </c>
-      <c r="B85" s="14" t="n">
+      <c r="B85" s="15" t="n">
         <v>226.274781</v>
       </c>
     </row>
@@ -5255,7 +5268,7 @@
           <t>FY2025 other income</t>
         </is>
       </c>
-      <c r="B86" s="14" t="n">
+      <c r="B86" s="15" t="n">
         <v>53.339508</v>
       </c>
     </row>
@@ -5265,7 +5278,7 @@
           <t>FY2025 finance costs</t>
         </is>
       </c>
-      <c r="B87" s="14" t="n">
+      <c r="B87" s="15" t="n">
         <v>49.841733</v>
       </c>
     </row>
@@ -5275,7 +5288,7 @@
           <t>FY2025 foreign exchange differences</t>
         </is>
       </c>
-      <c r="B88" s="14" t="n">
+      <c r="B88" s="15" t="n">
         <v>-101.57824</v>
       </c>
     </row>
@@ -5300,7 +5313,7 @@
           <t>FY2025 local sales of goods</t>
         </is>
       </c>
-      <c r="B90" s="14" t="n">
+      <c r="B90" s="15" t="n">
         <v>8350.454610000001</v>
       </c>
     </row>
@@ -5310,7 +5323,7 @@
           <t>FY2025 local services</t>
         </is>
       </c>
-      <c r="B91" s="14" t="n">
+      <c r="B91" s="15" t="n">
         <v>281.863546</v>
       </c>
     </row>
@@ -5320,7 +5333,7 @@
           <t>FY2025 export sales of goods</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n">
+      <c r="B92" s="15" t="n">
         <v>3356.422381</v>
       </c>
     </row>
@@ -5330,7 +5343,7 @@
           <t>FY2025 export services</t>
         </is>
       </c>
-      <c r="B93" s="14" t="n">
+      <c r="B93" s="15" t="n">
         <v>458.579544</v>
       </c>
     </row>
@@ -5340,7 +5353,7 @@
           <t>FY2024 total local sales</t>
         </is>
       </c>
-      <c r="B94" s="14" t="n">
+      <c r="B94" s="15" t="n">
         <v>4883.304477</v>
       </c>
     </row>
@@ -5350,7 +5363,7 @@
           <t>FY2024 total export sales</t>
         </is>
       </c>
-      <c r="B95" s="14" t="n">
+      <c r="B95" s="15" t="n">
         <v>3846.478344</v>
       </c>
     </row>
@@ -5360,7 +5373,7 @@
           <t>FY2025 cost of sales — materials and fuel</t>
         </is>
       </c>
-      <c r="B96" s="14" t="n">
+      <c r="B96" s="15" t="n">
         <v>5698.184715</v>
       </c>
     </row>
@@ -5370,7 +5383,7 @@
           <t>FY2025 cost of sales — transportation</t>
         </is>
       </c>
-      <c r="B97" s="14" t="n">
+      <c r="B97" s="15" t="n">
         <v>764.279332</v>
       </c>
     </row>
@@ -5380,7 +5393,7 @@
           <t>FY2025 cost of sales — overheads</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n">
+      <c r="B98" s="15" t="n">
         <v>641.143208</v>
       </c>
     </row>
@@ -5390,7 +5403,7 @@
           <t>FY2025 administrative depreciation</t>
         </is>
       </c>
-      <c r="B99" s="14" t="n">
+      <c r="B99" s="15" t="n">
         <v>4.324134</v>
       </c>
     </row>
@@ -5415,7 +5428,7 @@
           <t>Total assets FY2025</t>
         </is>
       </c>
-      <c r="B101" s="14" t="n">
+      <c r="B101" s="15" t="n">
         <v>8783.721849</v>
       </c>
     </row>
@@ -5425,7 +5438,7 @@
           <t>Total assets FY2024</t>
         </is>
       </c>
-      <c r="B102" s="14" t="n">
+      <c r="B102" s="15" t="n">
         <v>5848.616103</v>
       </c>
     </row>
@@ -5435,7 +5448,7 @@
           <t>Total assets FY2023</t>
         </is>
       </c>
-      <c r="B103" s="14" t="n">
+      <c r="B103" s="15" t="n">
         <v>3887.527427</v>
       </c>
     </row>
@@ -5445,7 +5458,7 @@
           <t>Total liabilities FY2025</t>
         </is>
       </c>
-      <c r="B104" s="14" t="n">
+      <c r="B104" s="15" t="n">
         <v>4140.989609</v>
       </c>
     </row>
@@ -5455,7 +5468,7 @@
           <t>Property, plant and equipment FY2025</t>
         </is>
       </c>
-      <c r="B105" s="14" t="n">
+      <c r="B105" s="15" t="n">
         <v>2522.323523</v>
       </c>
     </row>
@@ -5465,7 +5478,7 @@
           <t>Assets under construction FY2025</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
+      <c r="B106" s="15" t="n">
         <v>391.543753</v>
       </c>
     </row>
@@ -5475,7 +5488,7 @@
           <t>Intangible assets FY2025</t>
         </is>
       </c>
-      <c r="B107" s="14" t="n">
+      <c r="B107" s="15" t="n">
         <v>106.799617</v>
       </c>
     </row>
@@ -5485,7 +5498,7 @@
           <t>Inventories FY2025</t>
         </is>
       </c>
-      <c r="B108" s="14" t="n">
+      <c r="B108" s="15" t="n">
         <v>1053.646218</v>
       </c>
     </row>
@@ -5495,7 +5508,7 @@
           <t>Trade receivables FY2025</t>
         </is>
       </c>
-      <c r="B109" s="14" t="n">
+      <c r="B109" s="15" t="n">
         <v>244.416417</v>
       </c>
     </row>
@@ -5505,7 +5518,7 @@
           <t>Debtors and other debit balances FY2025</t>
         </is>
       </c>
-      <c r="B110" s="14" t="n">
+      <c r="B110" s="15" t="n">
         <v>1004.779062</v>
       </c>
     </row>
@@ -5515,7 +5528,7 @@
           <t>Cash and bank balances FY2025</t>
         </is>
       </c>
-      <c r="B111" s="14" t="n">
+      <c r="B111" s="15" t="n">
         <v>3459.391229</v>
       </c>
     </row>
@@ -5525,7 +5538,7 @@
           <t>Cash and bank balances FY2024</t>
         </is>
       </c>
-      <c r="B112" s="14" t="n">
+      <c r="B112" s="15" t="n">
         <v>1687.062873</v>
       </c>
     </row>
@@ -5535,7 +5548,7 @@
           <t>Cash and bank balances FY2023</t>
         </is>
       </c>
-      <c r="B113" s="14" t="n">
+      <c r="B113" s="15" t="n">
         <v>561.09968</v>
       </c>
     </row>
@@ -5545,7 +5558,7 @@
           <t>Equity attributable to owners FY2025</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
+      <c r="B114" s="15" t="n">
         <v>4642.574235</v>
       </c>
     </row>
@@ -5555,7 +5568,7 @@
           <t>Equity attributable to owners FY2024</t>
         </is>
       </c>
-      <c r="B115" s="14" t="n">
+      <c r="B115" s="15" t="n">
         <v>2303.472299</v>
       </c>
     </row>
@@ -5565,7 +5578,7 @@
           <t>Equity attributable to owners FY2023</t>
         </is>
       </c>
-      <c r="B116" s="14" t="n">
+      <c r="B116" s="15" t="n">
         <v>1754.221659</v>
       </c>
     </row>
@@ -5600,7 +5613,7 @@
           <t>CIB credit facilities — EGP</t>
         </is>
       </c>
-      <c r="B119" s="14" t="n">
+      <c r="B119" s="15" t="n">
         <v>99.916937</v>
       </c>
     </row>
@@ -5610,7 +5623,7 @@
           <t>National Bank of Egypt facility — EUR</t>
         </is>
       </c>
-      <c r="B120" s="14" t="n">
+      <c r="B120" s="15" t="n">
         <v>145.741484</v>
       </c>
     </row>
@@ -5620,7 +5633,7 @@
           <t>EBRD facility — EUR</t>
         </is>
       </c>
-      <c r="B121" s="14" t="n">
+      <c r="B121" s="15" t="n">
         <v>888.274195</v>
       </c>
     </row>
@@ -5630,7 +5643,7 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="B122" s="14" t="n">
+      <c r="B122" s="15" t="n">
         <v>1.176042</v>
       </c>
     </row>
@@ -5640,7 +5653,7 @@
           <t>Total interest-bearing debt FY2024</t>
         </is>
       </c>
-      <c r="B123" s="14" t="n">
+      <c r="B123" s="15" t="n">
         <v>760.917684</v>
       </c>
     </row>
@@ -5650,7 +5663,7 @@
           <t>Total interest-bearing debt FY2023</t>
         </is>
       </c>
-      <c r="B124" s="14" t="n">
+      <c r="B124" s="15" t="n">
         <v>90.07427300000001</v>
       </c>
     </row>
@@ -5660,7 +5673,7 @@
           <t>FY2025 loan interest expense</t>
         </is>
       </c>
-      <c r="B125" s="14" t="n">
+      <c r="B125" s="15" t="n">
         <v>24.61313</v>
       </c>
     </row>
@@ -5670,7 +5683,7 @@
           <t>FY2025 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B126" s="14" t="n">
+      <c r="B126" s="15" t="n">
         <v>23.00737</v>
       </c>
     </row>
@@ -5680,7 +5693,7 @@
           <t>FY2024 loan interest expense</t>
         </is>
       </c>
-      <c r="B127" s="14" t="n">
+      <c r="B127" s="15" t="n">
         <v>2.754107</v>
       </c>
     </row>
@@ -5690,7 +5703,7 @@
           <t>FY2024 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B128" s="14" t="n">
+      <c r="B128" s="15" t="n">
         <v>85.95302599999999</v>
       </c>
     </row>
@@ -5715,7 +5728,7 @@
           <t>FY2025 dividend declared</t>
         </is>
       </c>
-      <c r="B130" s="14" t="n">
+      <c r="B130" s="15" t="n">
         <v>2001.79216</v>
       </c>
     </row>
@@ -5725,7 +5738,7 @@
           <t>FY2024 dividend approved and paid</t>
         </is>
       </c>
-      <c r="B131" s="14" t="n">
+      <c r="B131" s="15" t="n">
         <v>1102.110289</v>
       </c>
     </row>
@@ -5735,7 +5748,7 @@
           <t>Q1-2026 sales</t>
         </is>
       </c>
-      <c r="B132" s="14" t="n">
+      <c r="B132" s="15" t="n">
         <v>2995.95935</v>
       </c>
     </row>
@@ -5745,7 +5758,7 @@
           <t>Q1-2025 sales</t>
         </is>
       </c>
-      <c r="B133" s="14" t="n">
+      <c r="B133" s="15" t="n">
         <v>2554.448091</v>
       </c>
     </row>
@@ -5755,7 +5768,7 @@
           <t>Q1-2026 gross profit</t>
         </is>
       </c>
-      <c r="B134" s="14" t="n">
+      <c r="B134" s="15" t="n">
         <v>1286.145881</v>
       </c>
     </row>
@@ -5765,7 +5778,7 @@
           <t>Q1-2026 attributable profit</t>
         </is>
       </c>
-      <c r="B135" s="14" t="n">
+      <c r="B135" s="15" t="n">
         <v>943.068309</v>
       </c>
     </row>
@@ -5775,7 +5788,7 @@
           <t>Q1-2026 cash and bank balances</t>
         </is>
       </c>
-      <c r="B136" s="14" t="n">
+      <c r="B136" s="15" t="n">
         <v>4379.627379</v>
       </c>
     </row>
@@ -5785,7 +5798,7 @@
           <t>Q1-2026 interest-bearing debt</t>
         </is>
       </c>
-      <c r="B137" s="14" t="n">
+      <c r="B137" s="15" t="n">
         <v>1260.509089</v>
       </c>
     </row>
@@ -5795,7 +5808,7 @@
           <t>Q1-2026 dividends payable</t>
         </is>
       </c>
-      <c r="B138" s="14" t="n">
+      <c r="B138" s="15" t="n">
         <v>2001.79216</v>
       </c>
     </row>
@@ -5805,7 +5818,7 @@
           <t>Q1-2026 finance costs</t>
         </is>
       </c>
-      <c r="B139" s="14" t="n">
+      <c r="B139" s="15" t="n">
         <v>11.168843</v>
       </c>
     </row>
@@ -5830,7 +5843,7 @@
           <t>Replacement cost per annual tonne</t>
         </is>
       </c>
-      <c r="B141" s="14" t="n">
+      <c r="B141" s="15" t="n">
         <v>130</v>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -5845,7 +5858,7 @@
           <t>Justified enterprise value per annual tonne</t>
         </is>
       </c>
-      <c r="B142" s="14" t="n">
+      <c r="B142" s="15" t="n">
         <v>95</v>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -6030,7 +6043,7 @@
           <t>Peer — Sinai Cement revenue</t>
         </is>
       </c>
-      <c r="B157" s="14" t="n">
+      <c r="B157" s="15" t="n">
         <v>9090</v>
       </c>
     </row>
@@ -6040,7 +6053,7 @@
           <t>Peer — Sinai Cement profit</t>
         </is>
       </c>
-      <c r="B158" s="14" t="n">
+      <c r="B158" s="15" t="n">
         <v>2290</v>
       </c>
     </row>
@@ -6050,7 +6063,7 @@
           <t>Peer — Sinai Cement market capitalisation</t>
         </is>
       </c>
-      <c r="B159" s="14" t="n">
+      <c r="B159" s="15" t="n">
         <v>20604.19</v>
       </c>
     </row>
@@ -6060,7 +6073,7 @@
           <t>Peer — Misr Beni Suef revenue</t>
         </is>
       </c>
-      <c r="B160" s="14" t="n">
+      <c r="B160" s="15" t="n">
         <v>5700</v>
       </c>
     </row>
@@ -6070,7 +6083,7 @@
           <t>Peer — Misr Beni Suef profit</t>
         </is>
       </c>
-      <c r="B161" s="14" t="n">
+      <c r="B161" s="15" t="n">
         <v>3946</v>
       </c>
     </row>
@@ -6080,7 +6093,7 @@
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B162" s="14" t="n">
+      <c r="B162" s="15" t="n">
         <v>13730</v>
       </c>
     </row>
@@ -6113,7 +6126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6131,7 +6144,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unit build — volume DERIVED from the audited revenue split</t>
+          <t>Unit build — the PLANT drives the tonnes, and the prices come OUT</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6147,14 +6160,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>EBITDA is a RESULT of this sheet, never an input.</t>
+          <t>Revision 3 assumed a price and divided revenue by it. That made the FY2025 check an identity that could not fail. Here the drivers are physical and all three realised prices are derived, so they can be tested against the market and disagree.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>FY2025 CALIBRATION — FROM THE AUDITED NOTES</t>
+          <t>FY2025 — THE PLANT IN TONNES (drivers in green, everything else derived)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -6170,98 +6183,98 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Export sales of goods (audited note 4)</t>
+          <t>Kiln clinker capacity (Mt, audited note 1)</t>
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Assumptions!$B$92</f>
+        <f>Assumptions!$B$14</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Export price (USD/t)</t>
+          <t>Kiln utilisation</t>
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Assumptions!$B$18</f>
+        <f>Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average USD/EGP FY2025 (audited note 2.5)</t>
+          <t>Clinker produced (Mt)</t>
         </is>
       </c>
       <c r="B7" s="19">
-        <f>Assumptions!$B$19</f>
+        <f>B5*B6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Export volume (Mt) — DERIVED</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>B5/(B6*B7)</f>
+          <t>Share sold as clinker</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Local sales of goods (audited note 4)</t>
-        </is>
-      </c>
-      <c r="B9" s="17">
-        <f>Assumptions!$B$90</f>
+          <t>Clinker EXPORTED (Mt)</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>B7*B8</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Local price (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B10" s="17">
-        <f>Assumptions!$B$17</f>
+          <t>Clinker ground into cement (Mt)</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>B7-B9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Local volume (Mt) — DERIVED</t>
+          <t>Clinker factor (t clinker / t cement)</t>
         </is>
       </c>
       <c r="B11" s="20">
-        <f>B9/B10</f>
+        <f>Assumptions!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAL VOLUME FY2025 (Mt)</t>
+          <t>Cement produced (Mt)</t>
         </is>
       </c>
       <c r="B12" s="21">
-        <f>B8+B11</f>
+        <f>B10/B11</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cement capacity (Mt)</t>
-        </is>
-      </c>
-      <c r="B13" s="19">
+          <t>Cement mill capacity (Mt, audited note 1)</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
         <f>Assumptions!$B$13</f>
         <v/>
       </c>
@@ -6269,7 +6282,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Implied utilisation — the cross-check</t>
+          <t>Mill utilisation</t>
         </is>
       </c>
       <c r="B14" s="22">
@@ -6280,1081 +6293,1503 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>National sector utilisation, for comparison</t>
-        </is>
-      </c>
-      <c r="B15" s="23">
-        <f>Assumptions!$B$153/Assumptions!$B$152</f>
+          <t>Cement exported, share of cement made</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Export share of volume</t>
-        </is>
-      </c>
-      <c r="B16" s="23">
-        <f>B8/B12</f>
+          <t>Cement EXPORTED (Mt)</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>B12*B15</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Export share of revenue</t>
-        </is>
-      </c>
-      <c r="B17" s="23">
-        <f>(Assumptions!$B$92+Assumptions!$B$93)/Assumptions!$B$54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 CASH COST PER TONNE — FROM THE AUDITED COST NOTES</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
+          <t>Cement sold LOCALLY (Mt)</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>B12-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TOTAL DESPATCHES FY2025 (Mt)</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>B12+B9</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Materials and fuel (note 5)</t>
-        </is>
-      </c>
-      <c r="B20" s="17">
-        <f>Assumptions!$B$96</f>
-        <v/>
-      </c>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 PRICES — DERIVED FROM THE AUDITED REVENUE NOTE, AND TESTABLE</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Transportation (note 5)</t>
-        </is>
-      </c>
-      <c r="B21" s="17">
-        <f>Assumptions!$B$97</f>
+          <t>Local sales of goods (audited note 4)</t>
+        </is>
+      </c>
+      <c r="B21" s="23">
+        <f>Assumptions!$B$90</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Overheads (note 5) plus cash administration (note 6)</t>
+          <t>LOCAL CEMENT PRICE (EGP/t) — DERIVED</t>
         </is>
       </c>
       <c r="B22" s="24">
-        <f>Assumptions!$B$98+Assumptions!$B$60-Assumptions!$B$99+Assumptions!$B$63+Assumptions!$B$66</f>
+        <f>B21/B17</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Total cash cost (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B23" s="24">
-        <f>SUM(B20:B22)</f>
+          <t>Export sales of goods (audited note 4)</t>
+        </is>
+      </c>
+      <c r="B23" s="23">
+        <f>Assumptions!$B$92</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Materials and fuel per tonne</t>
-        </is>
-      </c>
-      <c r="B24" s="24">
-        <f>B20/B12</f>
+          <t>Clinker price as a fraction of cement</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>Assumptions!$B$17</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Transportation per tonne</t>
-        </is>
-      </c>
-      <c r="B25" s="24">
-        <f>B21/B12</f>
+          <t>Export cement-equivalent tonnes</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>B16+B9*B24</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Overheads and administration per tonne</t>
-        </is>
-      </c>
-      <c r="B26" s="24">
-        <f>B22/B12</f>
+          <t>EXPORT CEMENT PRICE (USD/t) — DERIVED</t>
+        </is>
+      </c>
+      <c r="B26" s="25">
+        <f>B23/B25/Assumptions!$B$18</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOTAL CASH COST PER TONNE</t>
+          <t>EXPORT CLINKER PRICE (USD/t) — DERIVED</t>
         </is>
       </c>
       <c r="B27" s="25">
-        <f>B23/B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>THE BUILD — FY2025A THEN FY2026E TO FY2030E</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
+        <f>B26*B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cement exports as a share of cement made — against a 30% statutory cap</t>
+        </is>
+      </c>
+      <c r="B28" s="22">
+        <f>B16/B12</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr"/>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>FY2025A</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 CASH COST — DISCLOSED, AND ALLOCATED TO ITS OWN DRIVER</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Capacity utilisation</t>
-        </is>
-      </c>
-      <c r="B31" s="26">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="C31" s="26">
-        <f>Assumptions!$C$23</f>
-        <v/>
-      </c>
-      <c r="D31" s="26">
-        <f>Assumptions!$D$23</f>
-        <v/>
-      </c>
-      <c r="E31" s="26">
-        <f>Assumptions!$E$23</f>
-        <v/>
-      </c>
-      <c r="F31" s="26">
-        <f>Assumptions!$F$23</f>
-        <v/>
-      </c>
-      <c r="G31" s="26">
-        <f>Assumptions!$G$23</f>
+          <t>Materials and fuel (note 5)</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>Assumptions!$B$96</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B32" s="20">
-        <f>$B$13*B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="20">
-        <f>$B$13*C31</f>
-        <v/>
-      </c>
-      <c r="D32" s="20">
-        <f>$B$13*D31</f>
-        <v/>
-      </c>
-      <c r="E32" s="20">
-        <f>$B$13*E31</f>
-        <v/>
-      </c>
-      <c r="F32" s="20">
-        <f>$B$13*F31</f>
-        <v/>
-      </c>
-      <c r="G32" s="20">
-        <f>$B$13*G31</f>
+          <t>Transportation (note 5)</t>
+        </is>
+      </c>
+      <c r="B32" s="23">
+        <f>Assumptions!$B$97</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Export share of volume</t>
+          <t>Overheads (note 5) plus cash administration (note 6)</t>
         </is>
       </c>
       <c r="B33" s="26">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="C33" s="26">
-        <f>Assumptions!$C$24</f>
-        <v/>
-      </c>
-      <c r="D33" s="26">
-        <f>Assumptions!$D$24</f>
-        <v/>
-      </c>
-      <c r="E33" s="26">
-        <f>Assumptions!$E$24</f>
-        <v/>
-      </c>
-      <c r="F33" s="26">
-        <f>Assumptions!$F$24</f>
-        <v/>
-      </c>
-      <c r="G33" s="26">
-        <f>Assumptions!$G$24</f>
+        <f>Assumptions!$B$98+Assumptions!$B$60-Assumptions!$B$99</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Export volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B34" s="20">
-        <f>B32*B33</f>
-        <v/>
-      </c>
-      <c r="C34" s="20">
-        <f>C32*C33</f>
-        <v/>
-      </c>
-      <c r="D34" s="20">
-        <f>D32*D33</f>
-        <v/>
-      </c>
-      <c r="E34" s="20">
-        <f>E32*E33</f>
-        <v/>
-      </c>
-      <c r="F34" s="20">
-        <f>F32*F33</f>
-        <v/>
-      </c>
-      <c r="G34" s="20">
-        <f>G32*G33</f>
+          <t>Total cash cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B34" s="26">
+        <f>SUM(B31:B33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Local volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B35" s="20">
-        <f>B32-B34</f>
-        <v/>
-      </c>
-      <c r="C35" s="20">
-        <f>C32-C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="20">
-        <f>D32-D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="20">
-        <f>E32-E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="20">
-        <f>F32-F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="20">
-        <f>G32-G34</f>
+          <t>Materials and fuel per tonne of CLINKER — the kiln burns it</t>
+        </is>
+      </c>
+      <c r="B35" s="26">
+        <f>B31/B7</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Local price (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B36" s="24">
-        <f>$B$10*Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="C36" s="24">
-        <f>$B$10*Assumptions!$C$25</f>
-        <v/>
-      </c>
-      <c r="D36" s="24">
-        <f>$B$10*Assumptions!$D$25</f>
-        <v/>
-      </c>
-      <c r="E36" s="24">
-        <f>$B$10*Assumptions!$E$25</f>
-        <v/>
-      </c>
-      <c r="F36" s="24">
-        <f>$B$10*Assumptions!$F$25</f>
-        <v/>
-      </c>
-      <c r="G36" s="24">
-        <f>$B$10*Assumptions!$G$25</f>
+          <t>Transportation per tonne DESPATCHED</t>
+        </is>
+      </c>
+      <c r="B36" s="26">
+        <f>B32/B18</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Export price (USD/t)</t>
-        </is>
-      </c>
-      <c r="B37" s="27">
-        <f>$B$6*Assumptions!$B$26</f>
-        <v/>
-      </c>
-      <c r="C37" s="27">
-        <f>$B$6*Assumptions!$C$26</f>
-        <v/>
-      </c>
-      <c r="D37" s="27">
-        <f>$B$6*Assumptions!$D$26</f>
-        <v/>
-      </c>
-      <c r="E37" s="27">
-        <f>$B$6*Assumptions!$E$26</f>
-        <v/>
-      </c>
-      <c r="F37" s="27">
-        <f>$B$6*Assumptions!$F$26</f>
-        <v/>
-      </c>
-      <c r="G37" s="27">
-        <f>$B$6*Assumptions!$G$26</f>
+          <t>Overheads and administration per tonne DESPATCHED</t>
+        </is>
+      </c>
+      <c r="B37" s="26">
+        <f>B33/B18</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>USD/EGP</t>
-        </is>
-      </c>
-      <c r="B38" s="18">
-        <f>Assumptions!$B$27</f>
-        <v/>
-      </c>
-      <c r="C38" s="18">
-        <f>Assumptions!$C$27</f>
-        <v/>
-      </c>
-      <c r="D38" s="18">
-        <f>Assumptions!$D$27</f>
-        <v/>
-      </c>
-      <c r="E38" s="18">
-        <f>Assumptions!$E$27</f>
-        <v/>
-      </c>
-      <c r="F38" s="18">
-        <f>Assumptions!$F$27</f>
-        <v/>
-      </c>
-      <c r="G38" s="18">
-        <f>Assumptions!$G$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Local revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B39" s="24">
-        <f>B35*B36</f>
-        <v/>
-      </c>
-      <c r="C39" s="24">
-        <f>C35*C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="24">
-        <f>D35*D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="24">
-        <f>E35*E36</f>
-        <v/>
-      </c>
-      <c r="F39" s="24">
-        <f>F35*F36</f>
-        <v/>
-      </c>
-      <c r="G39" s="24">
-        <f>G35*G36</f>
+          <t>TOTAL CASH COST PER TONNE SOLD</t>
+        </is>
+      </c>
+      <c r="B38" s="24">
+        <f>B34/B18</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Export revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B40" s="24">
-        <f>B34*B37*B38</f>
-        <v/>
-      </c>
-      <c r="C40" s="24">
-        <f>C34*C37*C38</f>
-        <v/>
-      </c>
-      <c r="D40" s="24">
-        <f>D34*D37*D38</f>
-        <v/>
-      </c>
-      <c r="E40" s="24">
-        <f>E34*E37*E38</f>
-        <v/>
-      </c>
-      <c r="F40" s="24">
-        <f>F34*F37*F38</f>
-        <v/>
-      </c>
-      <c r="G40" s="24">
-        <f>G34*G37*G38</f>
-        <v/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Provisions and expected credit losses are NOT in this stack. They are operating charges that</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Goods revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B41" s="24">
-        <f>B39+B40</f>
-        <v/>
-      </c>
-      <c r="C41" s="24">
-        <f>C39+C40</f>
-        <v/>
-      </c>
-      <c r="D41" s="24">
-        <f>D39+D40</f>
-        <v/>
-      </c>
-      <c r="E41" s="24">
-        <f>E39+E40</f>
-        <v/>
-      </c>
-      <c r="F41" s="24">
-        <f>F39+F40</f>
-        <v/>
-      </c>
-      <c r="G41" s="24">
-        <f>G39+G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REVENUE (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B42" s="25">
-        <f>B41*(1+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="C42" s="25">
-        <f>C41*(1+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="D42" s="25">
-        <f>D41*(1+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="E42" s="25">
-        <f>E41*(1+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="F42" s="25">
-        <f>F41*(1+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="G42" s="25">
-        <f>G41*(1+Assumptions!$B$20)</f>
-        <v/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>belong in the EBITDA bridge, but they are not cash cost per tonne. Revision 3 carried them here.</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Blended realised price (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B43" s="24">
-        <f>B42/B32</f>
-        <v/>
-      </c>
-      <c r="C43" s="24">
-        <f>C42/C32</f>
-        <v/>
-      </c>
-      <c r="D43" s="24">
-        <f>D42/D32</f>
-        <v/>
-      </c>
-      <c r="E43" s="24">
-        <f>E42/E32</f>
-        <v/>
-      </c>
-      <c r="F43" s="24">
-        <f>F42/F32</f>
-        <v/>
-      </c>
-      <c r="G43" s="24">
-        <f>G42/G32</f>
-        <v/>
-      </c>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>THE BUILD — FY2025A THEN FY2026E TO FY2030E</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Materials and fuel (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B44" s="24">
-        <f>$B$24*Assumptions!$B$28*(1-Assumptions!$B$29)</f>
-        <v/>
-      </c>
-      <c r="C44" s="24">
-        <f>$B$24*Assumptions!$C$28*(1-Assumptions!$C$29)</f>
-        <v/>
-      </c>
-      <c r="D44" s="24">
-        <f>$B$24*Assumptions!$D$28*(1-Assumptions!$D$29)</f>
-        <v/>
-      </c>
-      <c r="E44" s="24">
-        <f>$B$24*Assumptions!$E$28*(1-Assumptions!$E$29)</f>
-        <v/>
-      </c>
-      <c r="F44" s="24">
-        <f>$B$24*Assumptions!$F$28*(1-Assumptions!$F$29)</f>
-        <v/>
-      </c>
-      <c r="G44" s="24">
-        <f>$B$24*Assumptions!$G$28*(1-Assumptions!$G$29)</f>
-        <v/>
+      <c r="A44" s="14" t="inlineStr"/>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Transportation (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B45" s="24">
-        <f>$B$25*Assumptions!$B$28</f>
-        <v/>
-      </c>
-      <c r="C45" s="24">
-        <f>$B$25*Assumptions!$C$28</f>
-        <v/>
-      </c>
-      <c r="D45" s="24">
-        <f>$B$25*Assumptions!$D$28</f>
-        <v/>
-      </c>
-      <c r="E45" s="24">
-        <f>$B$25*Assumptions!$E$28</f>
-        <v/>
-      </c>
-      <c r="F45" s="24">
-        <f>$B$25*Assumptions!$F$28</f>
-        <v/>
-      </c>
-      <c r="G45" s="24">
-        <f>$B$25*Assumptions!$G$28</f>
+          <t>Kiln utilisation  (DRIVER)</t>
+        </is>
+      </c>
+      <c r="B45" s="18">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f>Assumptions!$C$22</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>Assumptions!$D$22</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>Assumptions!$E$22</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>Assumptions!$F$22</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>Assumptions!$G$22</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Overheads and administration (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B46" s="24">
-        <f>$B$26*Assumptions!$B$28</f>
-        <v/>
-      </c>
-      <c r="C46" s="24">
-        <f>$B$26*Assumptions!$C$28</f>
-        <v/>
-      </c>
-      <c r="D46" s="24">
-        <f>$B$26*Assumptions!$D$28</f>
-        <v/>
-      </c>
-      <c r="E46" s="24">
-        <f>$B$26*Assumptions!$E$28</f>
-        <v/>
-      </c>
-      <c r="F46" s="24">
-        <f>$B$26*Assumptions!$F$28</f>
-        <v/>
-      </c>
-      <c r="G46" s="24">
-        <f>$B$26*Assumptions!$G$28</f>
+          <t>Clinker produced (Mt)</t>
+        </is>
+      </c>
+      <c r="B46" s="19">
+        <f>$B$5*B45</f>
+        <v/>
+      </c>
+      <c r="C46" s="19">
+        <f>$B$5*C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="19">
+        <f>$B$5*D45</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f>$B$5*E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="19">
+        <f>$B$5*F45</f>
+        <v/>
+      </c>
+      <c r="G46" s="19">
+        <f>$B$5*G45</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cash cost (EGP/t)</t>
-        </is>
-      </c>
-      <c r="B47" s="24">
-        <f>SUM(B44:B46)</f>
-        <v/>
-      </c>
-      <c r="C47" s="24">
-        <f>SUM(C44:C46)</f>
-        <v/>
-      </c>
-      <c r="D47" s="24">
-        <f>SUM(D44:D46)</f>
-        <v/>
-      </c>
-      <c r="E47" s="24">
-        <f>SUM(E44:E46)</f>
-        <v/>
-      </c>
-      <c r="F47" s="24">
-        <f>SUM(F44:F46)</f>
-        <v/>
-      </c>
-      <c r="G47" s="24">
-        <f>SUM(G44:G46)</f>
+          <t>Clinker sold as clinker, share  (DRIVER)</t>
+        </is>
+      </c>
+      <c r="B47" s="18">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="C47" s="18">
+        <f>Assumptions!$C$23</f>
+        <v/>
+      </c>
+      <c r="D47" s="18">
+        <f>Assumptions!$D$23</f>
+        <v/>
+      </c>
+      <c r="E47" s="18">
+        <f>Assumptions!$E$23</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>Assumptions!$F$23</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>Assumptions!$G$23</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cash cost (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B48" s="24">
-        <f>B47*B32</f>
-        <v/>
-      </c>
-      <c r="C48" s="24">
-        <f>C47*C32</f>
-        <v/>
-      </c>
-      <c r="D48" s="24">
-        <f>D47*D32</f>
-        <v/>
-      </c>
-      <c r="E48" s="24">
-        <f>E47*E32</f>
-        <v/>
-      </c>
-      <c r="F48" s="24">
-        <f>F47*F32</f>
-        <v/>
-      </c>
-      <c r="G48" s="24">
-        <f>G47*G32</f>
+          <t>Clinker exported (Mt)</t>
+        </is>
+      </c>
+      <c r="B48" s="19">
+        <f>B46*B47</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>C46*C47</f>
+        <v/>
+      </c>
+      <c r="D48" s="19">
+        <f>D46*D47</f>
+        <v/>
+      </c>
+      <c r="E48" s="19">
+        <f>E46*E47</f>
+        <v/>
+      </c>
+      <c r="F48" s="19">
+        <f>F46*F47</f>
+        <v/>
+      </c>
+      <c r="G48" s="19">
+        <f>G46*G47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EBITDA  (AN OUTPUT)</t>
-        </is>
-      </c>
-      <c r="B49" s="25">
-        <f>B42-B48</f>
-        <v/>
-      </c>
-      <c r="C49" s="25">
-        <f>C42-C48</f>
-        <v/>
-      </c>
-      <c r="D49" s="25">
-        <f>D42-D48</f>
-        <v/>
-      </c>
-      <c r="E49" s="25">
-        <f>E42-E48</f>
-        <v/>
-      </c>
-      <c r="F49" s="25">
-        <f>F42-F48</f>
-        <v/>
-      </c>
-      <c r="G49" s="25">
-        <f>G42-G48</f>
+          <t>Clinker ground (Mt)</t>
+        </is>
+      </c>
+      <c r="B49" s="19">
+        <f>B46-B48</f>
+        <v/>
+      </c>
+      <c r="C49" s="19">
+        <f>C46-C48</f>
+        <v/>
+      </c>
+      <c r="D49" s="19">
+        <f>D46-D48</f>
+        <v/>
+      </c>
+      <c r="E49" s="19">
+        <f>E46-E48</f>
+        <v/>
+      </c>
+      <c r="F49" s="19">
+        <f>F46-F48</f>
+        <v/>
+      </c>
+      <c r="G49" s="19">
+        <f>G46-G48</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B50" s="23">
-        <f>B49/B42</f>
-        <v/>
-      </c>
-      <c r="C50" s="23">
-        <f>C49/C42</f>
-        <v/>
-      </c>
-      <c r="D50" s="23">
-        <f>D49/D42</f>
-        <v/>
-      </c>
-      <c r="E50" s="23">
-        <f>E49/E42</f>
-        <v/>
-      </c>
-      <c r="F50" s="23">
-        <f>F49/F42</f>
-        <v/>
-      </c>
-      <c r="G50" s="23">
-        <f>G49/G42</f>
+          <t>Cement produced (Mt)</t>
+        </is>
+      </c>
+      <c r="B50" s="19">
+        <f>B49/$B$11</f>
+        <v/>
+      </c>
+      <c r="C50" s="19">
+        <f>C49/$B$11</f>
+        <v/>
+      </c>
+      <c r="D50" s="19">
+        <f>D49/$B$11</f>
+        <v/>
+      </c>
+      <c r="E50" s="19">
+        <f>E49/$B$11</f>
+        <v/>
+      </c>
+      <c r="F50" s="19">
+        <f>F49/$B$11</f>
+        <v/>
+      </c>
+      <c r="G50" s="19">
+        <f>G49/$B$11</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EBITDA per tonne (EGP)</t>
-        </is>
-      </c>
-      <c r="B51" s="24">
-        <f>B49/B32</f>
-        <v/>
-      </c>
-      <c r="C51" s="24">
-        <f>C49/C32</f>
-        <v/>
-      </c>
-      <c r="D51" s="24">
-        <f>D49/D32</f>
-        <v/>
-      </c>
-      <c r="E51" s="24">
-        <f>E49/E32</f>
-        <v/>
-      </c>
-      <c r="F51" s="24">
-        <f>F49/F32</f>
-        <v/>
-      </c>
-      <c r="G51" s="24">
-        <f>G49/G32</f>
+          <t>Mill utilisation</t>
+        </is>
+      </c>
+      <c r="B51" s="22">
+        <f>B50/$B$13</f>
+        <v/>
+      </c>
+      <c r="C51" s="22">
+        <f>C50/$B$13</f>
+        <v/>
+      </c>
+      <c r="D51" s="22">
+        <f>D50/$B$13</f>
+        <v/>
+      </c>
+      <c r="E51" s="22">
+        <f>E50/$B$13</f>
+        <v/>
+      </c>
+      <c r="F51" s="22">
+        <f>F50/$B$13</f>
+        <v/>
+      </c>
+      <c r="G51" s="22">
+        <f>G50/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Cement exported, share  (DRIVER)</t>
+        </is>
+      </c>
+      <c r="B52" s="18">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="C52" s="18">
+        <f>Assumptions!$C$24</f>
+        <v/>
+      </c>
+      <c r="D52" s="18">
+        <f>Assumptions!$D$24</f>
+        <v/>
+      </c>
+      <c r="E52" s="18">
+        <f>Assumptions!$E$24</f>
+        <v/>
+      </c>
+      <c r="F52" s="18">
+        <f>Assumptions!$F$24</f>
+        <v/>
+      </c>
+      <c r="G52" s="18">
+        <f>Assumptions!$G$24</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>VALIDATION — A TEST THAT CAN FAIL</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cement exported (Mt)</t>
+        </is>
+      </c>
+      <c r="B53" s="19">
+        <f>B50*B52</f>
+        <v/>
+      </c>
+      <c r="C53" s="19">
+        <f>C50*C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="19">
+        <f>D50*D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="19">
+        <f>E50*E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="19">
+        <f>F50*F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="19">
+        <f>G50*G52</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Reconstructed FY2025 revenue</t>
-        </is>
-      </c>
-      <c r="B54" s="24">
-        <f>B42</f>
+          <t>Cement local (Mt)</t>
+        </is>
+      </c>
+      <c r="B54" s="19">
+        <f>B50-B53</f>
+        <v/>
+      </c>
+      <c r="C54" s="19">
+        <f>C50-C53</f>
+        <v/>
+      </c>
+      <c r="D54" s="19">
+        <f>D50-D53</f>
+        <v/>
+      </c>
+      <c r="E54" s="19">
+        <f>E50-E53</f>
+        <v/>
+      </c>
+      <c r="F54" s="19">
+        <f>F50-F53</f>
+        <v/>
+      </c>
+      <c r="G54" s="19">
+        <f>G50-G53</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AUDITED FY2025 revenue</t>
-        </is>
-      </c>
-      <c r="B55" s="17">
-        <f>Assumptions!$B$54</f>
+          <t>TOTAL DESPATCHES (Mt)</t>
+        </is>
+      </c>
+      <c r="B55" s="21">
+        <f>B50+B48</f>
+        <v/>
+      </c>
+      <c r="C55" s="21">
+        <f>C50+C48</f>
+        <v/>
+      </c>
+      <c r="D55" s="21">
+        <f>D50+D48</f>
+        <v/>
+      </c>
+      <c r="E55" s="21">
+        <f>E50+E48</f>
+        <v/>
+      </c>
+      <c r="F55" s="21">
+        <f>F50+F48</f>
+        <v/>
+      </c>
+      <c r="G55" s="21">
+        <f>G50+G48</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="B56" s="23">
-        <f>B54/B55-1</f>
+          <t>Local cement price (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B56" s="26">
+        <f>$B$22*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C56" s="26">
+        <f>$B$22*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D56" s="26">
+        <f>$B$22*Assumptions!$D$25</f>
+        <v/>
+      </c>
+      <c r="E56" s="26">
+        <f>$B$22*Assumptions!$E$25</f>
+        <v/>
+      </c>
+      <c r="F56" s="26">
+        <f>$B$22*Assumptions!$F$25</f>
+        <v/>
+      </c>
+      <c r="G56" s="26">
+        <f>$B$22*Assumptions!$G$25</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Reconstructed FY2025 EBITDA</t>
-        </is>
-      </c>
-      <c r="B57" s="24">
-        <f>B49</f>
+          <t>Export cement price (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B57" s="26">
+        <f>$B$26*Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="C57" s="26">
+        <f>$B$26*Assumptions!$C$26*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="D57" s="26">
+        <f>$B$26*Assumptions!$D$26*Assumptions!$D$27</f>
+        <v/>
+      </c>
+      <c r="E57" s="26">
+        <f>$B$26*Assumptions!$E$26*Assumptions!$E$27</f>
+        <v/>
+      </c>
+      <c r="F57" s="26">
+        <f>$B$26*Assumptions!$F$26*Assumptions!$F$27</f>
+        <v/>
+      </c>
+      <c r="G57" s="26">
+        <f>$B$26*Assumptions!$G$26*Assumptions!$G$27</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AUDITED FY2025 EBITDA (operating profit plus D&amp;A)</t>
-        </is>
-      </c>
-      <c r="B58" s="17">
-        <f>'Income Statement'!D14</f>
+          <t>Export clinker price (EGP/t)</t>
+        </is>
+      </c>
+      <c r="B58" s="26">
+        <f>B57*$B$24</f>
+        <v/>
+      </c>
+      <c r="C58" s="26">
+        <f>C57*$B$24</f>
+        <v/>
+      </c>
+      <c r="D58" s="26">
+        <f>D57*$B$24</f>
+        <v/>
+      </c>
+      <c r="E58" s="26">
+        <f>E57*$B$24</f>
+        <v/>
+      </c>
+      <c r="F58" s="26">
+        <f>F57*$B$24</f>
+        <v/>
+      </c>
+      <c r="G58" s="26">
+        <f>G57*$B$24</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="B59" s="23">
-        <f>B57/B58-1</f>
+          <t>Local revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B59" s="26">
+        <f>B54*B56</f>
+        <v/>
+      </c>
+      <c r="C59" s="26">
+        <f>C54*C56</f>
+        <v/>
+      </c>
+      <c r="D59" s="26">
+        <f>D54*D56</f>
+        <v/>
+      </c>
+      <c r="E59" s="26">
+        <f>E54*E56</f>
+        <v/>
+      </c>
+      <c r="F59" s="26">
+        <f>F54*F56</f>
+        <v/>
+      </c>
+      <c r="G59" s="26">
+        <f>G54*G56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Export cement revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B60" s="26">
+        <f>B53*B57</f>
+        <v/>
+      </c>
+      <c r="C60" s="26">
+        <f>C53*C57</f>
+        <v/>
+      </c>
+      <c r="D60" s="26">
+        <f>D53*D57</f>
+        <v/>
+      </c>
+      <c r="E60" s="26">
+        <f>E53*E57</f>
+        <v/>
+      </c>
+      <c r="F60" s="26">
+        <f>F53*F57</f>
+        <v/>
+      </c>
+      <c r="G60" s="26">
+        <f>G53*G57</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Volume is DERIVED from the audited revenue split divided by the two price inputs, so the</t>
-        </is>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Export clinker revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B61" s="26">
+        <f>B48*B58</f>
+        <v/>
+      </c>
+      <c r="C61" s="26">
+        <f>C48*C58</f>
+        <v/>
+      </c>
+      <c r="D61" s="26">
+        <f>D48*D58</f>
+        <v/>
+      </c>
+      <c r="E61" s="26">
+        <f>E48*E58</f>
+        <v/>
+      </c>
+      <c r="F61" s="26">
+        <f>F48*F58</f>
+        <v/>
+      </c>
+      <c r="G61" s="26">
+        <f>G48*G58</f>
+        <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>utilisation on row 14 is an OUTPUT that can disagree with the sector. It does not: 69.7%</t>
-        </is>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Goods revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B62" s="26">
+        <f>SUM(B59:B61)</f>
+        <v/>
+      </c>
+      <c r="C62" s="26">
+        <f>SUM(C59:C61)</f>
+        <v/>
+      </c>
+      <c r="D62" s="26">
+        <f>SUM(D59:D61)</f>
+        <v/>
+      </c>
+      <c r="E62" s="26">
+        <f>SUM(E59:E61)</f>
+        <v/>
+      </c>
+      <c r="F62" s="26">
+        <f>SUM(F59:F61)</f>
+        <v/>
+      </c>
+      <c r="G62" s="26">
+        <f>SUM(G59:G61)</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>against a national 85.5% of nameplate production, on a plant running below the country average.</t>
-        </is>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>REVENUE (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B63" s="24">
+        <f>B62*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="C63" s="24">
+        <f>C62*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="D63" s="24">
+        <f>D62*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="E63" s="24">
+        <f>E62*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="F63" s="24">
+        <f>F62*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="G63" s="24">
+        <f>G62*(1+Assumptions!$B$19)</f>
+        <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>The cost stack is the DISCLOSED one from notes 5 and 6, not an invented physical build.</t>
-        </is>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Revenue per tonne despatched (EGP)</t>
+        </is>
+      </c>
+      <c r="B64" s="26">
+        <f>B63/B55</f>
+        <v/>
+      </c>
+      <c r="C64" s="26">
+        <f>C63/C55</f>
+        <v/>
+      </c>
+      <c r="D64" s="26">
+        <f>D63/D55</f>
+        <v/>
+      </c>
+      <c r="E64" s="26">
+        <f>E63/E55</f>
+        <v/>
+      </c>
+      <c r="F64" s="26">
+        <f>F63/F55</f>
+        <v/>
+      </c>
+      <c r="G64" s="26">
+        <f>G63/G55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Materials and fuel (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B65" s="26">
+        <f>$B$35*Assumptions!$B$28*(1-Assumptions!$B$29)*B46</f>
+        <v/>
+      </c>
+      <c r="C65" s="26">
+        <f>$B$35*Assumptions!$C$28*(1-Assumptions!$C$29)*C46</f>
+        <v/>
+      </c>
+      <c r="D65" s="26">
+        <f>$B$35*Assumptions!$D$28*(1-Assumptions!$D$29)*D46</f>
+        <v/>
+      </c>
+      <c r="E65" s="26">
+        <f>$B$35*Assumptions!$E$28*(1-Assumptions!$E$29)*E46</f>
+        <v/>
+      </c>
+      <c r="F65" s="26">
+        <f>$B$35*Assumptions!$F$28*(1-Assumptions!$F$29)*F46</f>
+        <v/>
+      </c>
+      <c r="G65" s="26">
+        <f>$B$35*Assumptions!$G$28*(1-Assumptions!$G$29)*G46</f>
+        <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>DOES THE VOLUME FIT THE KILN? — THE PHYSICAL CONSTRAINT</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Transportation (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B66" s="26">
+        <f>$B$36*Assumptions!$B$28*B55</f>
+        <v/>
+      </c>
+      <c r="C66" s="26">
+        <f>$B$36*Assumptions!$C$28*C55</f>
+        <v/>
+      </c>
+      <c r="D66" s="26">
+        <f>$B$36*Assumptions!$D$28*D55</f>
+        <v/>
+      </c>
+      <c r="E66" s="26">
+        <f>$B$36*Assumptions!$E$28*E55</f>
+        <v/>
+      </c>
+      <c r="F66" s="26">
+        <f>$B$36*Assumptions!$F$28*F55</f>
+        <v/>
+      </c>
+      <c r="G66" s="26">
+        <f>$B$36*Assumptions!$G$28*G55</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Clinker factor (t clinker / t cement)</t>
-        </is>
-      </c>
-      <c r="B67" s="28">
-        <f>Assumptions!$B$15</f>
+          <t>Overheads and administration (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B67" s="26">
+        <f>$B$37*Assumptions!$B$28*B55</f>
+        <v/>
+      </c>
+      <c r="C67" s="26">
+        <f>$B$37*Assumptions!$C$28*C55</f>
+        <v/>
+      </c>
+      <c r="D67" s="26">
+        <f>$B$37*Assumptions!$D$28*D55</f>
+        <v/>
+      </c>
+      <c r="E67" s="26">
+        <f>$B$37*Assumptions!$E$28*E55</f>
+        <v/>
+      </c>
+      <c r="F67" s="26">
+        <f>$B$37*Assumptions!$F$28*F55</f>
+        <v/>
+      </c>
+      <c r="G67" s="26">
+        <f>$B$37*Assumptions!$G$28*G55</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kiln clinker capacity (Mt, audited note 1)</t>
-        </is>
-      </c>
-      <c r="B68" s="19">
-        <f>Assumptions!$B$14</f>
+          <t>Cash cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B68" s="26">
+        <f>SUM(B65:B67)</f>
+        <v/>
+      </c>
+      <c r="C68" s="26">
+        <f>SUM(C65:C67)</f>
+        <v/>
+      </c>
+      <c r="D68" s="26">
+        <f>SUM(D65:D67)</f>
+        <v/>
+      </c>
+      <c r="E68" s="26">
+        <f>SUM(E65:E67)</f>
+        <v/>
+      </c>
+      <c r="F68" s="26">
+        <f>SUM(F65:F67)</f>
+        <v/>
+      </c>
+      <c r="G68" s="26">
+        <f>SUM(G65:G67)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Clinker required for FY2025 volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B69" s="20">
-        <f>B12*B67</f>
+          <t>Cash cost per tonne sold (EGP)</t>
+        </is>
+      </c>
+      <c r="B69" s="26">
+        <f>B68/B55</f>
+        <v/>
+      </c>
+      <c r="C69" s="26">
+        <f>C68/C55</f>
+        <v/>
+      </c>
+      <c r="D69" s="26">
+        <f>D68/D55</f>
+        <v/>
+      </c>
+      <c r="E69" s="26">
+        <f>E68/E55</f>
+        <v/>
+      </c>
+      <c r="F69" s="26">
+        <f>F68/F55</f>
+        <v/>
+      </c>
+      <c r="G69" s="26">
+        <f>G68/G55</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kiln utilisation implied, FY2025</t>
-        </is>
-      </c>
-      <c r="B70" s="23">
-        <f>B69/B68</f>
+          <t>Provisions and credit losses (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*B63</f>
+        <v/>
+      </c>
+      <c r="C70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*C63</f>
+        <v/>
+      </c>
+      <c r="D70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*D63</f>
+        <v/>
+      </c>
+      <c r="E70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*E63</f>
+        <v/>
+      </c>
+      <c r="F70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*F63</f>
+        <v/>
+      </c>
+      <c r="G70" s="26">
+        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*G63</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Clinker required for FY2030 volume (Mt)</t>
-        </is>
-      </c>
-      <c r="B71" s="20">
-        <f>G32*B67</f>
+          <t>EBITDA  (AN OUTPUT)</t>
+        </is>
+      </c>
+      <c r="B71" s="24">
+        <f>B63-B68-B70</f>
+        <v/>
+      </c>
+      <c r="C71" s="24">
+        <f>C63-C68-C70</f>
+        <v/>
+      </c>
+      <c r="D71" s="24">
+        <f>D63-D68-D70</f>
+        <v/>
+      </c>
+      <c r="E71" s="24">
+        <f>E63-E68-E70</f>
+        <v/>
+      </c>
+      <c r="F71" s="24">
+        <f>F63-F68-F70</f>
+        <v/>
+      </c>
+      <c r="G71" s="24">
+        <f>G63-G68-G70</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kiln utilisation implied, FY2030 — must stay below 100%</t>
+          <t>EBITDA margin</t>
         </is>
       </c>
       <c r="B72" s="22">
-        <f>B71/B68</f>
+        <f>B71/B63</f>
+        <v/>
+      </c>
+      <c r="C72" s="22">
+        <f>C71/C63</f>
+        <v/>
+      </c>
+      <c r="D72" s="22">
+        <f>D71/D63</f>
+        <v/>
+      </c>
+      <c r="E72" s="22">
+        <f>E71/E63</f>
+        <v/>
+      </c>
+      <c r="F72" s="22">
+        <f>F71/F63</f>
+        <v/>
+      </c>
+      <c r="G72" s="22">
+        <f>G71/G63</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Headroom at the kiln in FY2030 (Mt of clinker)</t>
-        </is>
-      </c>
-      <c r="B73" s="21">
-        <f>B68-B71</f>
+          <t>EBITDA per tonne (EGP)</t>
+        </is>
+      </c>
+      <c r="B73" s="26">
+        <f>B71/B55</f>
+        <v/>
+      </c>
+      <c r="C73" s="26">
+        <f>C71/C55</f>
+        <v/>
+      </c>
+      <c r="D73" s="26">
+        <f>D71/D55</f>
+        <v/>
+      </c>
+      <c r="E73" s="26">
+        <f>E71/E55</f>
+        <v/>
+      </c>
+      <c r="F73" s="26">
+        <f>F71/F55</f>
+        <v/>
+      </c>
+      <c r="G73" s="26">
+        <f>G71/G55</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>The volume forecast is built from cement capacity, so the KILN is the constraint that could</t>
-        </is>
-      </c>
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>VALIDATION — AND A PRICE TEST THAT CAN ACTUALLY FAIL</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="n"/>
+      <c r="J75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>bind first. Row 72 shows it does not: the FY2030 volume needs less clinker than the audited 4.2Mt</t>
-        </is>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Reconstructed FY2025 revenue</t>
+        </is>
+      </c>
+      <c r="B76" s="26">
+        <f>B63</f>
+        <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>kiln capacity, and row 73 states the headroom. A lower clinker factor — more blending, which is</t>
-        </is>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AUDITED FY2025 revenue</t>
+        </is>
+      </c>
+      <c r="B77" s="23">
+        <f>Assumptions!$B$54</f>
+        <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>what the alternative-fuel and supplementary-materials programmes are for — widens it further.</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B78" s="22">
+        <f>B76/B77-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Reconstructed FY2025 EBITDA</t>
+        </is>
+      </c>
+      <c r="B79" s="26">
+        <f>B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AUDITED FY2025 EBITDA (operating profit plus D&amp;A)</t>
+        </is>
+      </c>
+      <c r="B80" s="23">
+        <f>'Income Statement'!D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B81" s="22">
+        <f>B79/B80-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Rows 76-81 are a TIE, not a test: with prices derived from revenue, revenue reconstructs by</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>construction. Revision 3 presented exactly this identity as "a test that can fail". It cannot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>The real test is rows 22, 26 and 27 — three DERIVED prices, which can be held against the market:</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>local EGP 2,916/t, export cement USD 46.6/t, export clinker USD 30.3/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>The clinker figure sits roughly 30% BELOW the USD 44-48 the trade press quotes for Egyptian FOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>clinker. That gap is a live disagreement between the physical disclosure and the price indices, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>it is published rather than tuned away. It is the reason the volume base carries a sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>THE TWO CAPACITY CONSTRAINTS — BOTH LIVE, BOTH CHECKED EVERY YEAR</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="6" t="n"/>
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="6" t="n"/>
+      <c r="J91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kiln clinker capacity (Mt, audited note 1)</t>
+        </is>
+      </c>
+      <c r="B92" s="17">
+        <f>Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Peak clinker required across the forecast (Mt)</t>
+        </is>
+      </c>
+      <c r="B93" s="19">
+        <f>MAX(C46:G46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Peak kiln utilisation — must stay below 100%</t>
+        </is>
+      </c>
+      <c r="B94" s="27">
+        <f>B93/B92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Headroom at the kiln (Mt of clinker)</t>
+        </is>
+      </c>
+      <c r="B95" s="19">
+        <f>B92-B93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cement mill capacity (Mt, audited note 1)</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>Assumptions!$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Peak cement produced across the forecast (Mt)</t>
+        </is>
+      </c>
+      <c r="B97" s="19">
+        <f>MAX(C50:G50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Peak mill utilisation — must stay below 100%</t>
+        </is>
+      </c>
+      <c r="B98" s="27">
+        <f>B97/B96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Headroom at the mill (Mt of cement)</t>
+        </is>
+      </c>
+      <c r="B99" s="19">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Both constraints are now REAL. Clinker exports and domestic cement compete for the same kiln:</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>every tonne shipped as clinker is a tonne that could have been ground into cement worth several</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>times as much. Revision 3 could not see this at all — it carried one product, ignored clinker</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>exports, and its kiln check therefore ran on a volume base 28% too small. On the physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>disclosure its FY2030 forecast needed 103% of the kiln, not the 78% it published.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A75:J75"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A77:J77"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A63:J63"/>
+  <mergeCells count="14">
+    <mergeCell ref="A85:J85"/>
+    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A89:J89"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A105:J105"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A87:J87"/>
+    <mergeCell ref="A101:J101"/>
+    <mergeCell ref="A86:J86"/>
+    <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A41:J41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7401,28 +7836,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -7434,24 +7869,24 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="17">
-        <f>'Unit Build'!C42</f>
-        <v/>
-      </c>
-      <c r="C5" s="17">
-        <f>'Unit Build'!D42</f>
-        <v/>
-      </c>
-      <c r="D5" s="17">
-        <f>'Unit Build'!E42</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
-        <f>'Unit Build'!F42</f>
-        <v/>
-      </c>
-      <c r="F5" s="17">
-        <f>'Unit Build'!G42</f>
+      <c r="B5" s="23">
+        <f>'Unit Build'!C63</f>
+        <v/>
+      </c>
+      <c r="C5" s="23">
+        <f>'Unit Build'!D63</f>
+        <v/>
+      </c>
+      <c r="D5" s="23">
+        <f>'Unit Build'!E63</f>
+        <v/>
+      </c>
+      <c r="E5" s="23">
+        <f>'Unit Build'!F63</f>
+        <v/>
+      </c>
+      <c r="F5" s="23">
+        <f>'Unit Build'!G63</f>
         <v/>
       </c>
     </row>
@@ -7461,23 +7896,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="22">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="22">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="22">
         <f>F7/F5</f>
         <v/>
       </c>
@@ -7488,24 +7923,24 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="17">
-        <f>'Unit Build'!C49</f>
-        <v/>
-      </c>
-      <c r="C7" s="17">
-        <f>'Unit Build'!D49</f>
-        <v/>
-      </c>
-      <c r="D7" s="17">
-        <f>'Unit Build'!E49</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
-        <f>'Unit Build'!F49</f>
-        <v/>
-      </c>
-      <c r="F7" s="17">
-        <f>'Unit Build'!G49</f>
+      <c r="B7" s="23">
+        <f>'Unit Build'!C71</f>
+        <v/>
+      </c>
+      <c r="C7" s="23">
+        <f>'Unit Build'!D71</f>
+        <v/>
+      </c>
+      <c r="D7" s="23">
+        <f>'Unit Build'!E71</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>'Unit Build'!F71</f>
+        <v/>
+      </c>
+      <c r="F7" s="23">
+        <f>'Unit Build'!G71</f>
         <v/>
       </c>
     </row>
@@ -7515,23 +7950,23 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="26">
         <f>B5*Assumptions!$B$32</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="26">
         <f>C5*Assumptions!$C$32</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="26">
         <f>D5*Assumptions!$D$32</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="26">
         <f>E5*Assumptions!$E$32</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="26">
         <f>F5*Assumptions!$F$32</f>
         <v/>
       </c>
@@ -7542,23 +7977,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <f>B7-B8</f>
         <v/>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="26">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="26">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="26">
         <f>F7-F8</f>
         <v/>
       </c>
@@ -7569,23 +8004,23 @@
           <t>Tax rate (effective)</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="18">
         <f>Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="18">
         <f>Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="18">
         <f>Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="18">
         <f>Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="18">
         <f>Assumptions!$B$9</f>
         <v/>
       </c>
@@ -7596,23 +8031,23 @@
           <t>NOPAT  (EBIT × (1 − t))</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="26">
         <f>B9*(1-B10)</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="26">
         <f>D9*(1-D10)</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="26">
         <f>E9*(1-E10)</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <f>F9*(1-F10)</f>
         <v/>
       </c>
@@ -7623,23 +8058,23 @@
           <t>Plus depreciation</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="26">
         <f>B8</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="26">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="26">
         <f>D8</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="26">
         <f>E8</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="26">
         <f>F8</f>
         <v/>
       </c>
@@ -7650,23 +8085,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="26">
         <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="26">
         <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$D$27</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="26">
         <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="26">
         <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$F$27</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$G$27</f>
         <v/>
       </c>
@@ -7677,23 +8112,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="26">
         <f>-(B5-Assumptions!$B$54)*Assumptions!$B$36</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="26">
         <f>-(C5-B5)*Assumptions!$B$36</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="26">
         <f>-(D5-C5)*Assumptions!$B$36</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="26">
         <f>-(E5-D5)*Assumptions!$B$36</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="26">
         <f>-(F5-E5)*Assumptions!$B$36</f>
         <v/>
       </c>
@@ -7704,23 +8139,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="24">
         <f>(B11+B12+B13+B14)*(1-Assumptions!$B$50)</f>
         <v/>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <f>C11+C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <f>D11+D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <f>E11+E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f>F11+F12+F13+F14</f>
         <v/>
       </c>
@@ -7731,23 +8166,23 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="28">
         <f>(Assumptions!$B$33-Assumptions!$B$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="28">
         <f>(Assumptions!$B$33-Assumptions!$C$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <f>(Assumptions!$B$33-Assumptions!$D$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="28">
         <f>(Assumptions!$B$33-Assumptions!$E$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <f>(Assumptions!$B$33-Assumptions!$F$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
         <v/>
       </c>
@@ -7758,23 +8193,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="29">
         <f>$C$40-($C$40-$C$50)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <f>$C$40-($C$40-$C$50)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <f>$C$40-($C$40-$C$50)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <f>$C$40-($C$40-$C$50)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <f>$C$40-($C$40-$C$50)*F16</f>
         <v/>
       </c>
@@ -7785,24 +8220,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="28">
         <f>1/(1+B17)^((1-Assumptions!$B$50)/2)</f>
         <v/>
       </c>
-      <c r="C18" s="29">
-        <f>1/(1+B17)^(1-Assumptions!$B$50+0.5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="29">
-        <f>1/((1+B17)*(1+C17)^(1-Assumptions!$B$50+0.5))</f>
-        <v/>
-      </c>
-      <c r="E18" s="29">
-        <f>1/((1+B17)*(1+C17)*(1+D17)^(1-Assumptions!$B$50+0.5))</f>
-        <v/>
-      </c>
-      <c r="F18" s="29">
-        <f>1/((1+B17)*(1+C17)*(1+D17)*(1+E17)^(1-Assumptions!$B$50+0.5))</f>
+      <c r="C18" s="28">
+        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="28">
+        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
     </row>
@@ -7812,23 +8247,23 @@
           <t>PRESENT VALUE OF FCFF</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="26">
         <f>B15*B18</f>
         <v/>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="26">
         <f>C15*C18</f>
         <v/>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="26">
         <f>D15*D18</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="26">
         <f>E15*E18</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="26">
         <f>F15*F18</f>
         <v/>
       </c>
@@ -7850,11 +8285,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Replacement-cost invested capital (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B22" s="24">
-        <f>Assumptions!$B$13*Assumptions!$B$141*Assumptions!$B$11</f>
+          <t>Replacement-cost invested capital, in TERMINAL-year pounds (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B22" s="26">
+        <f>Assumptions!$B$13*Assumptions!$B$141*Assumptions!$B$11*Assumptions!$G$28</f>
         <v/>
       </c>
     </row>
@@ -7864,7 +8299,7 @@
           <t>Terminal NOPAT  (year 5 NOPAT grown at g)</t>
         </is>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="26">
         <f>F11*(1+Assumptions!$B$49)</f>
         <v/>
       </c>
@@ -7875,7 +8310,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="22">
         <f>B23/B22</f>
         <v/>
       </c>
@@ -7886,7 +8321,7 @@
           <t>Memo: FY2025 return on BOOK invested capital</t>
         </is>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="22">
         <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$114+$C$44)</f>
         <v/>
       </c>
@@ -7897,7 +8332,7 @@
           <t>Reinvestment rate  (g ÷ return on capital)</t>
         </is>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="22">
         <f>Assumptions!$B$49/B24</f>
         <v/>
       </c>
@@ -7908,7 +8343,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="26">
         <f>B23*(1-B26)/($C$50-Assumptions!$B$49)</f>
         <v/>
       </c>
@@ -7919,8 +8354,19 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="24">
-        <f>B27*F18</f>
+      <c r="B28" s="26">
+        <f>B27*B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>End-of-window discount factor  (t = 4.417y, not the year-5 mid-point)</t>
+        </is>
+      </c>
+      <c r="B29" s="28">
+        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
         <v/>
       </c>
     </row>
@@ -7944,7 +8390,7 @@
           <t>Present value of explicit years (FY2026E-FY2030E)</t>
         </is>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="26">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
@@ -7955,7 +8401,7 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="26">
         <f>B28</f>
         <v/>
       </c>
@@ -7966,7 +8412,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="24">
         <f>B31+B32</f>
         <v/>
       </c>
@@ -7977,7 +8423,7 @@
           <t>TERMINAL VALUE AS % OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="27">
         <f>B32/B33</f>
         <v/>
       </c>
@@ -7988,238 +8434,282 @@
           <t>Audited cash at 31 December 2025</t>
         </is>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="26">
         <f>Assumptions!$B$111</f>
         <v/>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL — BUILT HERE, FACILITY BY FACILITY (labels in column E:</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Plus free cash flow AND treasury income earned to the valuation date</t>
+        </is>
+      </c>
+      <c r="B36" s="26">
+        <f>B15/(1-Assumptions!$B$50)*Assumptions!$B$50+Assumptions!$B$111*Assumptions!$B$34*Assumptions!$B$50*(1-Assumptions!$B$9)</f>
+        <v/>
+      </c>
+      <c r="C36" s="29">
+        <f>Assumptions!$B$39</f>
+        <v/>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Risk-free rate (observed EGP 10-year)</t>
         </is>
-      </c>
-      <c r="B36" s="24">
-        <f>B15/(1-Assumptions!$B$50)*Assumptions!$B$50</f>
-        <v/>
-      </c>
-      <c r="C36" s="30">
-        <f>Assumptions!$B$39</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Less the FY2025 dividend declared and unpaid</t>
+        </is>
+      </c>
+      <c r="B37" s="26">
+        <f>-Assumptions!$B$130</f>
+        <v/>
+      </c>
+      <c r="C37" s="29">
+        <f>-Assumptions!$B$40</f>
+        <v/>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Less sovereign default spread</t>
         </is>
-      </c>
-      <c r="B37" s="24">
-        <f>-Assumptions!$B$130</f>
-        <v/>
-      </c>
-      <c r="C37" s="30">
-        <f>-Assumptions!$B$40</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Cash at the valuation date</t>
+        </is>
+      </c>
+      <c r="B38" s="26">
+        <f>SUM(B35:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="29">
+        <f>C36+C37</f>
+        <v/>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Normalised risk-free rate</t>
         </is>
-      </c>
-      <c r="B38" s="24">
-        <f>SUM(B35:B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="30">
-        <f>C36+C37</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Less interest-bearing debt (reviewed 31 March 2026, the FRESHER disclosure)</t>
+        </is>
+      </c>
+      <c r="B39" s="26">
+        <f>-Assumptions!$B$137</f>
+        <v/>
+      </c>
+      <c r="C39" s="29">
+        <f>C38+Assumptions!$B$10*Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Cost of equity  (rf* + beta × premium)</t>
         </is>
-      </c>
-      <c r="B39" s="24">
-        <f>-$C$44</f>
-        <v/>
-      </c>
-      <c r="C39" s="30">
-        <f>C38+Assumptions!$B$10*Assumptions!$B$41</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Net cash (ADDED — the company is net cash)</t>
+        </is>
+      </c>
+      <c r="B40" s="26">
+        <f>B38+B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="30">
+        <f>(1-C43)*C39+C43*C42</f>
+        <v/>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>WACC — explicit window</t>
         </is>
-      </c>
-      <c r="B40" s="24">
-        <f>B38+B39</f>
-        <v/>
-      </c>
-      <c r="C40" s="31">
-        <f>(1-C43)*C39+C43*C42</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Less non-controlling interests (audited note 24)</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>-Assumptions!$B$117</f>
+        <v/>
+      </c>
+      <c r="C41" s="30">
+        <f>(Assumptions!$B$119*Assumptions!$B$43+Assumptions!$B$120*(Assumptions!$B$42+0.03)+Assumptions!$B$121*(Assumptions!$B$42+0.0435)+Assumptions!$B$122*Assumptions!$B$43)/C44</f>
+        <v/>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Cost of debt, blended by currency</t>
         </is>
-      </c>
-      <c r="B41" s="32">
-        <f>-Assumptions!$B$117</f>
-        <v/>
-      </c>
-      <c r="C41" s="31">
-        <f>(Assumptions!$B$119*Assumptions!$B$43+Assumptions!$B$120*(Assumptions!$B$42+0.03)+Assumptions!$B$121*(Assumptions!$B$42+0.0435)+Assumptions!$B$122*Assumptions!$B$43)/C44</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B42" s="24">
+        <f>B33+B40+B41</f>
+        <v/>
+      </c>
+      <c r="C42" s="29">
+        <f>C41*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Cost of debt after tax</t>
         </is>
-      </c>
-      <c r="B42" s="25">
-        <f>B33+B40+B41</f>
-        <v/>
-      </c>
-      <c r="C42" s="30">
-        <f>C41*(1-Assumptions!$B$8)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="B43" s="31">
+        <f>Assumptions!$B$6-Assumptions!$B$7</f>
+        <v/>
+      </c>
+      <c r="C43" s="29">
+        <f>C44/(C44+C45)</f>
+        <v/>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Debt weight  D/(D+E)</t>
         </is>
-      </c>
-      <c r="B43" s="32">
-        <f>Assumptions!$B$6-Assumptions!$B$7</f>
-        <v/>
-      </c>
-      <c r="C43" s="30">
-        <f>C44/(C44+C45)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>FAIR VALUE PER SHARE (EGP)</t>
+        </is>
+      </c>
+      <c r="B44" s="32">
+        <f>B42/B43</f>
+        <v/>
+      </c>
+      <c r="C44" s="26">
+        <f>Assumptions!$B$119+Assumptions!$B$120+Assumptions!$B$121+Assumptions!$B$122</f>
+        <v/>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Total interest-bearing debt</t>
         </is>
       </c>
-      <c r="B44" s="33">
-        <f>B42/B43</f>
-        <v/>
-      </c>
-      <c r="C44" s="24">
-        <f>Assumptions!$B$119+Assumptions!$B$120+Assumptions!$B$121+Assumptions!$B$122</f>
-        <v/>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="C45" s="26">
+        <f>Assumptions!$B$5*(Assumptions!$B$6-Assumptions!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>Market capitalisation</t>
         </is>
       </c>
-      <c r="C45" s="24">
-        <f>Assumptions!$B$5*(Assumptions!$B$6-Assumptions!$B$7)</f>
-        <v/>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="C46" s="22">
+        <f>(Assumptions!$B$120+Assumptions!$B$121)/C44</f>
+        <v/>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>Euro share of the debt book</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="34">
-        <f>(Assumptions!$B$120+Assumptions!$B$121)/C44</f>
-        <v/>
-      </c>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Terminal beta, RE-LEVERED to the terminal structure</t>
-        </is>
-      </c>
-      <c r="C47" s="20">
-        <f>Assumptions!$B$10*(1+(1-Assumptions!$B$8)*Assumptions!$B$48/(1-Assumptions!$B$48))</f>
-        <v/>
+      <c r="C47" s="19">
+        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$48/(1-Assumptions!$B$48))</f>
+        <v/>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Terminal beta, UNLEVERED at the observed structure then re-levered</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="C48" s="29">
+        <f>Assumptions!$B$46+C47*Assumptions!$B$47</f>
+        <v/>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C48" s="30">
-        <f>Assumptions!$B$46+C47*Assumptions!$B$47</f>
-        <v/>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="C49" s="29">
+        <f>Assumptions!$B$45*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C49" s="30">
-        <f>Assumptions!$B$45*(1-Assumptions!$B$8)</f>
-        <v/>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="C50" s="30">
+        <f>(1-Assumptions!$B$48)*C48+Assumptions!$B$48*C49</f>
+        <v/>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>WACC — terminal</t>
         </is>
       </c>
-      <c r="C50" s="31">
-        <f>(1-Assumptions!$B$48)*C48+Assumptions!$B$48*C49</f>
-        <v/>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="C51" s="29">
+        <f>Assumptions!$B$39+Assumptions!$B$10*Assumptions!$B$41</f>
+        <v/>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>Memo: retired construction, risk-free NOT netted</t>
         </is>
       </c>
-      <c r="C51" s="30">
-        <f>Assumptions!$B$39+Assumptions!$B$10*Assumptions!$B$41</f>
-        <v/>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="C52" s="26">
+        <f>(C51-C39)*10000</f>
+        <v/>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>Memo: sovereign double-count removed (basis points)</t>
         </is>
-      </c>
-      <c r="C52" s="24">
-        <f>(C51-C39)*10000</f>
-        <v/>
       </c>
     </row>
     <row r="54">
@@ -8242,7 +8732,7 @@
           <t>Euro share of the book (audited note 25)</t>
         </is>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="22">
         <f>C46</f>
         <v/>
       </c>
@@ -8253,7 +8743,7 @@
           <t>CIB facility rate — EGP corridor + 0.6%</t>
         </is>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="29">
         <f>Assumptions!$B$43</f>
         <v/>
       </c>
@@ -8264,7 +8754,7 @@
           <t>NBE/KfW facility rate — Euribor + 3.00%</t>
         </is>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="29">
         <f>Assumptions!$B$42+0.03</f>
         <v/>
       </c>
@@ -8275,7 +8765,7 @@
           <t>EBRD facility rate — Euribor + 4.35%</t>
         </is>
       </c>
-      <c r="B58" s="30">
+      <c r="B58" s="29">
         <f>Assumptions!$B$42+0.0435</f>
         <v/>
       </c>
@@ -8286,7 +8776,7 @@
           <t>ADOPTED blended cost of debt</t>
         </is>
       </c>
-      <c r="B59" s="31">
+      <c r="B59" s="30">
         <f>C41</f>
         <v/>
       </c>
@@ -8297,7 +8787,7 @@
           <t>Effective rate computed FY2024 (interest / average debt)</t>
         </is>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="29">
         <f>(Assumptions!$B$127+Assumptions!$B$128)/((Assumptions!$B$124+Assumptions!$B$123)/2)</f>
         <v/>
       </c>
@@ -8308,7 +8798,7 @@
           <t>Effective rate computed FY2025</t>
         </is>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="29">
         <f>(Assumptions!$B$125+Assumptions!$B$126)/((Assumptions!$B$123+C44-Assumptions!$B$122)/2)</f>
         <v/>
       </c>
@@ -8319,7 +8809,7 @@
           <t>Effective rate computed Q1-2026, annualised</t>
         </is>
       </c>
-      <c r="B62" s="30">
+      <c r="B62" s="29">
         <f>Assumptions!$B$139*4/((C44+Assumptions!$B$137)/2)</f>
         <v/>
       </c>
@@ -8330,7 +8820,7 @@
           <t>Pound-EQUIVALENT cost of debt under interest parity</t>
         </is>
       </c>
-      <c r="B63" s="31">
+      <c r="B63" s="30">
         <f>(Assumptions!$B$119*Assumptions!$B$43+Assumptions!$B$120*(Assumptions!$B$42+0.03+Assumptions!$B$44)+Assumptions!$B$121*(Assumptions!$B$42+0.0435+Assumptions!$B$44)+Assumptions!$B$122*Assumptions!$B$43)/C44</f>
         <v/>
       </c>
@@ -8420,13 +8910,13 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>EGP mn</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Per share (EGP)</t>
         </is>
@@ -8438,11 +8928,11 @@
           <t>Present value of explicit free cash flow</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>DCF!B31</f>
         <v/>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>B5/DCF!$B$43</f>
         <v/>
       </c>
@@ -8453,11 +8943,11 @@
           <t>Present value of terminal value</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>DCF!B32</f>
         <v/>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <f>B6/DCF!$B$43</f>
         <v/>
       </c>
@@ -8468,11 +8958,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="34">
         <f>DCF!B33</f>
         <v/>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="32">
         <f>B7/DCF!$B$43</f>
         <v/>
       </c>
@@ -8483,11 +8973,11 @@
           <t>Plus net cash at the valuation date</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="23">
         <f>DCF!B40</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="33">
         <f>B8/DCF!$B$43</f>
         <v/>
       </c>
@@ -8498,11 +8988,11 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="23">
         <f>DCF!B41</f>
         <v/>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <f>B9/DCF!$B$43</f>
         <v/>
       </c>
@@ -8513,11 +9003,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="34">
         <f>DCF!B42</f>
         <v/>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <f>B10/DCF!$B$43</f>
         <v/>
       </c>
@@ -8528,7 +9018,7 @@
           <t>TERMINAL VALUE AS % OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="35">
         <f>DCF!B34</f>
         <v/>
       </c>
@@ -8539,7 +9029,7 @@
           <t>Memo: spot price</t>
         </is>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="36">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -8550,7 +9040,7 @@
           <t>Fair value less spot</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="33">
         <f>C10-C13</f>
         <v/>
       </c>
@@ -8561,7 +9051,7 @@
           <t>Upside / (downside) to the cash-flow lens</t>
         </is>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="22">
         <f>C10/C13-1</f>
         <v/>
       </c>
@@ -8572,7 +9062,7 @@
           <t>Memo: enterprise value per annual tonne of capacity (USD)</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="37">
         <f>B7/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
@@ -8653,43 +9143,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -8701,35 +9191,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>Assumptions!$B$52</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="23">
         <f>Assumptions!$B$53</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>Assumptions!$B$54</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="23">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="23">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="23">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="23">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -8740,23 +9230,23 @@
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>-Assumptions!$B$55</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>-Assumptions!$B$56</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f>-Assumptions!$B$57</f>
         <v/>
       </c>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8764,15 +9254,15 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <f>D5+D6</f>
         <v/>
       </c>
@@ -8783,15 +9273,15 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <f>D7/D5</f>
         <v/>
       </c>
@@ -8802,15 +9292,15 @@
           <t>General and administrative expenses</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="23">
         <f>-Assumptions!$B$58</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>-Assumptions!$B$59</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="23">
         <f>-Assumptions!$B$60</f>
         <v/>
       </c>
@@ -8821,15 +9311,15 @@
           <t>Provisions and credit losses</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="23">
         <f>-Assumptions!$B$61-Assumptions!$B$64</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="23">
         <f>-Assumptions!$B$62-Assumptions!$B$65</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="23">
         <f>-Assumptions!$B$63-Assumptions!$B$66</f>
         <v/>
       </c>
@@ -8840,35 +9330,35 @@
           <t>OPERATING PROFIT</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <f>B7+B9+B10</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <f>C7+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <f>D7+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <f>E14-E13</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <f>F14-F13</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="24">
         <f>G14-G13</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="24">
         <f>H14-H13</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <f>I14-I13</f>
         <v/>
       </c>
@@ -8876,38 +9366,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B12" s="24">
+          <t>Operating profit, opening the EBITDA bridge</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
         <f>B11</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="26">
         <f>C11</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="26">
         <f>D11</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="26">
         <f>E11</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="26">
         <f>F11</f>
         <v/>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="26">
         <f>G11</f>
         <v/>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="26">
         <f>H11</f>
         <v/>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="26">
         <f>I11</f>
         <v/>
       </c>
@@ -8915,38 +9405,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B13" s="17">
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B13" s="23">
         <f>Assumptions!$B$79</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>Assumptions!$B$80</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="23">
         <f>Assumptions!$B$81</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="23">
         <f>DCF!B8</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="23">
         <f>DCF!C8</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="23">
         <f>DCF!D8</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="23">
         <f>DCF!E8</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="23">
         <f>DCF!F8</f>
         <v/>
       </c>
@@ -8954,38 +9444,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B14" s="25">
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
         <f>B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="34">
         <f>DCF!B7</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="34">
         <f>DCF!C7</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="34">
         <f>DCF!D7</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="34">
         <f>DCF!E7</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="34">
         <f>DCF!F7</f>
         <v/>
       </c>
@@ -8993,38 +9483,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Net finance and other income</t>
-        </is>
-      </c>
-      <c r="B15" s="23">
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
         <f>B14/B5</f>
         <v/>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="22">
         <f>C14/C5</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <f>D14/D5</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <f>E14/E5</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="22">
         <f>F14/F5</f>
         <v/>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <f>G14/G5</f>
         <v/>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="22">
         <f>H14/H5</f>
         <v/>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <f>I14/I5</f>
         <v/>
       </c>
@@ -9032,38 +9522,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Profit before tax</t>
-        </is>
-      </c>
-      <c r="B16" s="24">
+          <t>Net finance and other income</t>
+        </is>
+      </c>
+      <c r="B16" s="26">
         <f>Assumptions!$B$67-B11</f>
         <v/>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="26">
         <f>Assumptions!$B$68-C11</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="26">
         <f>Assumptions!$B$85+Assumptions!$B$86-Assumptions!$B$87+Assumptions!$B$88+1.14</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="26">
         <f>('Balance Sheet'!D9-Assumptions!$B$130)*Assumptions!$B$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="26">
         <f>'Balance Sheet'!E9*Assumptions!$C$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <f>'Balance Sheet'!F9*Assumptions!$D$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
         <v/>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="26">
         <f>'Balance Sheet'!G9*Assumptions!$E$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
         <v/>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="26">
         <f>'Balance Sheet'!H9*Assumptions!$F$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
         <v/>
       </c>
@@ -9071,38 +9561,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Income tax</t>
-        </is>
-      </c>
-      <c r="B17" s="17">
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B17" s="23">
         <f>Assumptions!$B$67</f>
         <v/>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="23">
         <f>Assumptions!$B$68</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="23">
         <f>Assumptions!$B$69</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="26">
         <f>E11+E16</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="26">
         <f>F11+F16</f>
         <v/>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <f>G11+G16</f>
         <v/>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="26">
         <f>H11+H16</f>
         <v/>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="26">
         <f>I11+I16</f>
         <v/>
       </c>
@@ -9110,38 +9600,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Effective tax rate</t>
-        </is>
-      </c>
-      <c r="B18" s="17">
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="B18" s="23">
         <f>-Assumptions!$B$70</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="23">
         <f>-Assumptions!$B$71</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="23">
         <f>-Assumptions!$B$72</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="26">
         <f>-E17*Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="26">
         <f>-F17*Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="26">
         <f>-G17*Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="26">
         <f>-H17*Assumptions!$B$9</f>
         <v/>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="26">
         <f>-I17*Assumptions!$B$9</f>
         <v/>
       </c>
@@ -9149,38 +9639,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attributable profit</t>
-        </is>
-      </c>
-      <c r="B19" s="23">
+          <t>Effective tax rate</t>
+        </is>
+      </c>
+      <c r="B19" s="22">
         <f>-B18/B17</f>
         <v/>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="22">
         <f>-C18/C17</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <f>-D18/D17</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="22">
         <f>-E18/E17</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="22">
         <f>-F18/F17</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="22">
         <f>-G18/G17</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <f>-H18/H17</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <f>-I18/I17</f>
         <v/>
       </c>
@@ -9188,38 +9678,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Earnings per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B20" s="36">
+          <t>Attributable profit</t>
+        </is>
+      </c>
+      <c r="B20" s="34">
         <f>Assumptions!$B$73</f>
         <v/>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="34">
         <f>Assumptions!$B$74</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="34">
         <f>Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="24">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <f>G17+G18</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <f>H17+H18</f>
         <v/>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <f>I17+I18</f>
         <v/>
       </c>
@@ -9227,38 +9717,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dividends declared</t>
-        </is>
-      </c>
-      <c r="B21" s="38">
+          <t>Earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
         <f>Assumptions!$B$76</f>
         <v/>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="36">
         <f>Assumptions!$B$77</f>
         <v/>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="36">
         <f>Assumptions!$B$78</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="33">
         <f>E20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="33">
         <f>F20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="33">
         <f>G20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="33">
         <f>H20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="33">
         <f>I20/DCF!$B$43</f>
         <v/>
       </c>
@@ -9269,31 +9759,31 @@
           <t>Dividends declared</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="23">
         <f>Assumptions!$B$131</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="23">
         <f>Assumptions!$B$130</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="26">
         <f>E20*Assumptions!$B$37</f>
         <v/>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="26">
         <f>F20*Assumptions!$B$37</f>
         <v/>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <f>G20*Assumptions!$B$37</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="26">
         <f>H20*Assumptions!$B$37</f>
         <v/>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="26">
         <f>I20*Assumptions!$B$37</f>
         <v/>
       </c>
@@ -9304,31 +9794,31 @@
           <t>Dividend per share (EGP)</t>
         </is>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="33">
         <f>C22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="33">
         <f>D22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="33">
         <f>E22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="33">
         <f>F22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="33">
         <f>G22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="33">
         <f>H22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="33">
         <f>I22/DCF!$B$43</f>
         <v/>
       </c>
@@ -9339,7 +9829,7 @@
           <t>FY2025 check: components of non-operating income against the audited residual</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="31">
         <f>D16-(D17-D11)</f>
         <v/>
       </c>
@@ -9428,43 +9918,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -9476,7 +9966,7 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>Assumptions!$B$105</f>
         <v/>
       </c>
@@ -9487,7 +9977,7 @@
           <t>Assets under construction</t>
         </is>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f>Assumptions!$B$106</f>
         <v/>
       </c>
@@ -9498,7 +9988,7 @@
           <t>Intangible assets</t>
         </is>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="23">
         <f>Assumptions!$B$107</f>
         <v/>
       </c>
@@ -9509,27 +9999,27 @@
           <t>Total non-current assets</t>
         </is>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="26">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="26">
         <f>D8-DCF!B8-DCF!B13</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="26">
         <f>E8-DCF!C8-DCF!C13</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="26">
         <f>F8-DCF!D8-DCF!D13</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="26">
         <f>G8-DCF!E8-DCF!E13</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="26">
         <f>H8-DCF!F8-DCF!F13</f>
         <v/>
       </c>
@@ -9537,38 +10027,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Inventories, receivables and debtors</t>
-        </is>
-      </c>
-      <c r="B9" s="17">
+          <t>Cash and bank balances</t>
+        </is>
+      </c>
+      <c r="B9" s="23">
         <f>Assumptions!$B$113</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>Assumptions!$B$112</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="23">
         <f>Assumptions!$B$111</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="26">
         <f>D9-Assumptions!$B$130+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="26">
         <f>E9+'Income Statement'!F20+DCF!C8+DCF!C13+DCF!C14-'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="26">
         <f>F9+'Income Statement'!G20+DCF!D8+DCF!D13+DCF!D14-'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="26">
         <f>G9+'Income Statement'!H20+DCF!E8+DCF!E13+DCF!E14-'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="26">
         <f>H9+'Income Statement'!I20+DCF!F8+DCF!F13+DCF!F14-'Income Statement'!I22</f>
         <v/>
       </c>
@@ -9576,30 +10066,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cash and bank balances</t>
-        </is>
-      </c>
-      <c r="D10" s="24">
+          <t>Inventories, receivables and debtors</t>
+        </is>
+      </c>
+      <c r="D10" s="26">
         <f>Assumptions!$B$108+Assumptions!$B$109+Assumptions!$B$110</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="26">
         <f>D10-DCF!B14</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="26">
         <f>E10-DCF!C14</f>
         <v/>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="26">
         <f>F10-DCF!D14</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="26">
         <f>G10-DCF!E14</f>
         <v/>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="26">
         <f>H10-DCF!F14</f>
         <v/>
       </c>
@@ -9610,35 +10100,35 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="34">
         <f>Assumptions!$B$103</f>
         <v/>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="34">
         <f>Assumptions!$B$102</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="34">
         <f>Assumptions!$B$101</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="24">
         <f>G8+G9+G10</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="24">
         <f>H8+H9+H10</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <f>I8+I9+I10</f>
         <v/>
       </c>
@@ -9649,35 +10139,35 @@
           <t>Interest-bearing debt</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="23">
         <f>Assumptions!$B$124</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>Assumptions!$B$123</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="23">
         <f>DCF!C44</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="23">
         <f>DCF!$C$44</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="23">
         <f>DCF!$C$44</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="23">
         <f>DCF!$C$44</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="23">
         <f>DCF!$C$44</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="23">
         <f>DCF!$C$44</f>
         <v/>
       </c>
@@ -9688,27 +10178,27 @@
           <t>Other liabilities</t>
         </is>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="26">
         <f>D14-D12</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="26">
         <f>D13</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f>D13</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="26">
         <f>D13</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <f>D13</f>
         <v/>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="26">
         <f>D13</f>
         <v/>
       </c>
@@ -9719,27 +10209,27 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="23">
         <f>Assumptions!$B$104</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="26">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="26">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="26">
         <f>G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="26">
         <f>H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="26">
         <f>I12+I13</f>
         <v/>
       </c>
@@ -9750,35 +10240,35 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="34">
         <f>Assumptions!$B$116</f>
         <v/>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="34">
         <f>Assumptions!$B$115</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="34">
         <f>Assumptions!$B$114</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <f>D15-Assumptions!$B$130+'Income Statement'!E20-'Income Statement'!E22</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f>E15+'Income Statement'!F20-'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <f>F15+'Income Statement'!G20-'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <f>G15+'Income Statement'!H20-'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <f>H15+'Income Statement'!I20-'Income Statement'!I22</f>
         <v/>
       </c>
@@ -9789,35 +10279,35 @@
           <t>Net (cash) / debt</t>
         </is>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="26">
         <f>B12-B9</f>
         <v/>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="26">
         <f>C12-C9</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="26">
         <f>D12-D9</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="26">
         <f>E12-E9</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="26">
         <f>F12-F9</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="26">
         <f>G12-G9</f>
         <v/>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="26">
         <f>H12-H9</f>
         <v/>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="26">
         <f>I12-I9</f>
         <v/>
       </c>
@@ -9828,35 +10318,35 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="33">
         <f>B15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="33">
         <f>C15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="33">
         <f>D15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="33">
         <f>E15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="33">
         <f>F15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="33">
         <f>G15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="33">
         <f>H15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="33">
         <f>I15/DCF!$B$43</f>
         <v/>
       </c>
@@ -9867,35 +10357,35 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="22">
         <f>'Income Statement'!B20/B15</f>
         <v/>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="22">
         <f>'Income Statement'!C20/C15</f>
         <v/>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <f>'Income Statement'!D20/D15</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="22">
         <f>'Income Statement'!E20/E15</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="22">
         <f>'Income Statement'!F20/F15</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="22">
         <f>'Income Statement'!G20/G15</f>
         <v/>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <f>'Income Statement'!H20/H15</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <f>'Income Statement'!I20/I15</f>
         <v/>
       </c>
@@ -9922,7 +10412,7 @@
           <t>Total assets (audited)</t>
         </is>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="26">
         <f>Assumptions!$B$101</f>
         <v/>
       </c>
@@ -9933,7 +10423,7 @@
           <t>Less total liabilities (audited)</t>
         </is>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="26">
         <f>-Assumptions!$B$104</f>
         <v/>
       </c>
@@ -9944,7 +10434,7 @@
           <t>Equals total equity</t>
         </is>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="26">
         <f>B21+B22</f>
         <v/>
       </c>
@@ -9955,7 +10445,7 @@
           <t>Equity attributable to owners plus minorities (audited)</t>
         </is>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="26">
         <f>Assumptions!$B$114+Assumptions!$B$117</f>
         <v/>
       </c>
@@ -9966,7 +10456,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="38">
         <f>B23-B24</f>
         <v/>
       </c>
@@ -10043,33 +10533,33 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -10081,27 +10571,27 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="23">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="23">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="23">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -10112,27 +10602,27 @@
           <t>Add back depreciation</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>Assumptions!$B$81</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>DCF!B8</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f>DCF!C8</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="23">
         <f>DCF!D8</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="23">
         <f>DCF!E8</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="23">
         <f>DCF!F8</f>
         <v/>
       </c>
@@ -10143,23 +10633,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="23">
         <f>DCF!B14</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="23">
         <f>DCF!C14</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="23">
         <f>DCF!D14</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="23">
         <f>DCF!E14</f>
         <v/>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="23">
         <f>DCF!F14</f>
         <v/>
       </c>
@@ -10170,27 +10660,27 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="24">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -10201,27 +10691,27 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="23">
         <f>-Assumptions!$B$84</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="23">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="23">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="23">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="23">
         <f>DCF!F13</f>
         <v/>
       </c>
@@ -10232,27 +10722,27 @@
           <t>Free cash flow to equity</t>
         </is>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="24">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="24">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="24">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="24">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -10263,27 +10753,27 @@
           <t>Dividends declared</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="23">
         <f>-Assumptions!$B$130</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="26">
         <f>-'Income Statement'!E22</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="26">
         <f>-'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="26">
         <f>-'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <f>-'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="26">
         <f>-'Income Statement'!I22</f>
         <v/>
       </c>
@@ -10294,27 +10784,27 @@
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="23">
         <f>Assumptions!$B$111</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="23">
         <f>'Balance Sheet'!E9</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="23">
         <f>'Balance Sheet'!F9</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="23">
         <f>'Balance Sheet'!G9</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="23">
         <f>'Balance Sheet'!H9</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="23">
         <f>'Balance Sheet'!I9</f>
         <v/>
       </c>
@@ -10325,23 +10815,23 @@
           <t>Memo: free cash flow to the firm</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="23">
         <f>DCF!B15</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="23">
         <f>DCF!C15</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="23">
         <f>DCF!D15</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="23">
         <f>DCF!E15</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="23">
         <f>DCF!F15</f>
         <v/>
       </c>
@@ -10422,43 +10912,43 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
@@ -10470,35 +10960,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="23">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="23">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="23">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="23">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="23">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="23">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="23">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
@@ -10509,35 +10999,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="23">
         <f>'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="23">
         <f>'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f>'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="23">
         <f>'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="23">
         <f>'Income Statement'!F14</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="23">
         <f>'Income Statement'!G14</f>
         <v/>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="23">
         <f>'Income Statement'!H14</f>
         <v/>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="23">
         <f>'Income Statement'!I14</f>
         <v/>
       </c>
@@ -10548,35 +11038,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="18">
         <f>'Income Statement'!B15</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="18">
         <f>'Income Statement'!C15</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="18">
         <f>'Income Statement'!D15</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="18">
         <f>'Income Statement'!E15</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="18">
         <f>'Income Statement'!F15</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="18">
         <f>'Income Statement'!G15</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="18">
         <f>'Income Statement'!H15</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="18">
         <f>'Income Statement'!I15</f>
         <v/>
       </c>
@@ -10587,35 +11077,35 @@
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="23">
         <f>'Income Statement'!B11</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="23">
         <f>'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="23">
         <f>'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="23">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="23">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="23">
         <f>'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="23">
         <f>'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="23">
         <f>'Income Statement'!I11</f>
         <v/>
       </c>
@@ -10626,35 +11116,35 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="23">
         <f>'Income Statement'!B20</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="23">
         <f>'Income Statement'!C20</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="23">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="23">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="23">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="23">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="23">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="23">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -10665,35 +11155,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="36">
         <f>'Income Statement'!B21</f>
         <v/>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="36">
         <f>'Income Statement'!C21</f>
         <v/>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="36">
         <f>'Income Statement'!D21</f>
         <v/>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="36">
         <f>'Income Statement'!E21</f>
         <v/>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="36">
         <f>'Income Statement'!F21</f>
         <v/>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="36">
         <f>'Income Statement'!G21</f>
         <v/>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="36">
         <f>'Income Statement'!H21</f>
         <v/>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="36">
         <f>'Income Statement'!I21</f>
         <v/>
       </c>
@@ -10720,31 +11210,31 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="22">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="22">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="22">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="22">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="22">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -10755,31 +11245,31 @@
           <t>EBITDA growth</t>
         </is>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <f>C6/B6-1</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <f>D6/C6-1</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="22">
         <f>E6/D6-1</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="22">
         <f>F6/E6-1</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="22">
         <f>G6/F6-1</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="22">
         <f>H6/G6-1</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <f>I6/H6-1</f>
         <v/>
       </c>
@@ -10790,31 +11280,31 @@
           <t>Profit growth</t>
         </is>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="22">
         <f>C9/B9-1</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <f>D9/C9-1</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <f>E9/D9-1</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="22">
         <f>F9/E9-1</f>
         <v/>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <f>G9/F9-1</f>
         <v/>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="22">
         <f>H9/G9-1</f>
         <v/>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <f>I9/H9-1</f>
         <v/>
       </c>

--- a/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +150,7 @@
     <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1137,35 +1138,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="37">
         <f>'Income Statement'!B21</f>
         <v/>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="37">
         <f>'Income Statement'!C21</f>
         <v/>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="37">
         <f>'Income Statement'!D21</f>
         <v/>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="37">
         <f>'Income Statement'!E21</f>
         <v/>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="37">
         <f>'Income Statement'!F21</f>
         <v/>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="37">
         <f>'Income Statement'!G21</f>
         <v/>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="37">
         <f>'Income Statement'!H21</f>
         <v/>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="37">
         <f>'Income Statement'!I21</f>
         <v/>
       </c>
@@ -1176,35 +1177,35 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="37">
         <f>'Balance Sheet'!B17</f>
         <v/>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>'Balance Sheet'!C17</f>
         <v/>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <f>'Balance Sheet'!D17</f>
         <v/>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="37">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="37">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="37">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="37">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="37">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -1215,35 +1216,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="40">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="40">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="40">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="40">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="40">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="40">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I7" s="39">
+      <c r="I7" s="40">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -1254,35 +1255,35 @@
           <t>Price / book (at spot)</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="40">
         <f>Assumptions!$B$5/B6</f>
         <v/>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="40">
         <f>Assumptions!$B$5/C6</f>
         <v/>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="40">
         <f>Assumptions!$B$5/D6</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="40">
         <f>Assumptions!$B$5/E6</f>
         <v/>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="40">
         <f>Assumptions!$B$5/F6</f>
         <v/>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="40">
         <f>Assumptions!$B$5/G6</f>
         <v/>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="40">
         <f>Assumptions!$B$5/H6</f>
         <v/>
       </c>
-      <c r="I8" s="39">
+      <c r="I8" s="40">
         <f>Assumptions!$B$5/I6</f>
         <v/>
       </c>
@@ -1363,35 +1364,35 @@
           <t>Net (cash) / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="40">
         <f>'Balance Sheet'!B16/'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="40">
         <f>'Balance Sheet'!C16/'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="40">
         <f>'Balance Sheet'!D16/'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="40">
         <f>'Balance Sheet'!E16/'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <f>'Balance Sheet'!F16/'Income Statement'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="40">
         <f>'Balance Sheet'!G16/'Income Statement'!G14</f>
         <v/>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="40">
         <f>'Balance Sheet'!H16/'Income Statement'!H14</f>
         <v/>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="40">
         <f>'Balance Sheet'!I16/'Income Statement'!I14</f>
         <v/>
       </c>
@@ -1418,7 +1419,7 @@
           <t>Shares issued (audited note 20)</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -1429,7 +1430,7 @@
           <t>Less treasury shares (audited note 21)</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>-Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1440,7 +1441,7 @@
           <t>Shares outstanding — ADOPTED</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <f>B14+B15</f>
         <v/>
       </c>
@@ -1451,8 +1452,8 @@
           <t>Shares implied by the FY2025 dividend at EGP 5.34 per share</t>
         </is>
       </c>
-      <c r="B17" s="31">
-        <f>Assumptions!$B$130/5.34</f>
+      <c r="B17" s="32">
+        <f>Assumptions!$B$131/5.34</f>
         <v/>
       </c>
     </row>
@@ -1462,7 +1463,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="41">
         <f>B17/B16-1</f>
         <v/>
       </c>
@@ -1485,7 +1486,7 @@
         </is>
       </c>
       <c r="B20" s="22">
-        <f>Assumptions!$B$132/Assumptions!$B$133-1</f>
+        <f>Assumptions!$B$133/Assumptions!$B$134-1</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1497,7 @@
         </is>
       </c>
       <c r="B21" s="26">
-        <f>Assumptions!$B$54*Assumptions!$B$132/Assumptions!$B$133</f>
+        <f>Assumptions!$B$55*Assumptions!$B$133/Assumptions!$B$134</f>
         <v/>
       </c>
     </row>
@@ -1529,7 +1530,7 @@
         </is>
       </c>
       <c r="B24" s="22">
-        <f>Assumptions!$B$134/Assumptions!$B$132</f>
+        <f>Assumptions!$B$135/Assumptions!$B$133</f>
         <v/>
       </c>
     </row>
@@ -1551,7 +1552,7 @@
         </is>
       </c>
       <c r="B26" s="26">
-        <f>4*Assumptions!$B$135</f>
+        <f>4*Assumptions!$B$136</f>
         <v/>
       </c>
     </row>
@@ -1584,7 +1585,7 @@
         </is>
       </c>
       <c r="B29" s="26">
-        <f>Assumptions!$B$136-Assumptions!$B$137-Assumptions!$B$138</f>
+        <f>Assumptions!$B$137-Assumptions!$B$138-Assumptions!$B$139</f>
         <v/>
       </c>
     </row>
@@ -1681,7 +1682,7 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
     </row>
@@ -1692,7 +1693,7 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>Assumptions!$B$146</f>
+        <f>Assumptions!$B$147</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1715,7 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>Assumptions!$B$145</f>
+        <f>Assumptions!$B$146</f>
         <v/>
       </c>
     </row>
@@ -1736,7 +1737,7 @@
         </is>
       </c>
       <c r="B10" s="26">
-        <f>-Assumptions!$B$81</f>
+        <f>-Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -1814,8 +1815,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="39">
-        <f>Assumptions!$B$143</f>
+      <c r="B18" s="40">
+        <f>Assumptions!$B$144</f>
         <v/>
       </c>
     </row>
@@ -1847,7 +1848,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="42">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -1869,7 +1870,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="33">
         <f>B22/DCF!$B$43</f>
         <v/>
       </c>
@@ -1893,8 +1894,8 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="B26" s="39">
-        <f>Assumptions!$B$144</f>
+      <c r="B26" s="40">
+        <f>Assumptions!$B$145</f>
         <v/>
       </c>
     </row>
@@ -1926,7 +1927,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="42">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -1948,7 +1949,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="33">
         <f>B30/DCF!$B$43</f>
         <v/>
       </c>
@@ -2018,7 +2019,7 @@
           <t>Cement capacity (Mt/yr, audited note 1)</t>
         </is>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="43">
         <f>Assumptions!$B$13</f>
         <v/>
       </c>
@@ -2030,7 +2031,7 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>Assumptions!$B$141</f>
+        <f>Assumptions!$B$142</f>
         <v/>
       </c>
     </row>
@@ -2041,7 +2042,7 @@
         </is>
       </c>
       <c r="B7" s="26">
-        <f>Assumptions!$B$142</f>
+        <f>Assumptions!$B$143</f>
         <v/>
       </c>
     </row>
@@ -2084,7 +2085,7 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="42">
         <f>DCF!B41</f>
         <v/>
       </c>
@@ -2106,7 +2107,7 @@
           <t>Value per share (EGP)</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>B12/DCF!$B$43</f>
         <v/>
       </c>
@@ -2117,8 +2118,8 @@
           <t>Memo: what the MARKET is paying per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B14" s="37">
-        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$117)/Assumptions!$B$13/Assumptions!$B$11</f>
+      <c r="B14" s="38">
+        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$118)/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2130,7 @@
         </is>
       </c>
       <c r="B15" s="26">
-        <f>Assumptions!$B$105+Assumptions!$B$106</f>
+        <f>Assumptions!$B$106+Assumptions!$B$107</f>
         <v/>
       </c>
     </row>
@@ -2139,7 +2140,7 @@
           <t>Memo: that book value per annual tonne (USD)</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="38">
         <f>B15/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
@@ -2190,7 +2191,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>Cost of debt: currency composition as contracted (adopted) vs the pound-equivalent under uncovered interest parity</t>
         </is>
@@ -2205,12 +2206,12 @@
           <t>13.36%</t>
         </is>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E20" s="7" t="n">
-        <v>61.80028530387204</v>
+        <v>57.11539589886546</v>
       </c>
       <c r="F20" s="22">
         <f>E20/D20-1</f>
@@ -2218,7 +2219,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>Beta: contemporaneous regression (adopted) vs lead-lag sum-beta</t>
         </is>
@@ -2233,12 +2234,12 @@
           <t>0.919</t>
         </is>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E21" s="7" t="n">
-        <v>53.48004877782317</v>
+        <v>49.58022435083235</v>
       </c>
       <c r="F21" s="22">
         <f>E21/D21-1</f>
@@ -2246,7 +2247,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Capex: economic maintenance in dollars per tonne (adopted) vs book depreciation</t>
         </is>
@@ -2261,12 +2262,12 @@
           <t>book depreciation</t>
         </is>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="37">
         <f>DCF!$B$44</f>
         <v/>
       </c>
       <c r="E22" s="7" t="n">
-        <v>67.29433644504972</v>
+        <v>62.66429612426797</v>
       </c>
       <c r="F22" s="22">
         <f>E22/D22-1</f>
@@ -2318,15 +2319,15 @@
         </is>
       </c>
       <c r="B28" s="23">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C28" s="23">
-        <f>Assumptions!$B$83</f>
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
       <c r="D28" s="23">
-        <f>Assumptions!$B$84</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
     </row>
@@ -2356,15 +2357,15 @@
         </is>
       </c>
       <c r="B30" s="23">
-        <f>Assumptions!$B$79</f>
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2432,15 +2433,15 @@
         </is>
       </c>
       <c r="B34" s="22">
-        <f>B32/(Assumptions!$B$116+Assumptions!$B$124)</f>
+        <f>B32/(Assumptions!$B$117+Assumptions!$B$125)</f>
         <v/>
       </c>
       <c r="C34" s="22">
-        <f>C32/(Assumptions!$B$115+Assumptions!$B$123)</f>
+        <f>C32/(Assumptions!$B$116+Assumptions!$B$124)</f>
         <v/>
       </c>
       <c r="D34" s="22">
-        <f>D32/(Assumptions!$B$114+DCF!$C$44)</f>
+        <f>D32/(Assumptions!$B$115+DCF!$C$44)</f>
         <v/>
       </c>
     </row>
@@ -2525,7 +2526,7 @@
         </is>
       </c>
       <c r="B41" s="22">
-        <f>Assumptions!$B$49</f>
+        <f>Assumptions!$B$50</f>
         <v/>
       </c>
     </row>
@@ -2645,15 +2646,15 @@
           <t>DCF (cash flow)</t>
         </is>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="45">
         <f>DCF!B44</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>Assumptions!$B$147</f>
-        <v/>
-      </c>
-      <c r="D5" s="33">
+        <f>Assumptions!$B$148</f>
+        <v/>
+      </c>
+      <c r="D5" s="34">
         <f>B5*C5</f>
         <v/>
       </c>
@@ -2661,7 +2662,7 @@
         <f>B5/Assumptions!$B$5-1</f>
         <v/>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <f>DCF!B34</f>
         <v/>
       </c>
@@ -2672,15 +2673,15 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="45">
         <f>'Relative &amp; Normalized'!B23</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Assumptions!$B$148</f>
-        <v/>
-      </c>
-      <c r="D6" s="33">
+        <f>Assumptions!$B$149</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
         <f>B6*C6</f>
         <v/>
       </c>
@@ -2700,15 +2701,15 @@
           <t>Normalised earnings</t>
         </is>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="45">
         <f>'Relative &amp; Normalized'!B31</f>
         <v/>
       </c>
       <c r="C7" s="18">
-        <f>Assumptions!$B$149</f>
-        <v/>
-      </c>
-      <c r="D7" s="33">
+        <f>Assumptions!$B$150</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
         <f>B7*C7</f>
         <v/>
       </c>
@@ -2728,15 +2729,15 @@
           <t>Asset / replacement cost</t>
         </is>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="45">
         <f>'Fundamental Valuation'!B13</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>Assumptions!$B$150</f>
-        <v/>
-      </c>
-      <c r="D8" s="33">
+        <f>Assumptions!$B$151</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
         <f>B8*C8</f>
         <v/>
       </c>
@@ -2756,19 +2757,19 @@
           <t>WEIGHTED CENTRAL FAIR VALUE</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>SUMPRODUCT(B5:B8,C5:C8)</f>
         <v/>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>B9/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -2779,7 +2780,7 @@
           <t>Lowest lens</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <f>MIN(B5:B8)</f>
         <v/>
       </c>
@@ -2794,7 +2795,7 @@
           <t>Highest lens</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="34">
         <f>MAX(B5:B8)</f>
         <v/>
       </c>
@@ -2809,7 +2810,7 @@
           <t>Market price, 6 August 2026</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -2868,13 +2869,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>59.0043470762966</v>
+        <v>58.81090803276457</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>69.06790434251907</v>
+        <v>68.87446529898703</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>79.13146160874153</v>
+        <v>78.93802256520951</v>
       </c>
       <c r="E17" s="22">
         <f>C17/Assumptions!$B$5-1</f>
@@ -2888,13 +2889,13 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46.31038656787247</v>
+        <v>46.11694752434044</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>53.1401107197773</v>
+        <v>52.94667167624527</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>59.96983487168214</v>
+        <v>59.77639582815011</v>
       </c>
       <c r="E18" s="22">
         <f>C18/Assumptions!$B$5-1</f>
@@ -2908,13 +2909,13 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>49.13650867854979</v>
+        <v>46.44553116758097</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>55.39428968170785</v>
+        <v>52.3465209611052</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>63.73799768591857</v>
+        <v>60.21450735247083</v>
       </c>
       <c r="E19" s="22">
         <f>C19/Assumptions!$B$5-1</f>
@@ -2927,7 +2928,7 @@
           <t>Panel median</t>
         </is>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="33">
         <f>MEDIAN(C17:C19)</f>
         <v/>
       </c>
@@ -3088,11 +3089,11 @@
           <t>Spot</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -3320,7 +3321,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window cost of capital against terminal growth</t>
         </is>
@@ -3359,19 +3360,19 @@
         <v>0.2151592218162085</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>69.68480446917765</v>
+        <v>65.4358916875569</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>67.02354639938432</v>
+        <v>62.50166028165984</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>63.80382223673868</v>
+        <v>58.95167921684183</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>59.82923330334724</v>
+        <v>54.56940460534815</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>54.79906056677138</v>
+        <v>49.0232717487574</v>
       </c>
     </row>
     <row r="7">
@@ -3379,19 +3380,19 @@
         <v>0.2301592218162085</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>68.62467545844318</v>
+        <v>64.4439240155076</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>66.01291262285645</v>
+        <v>61.56426472056051</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>62.85307028953042</v>
+        <v>58.08030774646356</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>58.95240248854102</v>
+        <v>53.77953658279984</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>54.01578309071213</v>
+        <v>48.33655311551247</v>
       </c>
     </row>
     <row r="8">
@@ -3399,19 +3400,19 @@
         <v>0.2451592218162085</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>67.59129378051799</v>
+        <v>63.47697718452289</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>65.02774111983067</v>
+        <v>60.65047312877611</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>61.9262258862966</v>
+        <v>57.23082604253523</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58.09755998163097</v>
+        <v>53.00944222874014</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>53.2520649697296</v>
+        <v>47.66693005285683</v>
       </c>
     </row>
     <row r="9">
@@ -3419,19 +3420,19 @@
         <v>0.2601592218162085</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>66.58375921938828</v>
+        <v>62.53420917582012</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>64.0671754246041</v>
+        <v>59.75949172543742</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>61.0224854926659</v>
+        <v>56.40249868484688</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>57.26396758933526</v>
+        <v>52.25845816628281</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>52.50725070512303</v>
+        <v>47.01383036072006</v>
       </c>
     </row>
     <row r="10">
@@ -3439,23 +3440,23 @@
         <v>0.2751592218162085</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>65.60120983131745</v>
+        <v>61.61481376702958</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>63.13039547455369</v>
+        <v>58.89056046516151</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>60.14107971589755</v>
+        <v>55.59462149526185</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>56.45091846835627</v>
+        <v>51.52594918262109</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>51.78071261511543</v>
+        <v>46.376706107654</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window rate against TERMINAL rate</t>
         </is>
@@ -3494,19 +3495,19 @@
         <v>0.2151592218162085</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>74.54479265991846</v>
+        <v>68.64597961649716</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>68.55901969603394</v>
+        <v>63.24452286800533</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>63.80382223673868</v>
+        <v>58.95167921684183</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>59.92930060886857</v>
+        <v>55.45228030851626</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>56.70691323937821</v>
+        <v>52.54046790287568</v>
       </c>
     </row>
     <row r="15">
@@ -3514,19 +3515,19 @@
         <v>0.2301592218162085</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>73.38777996625358</v>
+        <v>67.58840394218933</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>67.5169597654033</v>
+        <v>62.29070054744534</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>62.85307028953042</v>
+        <v>58.08030774646356</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>59.05293251959468</v>
+        <v>54.64811079075967</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>55.89239471828357</v>
+        <v>51.79220562056756</v>
       </c>
     </row>
     <row r="16">
@@ -3534,19 +3535,19 @@
         <v>0.2451592218162085</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>72.26016858976557</v>
+        <v>66.55767856176094</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>66.50123914144211</v>
+        <v>61.36096433551278</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>61.9262258862966</v>
+        <v>57.23082604253523</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>58.19849137161848</v>
+        <v>53.86404122630424</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>55.09815671448623</v>
+        <v>51.06255463427581</v>
       </c>
     </row>
     <row r="17">
@@ -3554,19 +3555,19 @@
         <v>0.2601592218162085</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>71.16096421323304</v>
+        <v>65.55289576343243</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>65.51096985080824</v>
+        <v>60.45450253462565</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>61.0224854926659</v>
+        <v>56.40249868484688</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>57.36524238774131</v>
+        <v>53.09939834102199</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>54.32352159125278</v>
+        <v>50.35089334641367</v>
       </c>
     </row>
     <row r="18">
@@ -3574,23 +3575,23 @@
         <v>0.2751592218162085</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>70.08921493439811</v>
+        <v>64.57318654984805</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>64.54530172310298</v>
+        <v>59.57053799713047</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>60.14107971589755</v>
+        <v>55.59462149526185</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>56.55248195173446</v>
+        <v>52.35353740838655</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>53.56784039640031</v>
+        <v>49.65662646699894</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): beta</t>
         </is>
@@ -3631,23 +3632,23 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>62.1918530339136</v>
+        <v>57.47276405811282</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>56.34393307051827</v>
+        <v>52.17638945894387</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>51.73278769457785</v>
+        <v>47.99537909787394</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>48.86156459044297</v>
+        <v>45.38931766855932</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>46.37628177687942</v>
+        <v>43.13157219177125</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): margin shift</t>
         </is>
@@ -3688,23 +3689,23 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>49.80257797286092</v>
+        <v>45.32347853334107</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>55.86440192957877</v>
+        <v>51.27715228793815</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>61.9262258862966</v>
+        <v>57.23082604253523</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>67.98804984301447</v>
+        <v>63.18449979713233</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>74.04987379973232</v>
+        <v>69.13817355172941</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="A28" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): net cash (EGP mn)</t>
         </is>
@@ -3714,27 +3715,27 @@
       <c r="A29" s="14" t="inlineStr"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>426</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1,249</t>
+          <t>1,176</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1,999</t>
+          <t>1,926</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2,749</t>
+          <t>2,676</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>3,499</t>
+          <t>3,426</t>
         </is>
       </c>
     </row>
@@ -3745,19 +3746,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>57.92481146632743</v>
+        <v>53.22941162256606</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>59.92551867631202</v>
+        <v>55.23011883255064</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>61.9262258862966</v>
+        <v>57.23082604253523</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>63.92693309628118</v>
+        <v>59.23153325251982</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>65.92764030626577</v>
+        <v>61.2322404625044</v>
       </c>
     </row>
     <row r="32">
@@ -3864,22 +3865,22 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="C5" s="23">
-        <f>Assumptions!$B$75</f>
+        <f>Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D5" s="23">
         <f>DCF!C45</f>
         <v/>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="40">
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="40">
         <f>D5/B5</f>
         <v/>
       </c>
@@ -3895,22 +3896,22 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>Assumptions!$B$157</f>
+        <f>Assumptions!$B$158</f>
         <v/>
       </c>
       <c r="C6" s="23">
-        <f>Assumptions!$B$158</f>
+        <f>Assumptions!$B$159</f>
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>Assumptions!$B$159</f>
-        <v/>
-      </c>
-      <c r="E6" s="39">
+        <f>Assumptions!$B$160</f>
+        <v/>
+      </c>
+      <c r="E6" s="40">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <f>D6/B6</f>
         <v/>
       </c>
@@ -3926,22 +3927,22 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>Assumptions!$B$160</f>
+        <f>Assumptions!$B$161</f>
         <v/>
       </c>
       <c r="C7" s="23">
-        <f>Assumptions!$B$161</f>
+        <f>Assumptions!$B$162</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>Assumptions!$B$162</f>
-        <v/>
-      </c>
-      <c r="E7" s="39">
+        <f>Assumptions!$B$163</f>
+        <v/>
+      </c>
+      <c r="E7" s="40">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <f>D7/B7</f>
         <v/>
       </c>
@@ -3956,7 +3957,7 @@
           <t>Peer average price / earnings (excluding the subject)</t>
         </is>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="47">
         <f>AVERAGE(E6:E7)</f>
         <v/>
       </c>
@@ -3992,8 +3993,8 @@
           <t>Nameplate capacity (Mt)</t>
         </is>
       </c>
-      <c r="B13" s="47">
-        <f>Assumptions!$B$152</f>
+      <c r="B13" s="48">
+        <f>Assumptions!$B$153</f>
         <v/>
       </c>
     </row>
@@ -4003,8 +4004,8 @@
           <t>Production 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B14" s="47">
-        <f>Assumptions!$B$153</f>
+      <c r="B14" s="48">
+        <f>Assumptions!$B$154</f>
         <v/>
       </c>
     </row>
@@ -4014,8 +4015,8 @@
           <t>Domestic consumption 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B15" s="47">
-        <f>Assumptions!$B$154</f>
+      <c r="B15" s="48">
+        <f>Assumptions!$B$155</f>
         <v/>
       </c>
     </row>
@@ -4025,8 +4026,8 @@
           <t>Exports 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B16" s="47">
-        <f>Assumptions!$B$155</f>
+      <c r="B16" s="48">
+        <f>Assumptions!$B$156</f>
         <v/>
       </c>
     </row>
@@ -4036,8 +4037,8 @@
           <t>Dormant capacity under revival (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="47">
-        <f>Assumptions!$B$156</f>
+      <c r="B17" s="48">
+        <f>Assumptions!$B$157</f>
         <v/>
       </c>
     </row>
@@ -4114,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -4307,7 +4308,7 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>0.733</v>
+        <v>0.7329</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -4466,7 +4467,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cement exported, share of cement made</t>
+          <t>Cement exported, share of cement sold</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
@@ -4491,685 +4492,695 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Local price index</t>
+          <t>Cement stock draw (Mt)</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>1</v>
+        <v>0.0725</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1.1772</v>
+        <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1.2714</v>
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1.3604</v>
+        <v>0</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>1.4488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Export price index (USD)</t>
+          <t>Local price index</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.968</v>
+        <v>1.08</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.944</v>
+        <v>1.1772</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.927</v>
+        <v>1.2714</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.911</v>
+        <v>1.3604</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.895</v>
+        <v>1.4488</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USD/EGP path</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="C27" s="12" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>61.5</v>
+          <t>Export price index (USD)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Local cost-inflation index</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>1.226</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>1.336</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>1.544</v>
+          <t>USD/EGP path</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>61.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Local cost-inflation index</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>1.544</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Alternative-fuel saving on materials</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C30" s="9" t="n">
         <v>0.015</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D30" s="9" t="n">
         <v>0.03</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E30" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.048</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G30" s="9" t="n">
         <v>0.055</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>FORECAST DRIVERS — FY2026E to FY2030E</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr"/>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr"/>
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Depreciation as % of revenue</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>0.033</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EGP marginal cost-of-debt path</t>
+          <t>Depreciation as % of revenue</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.206</v>
+        <v>0.025</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>0.181</v>
+        <v>0.027</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.161</v>
+        <v>0.029</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.149</v>
+        <v>0.031</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.14</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yield earned on cash</t>
+          <t>EGP marginal cost-of-debt path</t>
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.15</v>
+        <v>0.206</v>
       </c>
       <c r="C34" s="9" t="n">
-        <v>0.13</v>
+        <v>0.181</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.12</v>
+        <v>0.161</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.112</v>
+        <v>0.149</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.108</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>USD/t capacity</t>
-        </is>
+          <t>Yield earned on cash</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change in working capital / change in revenue</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>0.12</v>
+          <t>Maintenance capital expenditure</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>USD/t capacity</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Change in working capital / change in revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B38" s="9" t="n">
         <v>0.556</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Risk-free rate (EGP 10-year government)</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.2295</v>
-      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Risk-free rate (EGP 10-year government)</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>0.034</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>0.0941</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Euribor (EBRD and NBE reference rate)</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>0.0249</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
+          <t>Euribor (EBRD and NBE reference rate)</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>0.206</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Expected EGP depreciation against the euro</t>
+          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>0.06</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Expected EGP depreciation against the euro</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>0.135</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="n">
-        <v>0.2</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Terminal growth rate</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Elapsed fraction of FY2026 at the valuation date</t>
         </is>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B51" s="11" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>AUDITED INCOME STATEMENT — PASTED CLASS 1 (EGP mn)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>FY2023 sales (net)</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>6042.831338</v>
-      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FY2024 sales (net)</t>
+          <t>FY2023 sales (net)</t>
         </is>
       </c>
       <c r="B53" s="15" t="n">
-        <v>8729.782821000001</v>
+        <v>6042.831338</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FY2025 sales (net)</t>
+          <t>FY2024 sales (net)</t>
         </is>
       </c>
       <c r="B54" s="15" t="n">
-        <v>12447.320081</v>
+        <v>8729.782821000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FY2023 cost of sales</t>
+          <t>FY2025 sales (net)</t>
         </is>
       </c>
       <c r="B55" s="15" t="n">
-        <v>4759.815212</v>
+        <v>12447.320081</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FY2024 cost of sales</t>
+          <t>FY2023 cost of sales</t>
         </is>
       </c>
       <c r="B56" s="15" t="n">
-        <v>6642.972487</v>
+        <v>4759.815212</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales</t>
+          <t>FY2024 cost of sales</t>
         </is>
       </c>
       <c r="B57" s="15" t="n">
-        <v>7389.054416</v>
+        <v>6642.972487</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FY2023 general and administrative expenses</t>
+          <t>FY2025 cost of sales</t>
         </is>
       </c>
       <c r="B58" s="15" t="n">
-        <v>183.940276</v>
+        <v>7389.054416</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FY2024 general and administrative expenses</t>
+          <t>FY2023 general and administrative expenses</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>267.798104</v>
+        <v>183.940276</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FY2025 general and administrative expenses</t>
+          <t>FY2024 general and administrative expenses</t>
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>384.332833</v>
+        <v>267.798104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FY2023 provisions charged</t>
+          <t>FY2025 general and administrative expenses</t>
         </is>
       </c>
       <c r="B61" s="15" t="n">
-        <v>15.220195</v>
+        <v>384.332833</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FY2024 provisions charged</t>
+          <t>FY2023 provisions charged</t>
         </is>
       </c>
       <c r="B62" s="15" t="n">
-        <v>56.05295</v>
+        <v>15.220195</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FY2025 provisions charged</t>
+          <t>FY2024 provisions charged</t>
         </is>
       </c>
       <c r="B63" s="15" t="n">
-        <v>74.505707</v>
+        <v>56.05295</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FY2023 expected credit losses</t>
+          <t>FY2025 provisions charged</t>
         </is>
       </c>
       <c r="B64" s="15" t="n">
-        <v>4.745753</v>
+        <v>74.505707</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FY2024 expected credit losses</t>
+          <t>FY2023 expected credit losses</t>
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>-1.106452</v>
+        <v>4.745753</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FY2025 expected credit losses</t>
+          <t>FY2024 expected credit losses</t>
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>3.603563</v>
+        <v>-1.106452</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FY2023 profit before tax</t>
+          <t>FY2025 expected credit losses</t>
         </is>
       </c>
       <c r="B67" s="15" t="n">
-        <v>930.231432</v>
+        <v>3.603563</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FY2024 profit before tax</t>
+          <t>FY2023 profit before tax</t>
         </is>
       </c>
       <c r="B68" s="15" t="n">
-        <v>1505.866118</v>
+        <v>930.231432</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FY2025 profit before tax</t>
+          <t>FY2024 profit before tax</t>
         </is>
       </c>
       <c r="B69" s="15" t="n">
-        <v>4725.157878</v>
+        <v>1505.866118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FY2023 income tax</t>
+          <t>FY2025 profit before tax</t>
         </is>
       </c>
       <c r="B70" s="15" t="n">
-        <v>232.732802</v>
+        <v>4725.157878</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FY2024 income tax</t>
+          <t>FY2023 income tax</t>
         </is>
       </c>
       <c r="B71" s="15" t="n">
-        <v>345.730996</v>
+        <v>232.732802</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FY2025 income tax</t>
+          <t>FY2024 income tax</t>
         </is>
       </c>
       <c r="B72" s="15" t="n">
-        <v>1125.467657</v>
+        <v>345.730996</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FY2023 attributable profit</t>
+          <t>FY2025 income tax</t>
         </is>
       </c>
       <c r="B73" s="15" t="n">
-        <v>697.488741</v>
+        <v>1125.467657</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FY2024 attributable profit</t>
+          <t>FY2023 attributable profit</t>
         </is>
       </c>
       <c r="B74" s="15" t="n">
-        <v>1160.129411</v>
+        <v>697.488741</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit</t>
+          <t>FY2024 attributable profit</t>
         </is>
       </c>
       <c r="B75" s="15" t="n">
-        <v>3599.585937</v>
+        <v>1160.129411</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FY2023 earnings per share</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+          <t>FY2025 attributable profit</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n">
+        <v>3599.585937</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FY2024 earnings per share</t>
+          <t>FY2023 earnings per share</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>3.02</v>
+        <v>1.81</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
@@ -5180,11 +5191,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FY2025 earnings per share</t>
+          <t>FY2024 earnings per share</t>
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>9.49</v>
+        <v>3.02</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
@@ -5195,671 +5206,671 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FY2023 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="n">
-        <v>250.424521</v>
+          <t>FY2025 earnings per share</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FY2024 depreciation and amortisation</t>
+          <t>FY2023 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B80" s="15" t="n">
-        <v>256.801527</v>
+        <v>250.424521</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FY2025 depreciation and amortisation</t>
+          <t>FY2024 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B81" s="15" t="n">
-        <v>289.771295</v>
+        <v>256.801527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FY2023 capital expenditure</t>
+          <t>FY2025 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B82" s="15" t="n">
-        <v>58.543963</v>
+        <v>289.771295</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FY2024 capital expenditure</t>
+          <t>FY2023 capital expenditure</t>
         </is>
       </c>
       <c r="B83" s="15" t="n">
-        <v>912.0154</v>
+        <v>58.543963</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FY2025 capital expenditure</t>
+          <t>FY2024 capital expenditure</t>
         </is>
       </c>
       <c r="B84" s="15" t="n">
-        <v>796.47076</v>
+        <v>912.0154</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FY2025 interest income</t>
+          <t>FY2025 capital expenditure</t>
         </is>
       </c>
       <c r="B85" s="15" t="n">
-        <v>226.274781</v>
+        <v>796.47076</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FY2025 other income</t>
+          <t>FY2025 interest income</t>
         </is>
       </c>
       <c r="B86" s="15" t="n">
-        <v>53.339508</v>
+        <v>226.274781</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FY2025 finance costs</t>
+          <t>FY2025 other income</t>
         </is>
       </c>
       <c r="B87" s="15" t="n">
-        <v>49.841733</v>
+        <v>53.339508</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>FY2025 finance costs</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n">
+        <v>49.841733</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>FY2025 foreign exchange differences</t>
         </is>
       </c>
-      <c r="B88" s="15" t="n">
+      <c r="B89" s="15" t="n">
         <v>-101.57824</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>AUDITED REVENUE AND COST NOTES (EGP mn)</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>FY2025 local sales of goods</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="n">
-        <v>8350.454610000001</v>
-      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
+      <c r="I90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FY2025 local services</t>
+          <t>FY2025 local sales of goods</t>
         </is>
       </c>
       <c r="B91" s="15" t="n">
-        <v>281.863546</v>
+        <v>8350.454610000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FY2025 export sales of goods</t>
+          <t>FY2025 local services</t>
         </is>
       </c>
       <c r="B92" s="15" t="n">
-        <v>3356.422381</v>
+        <v>281.863546</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FY2025 export services</t>
+          <t>FY2025 export sales of goods</t>
         </is>
       </c>
       <c r="B93" s="15" t="n">
-        <v>458.579544</v>
+        <v>3356.422381</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FY2024 total local sales</t>
+          <t>FY2025 export services</t>
         </is>
       </c>
       <c r="B94" s="15" t="n">
-        <v>4883.304477</v>
+        <v>458.579544</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FY2024 total export sales</t>
+          <t>FY2024 total local sales</t>
         </is>
       </c>
       <c r="B95" s="15" t="n">
-        <v>3846.478344</v>
+        <v>4883.304477</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — materials and fuel</t>
+          <t>FY2024 total export sales</t>
         </is>
       </c>
       <c r="B96" s="15" t="n">
-        <v>5698.184715</v>
+        <v>3846.478344</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — transportation</t>
+          <t>FY2025 cost of sales — materials and fuel</t>
         </is>
       </c>
       <c r="B97" s="15" t="n">
-        <v>764.279332</v>
+        <v>5698.184715</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — overheads</t>
+          <t>FY2025 cost of sales — transportation</t>
         </is>
       </c>
       <c r="B98" s="15" t="n">
-        <v>641.143208</v>
+        <v>764.279332</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>FY2025 cost of sales — overheads</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="n">
+        <v>641.143208</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>FY2025 administrative depreciation</t>
         </is>
       </c>
-      <c r="B99" s="15" t="n">
+      <c r="B100" s="15" t="n">
         <v>4.324134</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>AUDITED BALANCE SHEET — PASTED CLASS 1 (EGP mn)</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
-      <c r="I100" s="6" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Total assets FY2025</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="n">
-        <v>8783.721849</v>
-      </c>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="6" t="n"/>
+      <c r="H101" s="6" t="n"/>
+      <c r="I101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Total assets FY2024</t>
+          <t>Total assets FY2025</t>
         </is>
       </c>
       <c r="B102" s="15" t="n">
-        <v>5848.616103</v>
+        <v>8783.721849</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Total assets FY2023</t>
+          <t>Total assets FY2024</t>
         </is>
       </c>
       <c r="B103" s="15" t="n">
-        <v>3887.527427</v>
+        <v>5848.616103</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Total liabilities FY2025</t>
+          <t>Total assets FY2023</t>
         </is>
       </c>
       <c r="B104" s="15" t="n">
-        <v>4140.989609</v>
+        <v>3887.527427</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Property, plant and equipment FY2025</t>
+          <t>Total liabilities FY2025</t>
         </is>
       </c>
       <c r="B105" s="15" t="n">
-        <v>2522.323523</v>
+        <v>4140.989609</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Assets under construction FY2025</t>
+          <t>Property, plant and equipment FY2025</t>
         </is>
       </c>
       <c r="B106" s="15" t="n">
-        <v>391.543753</v>
+        <v>2522.323523</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Intangible assets FY2025</t>
+          <t>Assets under construction FY2025</t>
         </is>
       </c>
       <c r="B107" s="15" t="n">
-        <v>106.799617</v>
+        <v>391.543753</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Inventories FY2025</t>
+          <t>Intangible assets FY2025</t>
         </is>
       </c>
       <c r="B108" s="15" t="n">
-        <v>1053.646218</v>
+        <v>106.799617</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Trade receivables FY2025</t>
+          <t>Inventories FY2025</t>
         </is>
       </c>
       <c r="B109" s="15" t="n">
-        <v>244.416417</v>
+        <v>1053.646218</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Debtors and other debit balances FY2025</t>
+          <t>Trade receivables FY2025</t>
         </is>
       </c>
       <c r="B110" s="15" t="n">
-        <v>1004.779062</v>
+        <v>244.416417</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2025</t>
+          <t>Debtors and other debit balances FY2025</t>
         </is>
       </c>
       <c r="B111" s="15" t="n">
-        <v>3459.391229</v>
+        <v>1004.779062</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2024</t>
+          <t>Cash and bank balances FY2025</t>
         </is>
       </c>
       <c r="B112" s="15" t="n">
-        <v>1687.062873</v>
+        <v>3459.391229</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2023</t>
+          <t>Cash and bank balances FY2024</t>
         </is>
       </c>
       <c r="B113" s="15" t="n">
-        <v>561.09968</v>
+        <v>1687.062873</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2025</t>
+          <t>Cash and bank balances FY2023</t>
         </is>
       </c>
       <c r="B114" s="15" t="n">
-        <v>4642.574235</v>
+        <v>561.09968</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2024</t>
+          <t>Equity attributable to owners FY2025</t>
         </is>
       </c>
       <c r="B115" s="15" t="n">
-        <v>2303.472299</v>
+        <v>4642.574235</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2023</t>
+          <t>Equity attributable to owners FY2024</t>
         </is>
       </c>
       <c r="B116" s="15" t="n">
-        <v>1754.221659</v>
+        <v>2303.472299</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Equity attributable to owners FY2023</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="n">
+        <v>1754.221659</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>Non-controlling interests FY2025</t>
         </is>
       </c>
-      <c r="B117" s="8" t="n">
+      <c r="B118" s="8" t="n">
         <v>0.158005</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>AUDITED DEBT NOTE 25 (EGP mn)</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="6" t="n"/>
-      <c r="I118" s="6" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>CIB credit facilities — EGP</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="n">
-        <v>99.916937</v>
-      </c>
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+      <c r="E119" s="6" t="n"/>
+      <c r="F119" s="6" t="n"/>
+      <c r="G119" s="6" t="n"/>
+      <c r="H119" s="6" t="n"/>
+      <c r="I119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>National Bank of Egypt facility — EUR</t>
+          <t>CIB credit facilities — EGP</t>
         </is>
       </c>
       <c r="B120" s="15" t="n">
-        <v>145.741484</v>
+        <v>99.916937</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EBRD facility — EUR</t>
+          <t>National Bank of Egypt facility — EUR</t>
         </is>
       </c>
       <c r="B121" s="15" t="n">
-        <v>888.274195</v>
+        <v>145.741484</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lease liabilities</t>
+          <t>EBRD facility — EUR</t>
         </is>
       </c>
       <c r="B122" s="15" t="n">
-        <v>1.176042</v>
+        <v>888.274195</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2024</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="B123" s="15" t="n">
-        <v>760.917684</v>
+        <v>1.176042</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2023</t>
+          <t>Total interest-bearing debt FY2024</t>
         </is>
       </c>
       <c r="B124" s="15" t="n">
-        <v>90.07427300000001</v>
+        <v>760.917684</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FY2025 loan interest expense</t>
+          <t>Total interest-bearing debt FY2023</t>
         </is>
       </c>
       <c r="B125" s="15" t="n">
-        <v>24.61313</v>
+        <v>90.07427300000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FY2025 credit-facility interest expense</t>
+          <t>FY2025 loan interest expense</t>
         </is>
       </c>
       <c r="B126" s="15" t="n">
-        <v>23.00737</v>
+        <v>24.61313</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FY2024 loan interest expense</t>
+          <t>FY2025 credit-facility interest expense</t>
         </is>
       </c>
       <c r="B127" s="15" t="n">
-        <v>2.754107</v>
+        <v>23.00737</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>FY2024 loan interest expense</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="n">
+        <v>2.754107</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>FY2024 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B128" s="15" t="n">
+      <c r="B129" s="15" t="n">
         <v>85.95302599999999</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>DIVIDENDS AND Q1-2026 (EGP mn)</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
-      <c r="G129" s="6" t="n"/>
-      <c r="H129" s="6" t="n"/>
-      <c r="I129" s="6" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>FY2025 dividend declared</t>
-        </is>
-      </c>
-      <c r="B130" s="15" t="n">
-        <v>2001.79216</v>
-      </c>
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="6" t="n"/>
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="6" t="n"/>
+      <c r="I130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FY2024 dividend approved and paid</t>
+          <t>FY2025 dividend declared</t>
         </is>
       </c>
       <c r="B131" s="15" t="n">
-        <v>1102.110289</v>
+        <v>2001.79216</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Q1-2026 sales</t>
+          <t>FY2024 dividend approved and paid</t>
         </is>
       </c>
       <c r="B132" s="15" t="n">
-        <v>2995.95935</v>
+        <v>1102.110289</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Q1-2025 sales</t>
+          <t>Q1-2026 sales</t>
         </is>
       </c>
       <c r="B133" s="15" t="n">
-        <v>2554.448091</v>
+        <v>2995.95935</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q1-2026 gross profit</t>
+          <t>Q1-2025 sales</t>
         </is>
       </c>
       <c r="B134" s="15" t="n">
-        <v>1286.145881</v>
+        <v>2554.448091</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q1-2026 attributable profit</t>
+          <t>Q1-2026 gross profit</t>
         </is>
       </c>
       <c r="B135" s="15" t="n">
-        <v>943.068309</v>
+        <v>1286.145881</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q1-2026 cash and bank balances</t>
+          <t>Q1-2026 attributable profit</t>
         </is>
       </c>
       <c r="B136" s="15" t="n">
-        <v>4379.627379</v>
+        <v>943.068309</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q1-2026 interest-bearing debt</t>
+          <t>Q1-2026 cash and bank balances</t>
         </is>
       </c>
       <c r="B137" s="15" t="n">
-        <v>1260.509089</v>
+        <v>4379.627379</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Q1-2026 dividends payable</t>
+          <t>Q1-2026 interest-bearing debt</t>
         </is>
       </c>
       <c r="B138" s="15" t="n">
-        <v>2001.79216</v>
+        <v>1260.509089</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Q1-2026 dividends payable</t>
+        </is>
+      </c>
+      <c r="B139" s="15" t="n">
+        <v>2001.79216</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Q1-2026 finance costs</t>
         </is>
       </c>
-      <c r="B139" s="15" t="n">
+      <c r="B140" s="15" t="n">
         <v>11.168843</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>LENS INPUTS</t>
         </is>
       </c>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
-      <c r="G140" s="6" t="n"/>
-      <c r="H140" s="6" t="n"/>
-      <c r="I140" s="6" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Replacement cost per annual tonne</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
-      </c>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="6" t="n"/>
+      <c r="F141" s="6" t="n"/>
+      <c r="G141" s="6" t="n"/>
+      <c r="H141" s="6" t="n"/>
+      <c r="I141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Justified enterprise value per annual tonne</t>
+          <t>Replacement cost per annual tonne</t>
         </is>
       </c>
       <c r="B142" s="15" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
@@ -5870,121 +5881,121 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B143" s="16" t="n">
-        <v>4.5</v>
+          <t>Justified enterprise value per annual tonne</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
+          <t>Justified EV/EBITDA</t>
         </is>
       </c>
       <c r="B144" s="16" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="n">
-        <v>0.312</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Normalised revenue haircut</t>
+          <t>Mid-cycle EBITDA margin</t>
         </is>
       </c>
       <c r="B146" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Weight — cash-flow lens</t>
+          <t>Normalised revenue haircut</t>
         </is>
       </c>
       <c r="B147" s="9" t="n">
-        <v>0.5</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Weight — relative lens</t>
+          <t>Weight — cash-flow lens</t>
         </is>
       </c>
       <c r="B148" s="9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Weight — normalised lens</t>
+          <t>Weight — relative lens</t>
         </is>
       </c>
       <c r="B149" s="9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>Weight — normalised lens</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>Weight — asset lens</t>
         </is>
       </c>
-      <c r="B150" s="9" t="n">
+      <c r="B151" s="9" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>SECTOR AND PEERS</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="6" t="n"/>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Egyptian nameplate capacity</t>
-        </is>
-      </c>
-      <c r="B152" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="n"/>
+      <c r="F152" s="6" t="n"/>
+      <c r="G152" s="6" t="n"/>
+      <c r="H152" s="6" t="n"/>
+      <c r="I152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Egyptian production 2025</t>
+          <t>Egyptian nameplate capacity</t>
         </is>
       </c>
       <c r="B153" s="12" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
@@ -5995,11 +6006,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Egyptian consumption 2025</t>
+          <t>Egyptian production 2025</t>
         </is>
       </c>
       <c r="B154" s="12" t="n">
-        <v>54</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
@@ -6010,11 +6021,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Egyptian exports 2025</t>
+          <t>Egyptian consumption 2025</t>
         </is>
       </c>
       <c r="B155" s="12" t="n">
-        <v>18.5</v>
+        <v>53.9</v>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
@@ -6025,11 +6036,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dormant capacity under revival</t>
+          <t>Egyptian exports 2025</t>
         </is>
       </c>
       <c r="B156" s="12" t="n">
-        <v>12.6</v>
+        <v>18.6</v>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
@@ -6040,72 +6051,87 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement revenue</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="n">
-        <v>9090</v>
+          <t>Dormant capacity under revival</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement profit</t>
+          <t>Peer — Sinai Cement revenue</t>
         </is>
       </c>
       <c r="B158" s="15" t="n">
-        <v>2290</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement market capitalisation</t>
+          <t>Peer — Sinai Cement profit</t>
         </is>
       </c>
       <c r="B159" s="15" t="n">
-        <v>20604.19</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef revenue</t>
+          <t>Peer — Sinai Cement market capitalisation</t>
         </is>
       </c>
       <c r="B160" s="15" t="n">
-        <v>5700</v>
+        <v>20604.19</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef profit</t>
+          <t>Peer — Misr Beni Suef revenue</t>
         </is>
       </c>
       <c r="B161" s="15" t="n">
-        <v>3946</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>Peer — Misr Beni Suef profit</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="n">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B162" s="15" t="n">
+      <c r="B163" s="15" t="n">
         <v>13730</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>Every cell on this sheet is BLUE — an input. Nothing here is computed from anything else here.</t>
-        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Every cell on this sheet is BLUE — an input. Nothing here is computed from anything else here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>Everything on every other sheet that can be derived from these is a formula.</t>
         </is>
@@ -6114,7 +6140,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A165:J165"/>
-    <mergeCell ref="A164:J164"/>
+    <mergeCell ref="A166:J166"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6293,7 +6319,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cement exported, share of cement made</t>
+          <t>Cement exported, share of cement sold</t>
         </is>
       </c>
       <c r="B15" s="18">
@@ -6308,7 +6334,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>B12*B15</f>
+        <f>B29*B15</f>
         <v/>
       </c>
     </row>
@@ -6319,7 +6345,7 @@
         </is>
       </c>
       <c r="B17" s="19">
-        <f>B12-B16</f>
+        <f>B29-B16</f>
         <v/>
       </c>
     </row>
@@ -6330,7 +6356,18 @@
         </is>
       </c>
       <c r="B18" s="21">
-        <f>B12+B9</f>
+        <f>B29+B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Plus draw from finished-goods stock (Mt)</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -6357,7 +6394,7 @@
         </is>
       </c>
       <c r="B21" s="23">
-        <f>Assumptions!$B$90</f>
+        <f>Assumptions!$B$91</f>
         <v/>
       </c>
     </row>
@@ -6379,7 +6416,7 @@
         </is>
       </c>
       <c r="B23" s="23">
-        <f>Assumptions!$B$92</f>
+        <f>Assumptions!$B$93</f>
         <v/>
       </c>
     </row>
@@ -6430,11 +6467,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cement exports as a share of cement made — against a 30% statutory cap</t>
+          <t>Cement exports as a share of cement PRODUCED — the 30% statutory cap bites here</t>
         </is>
       </c>
       <c r="B28" s="22">
         <f>B16/B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cement SOLD (Mt)</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>B12+B19</f>
         <v/>
       </c>
     </row>
@@ -6461,7 +6509,7 @@
         </is>
       </c>
       <c r="B31" s="23">
-        <f>Assumptions!$B$96</f>
+        <f>Assumptions!$B$97</f>
         <v/>
       </c>
     </row>
@@ -6472,7 +6520,7 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>Assumptions!$B$97</f>
+        <f>Assumptions!$B$98</f>
         <v/>
       </c>
     </row>
@@ -6483,7 +6531,7 @@
         </is>
       </c>
       <c r="B33" s="26">
-        <f>Assumptions!$B$98+Assumptions!$B$60-Assumptions!$B$99</f>
+        <f>Assumptions!$B$99+Assumptions!$B$61-Assumptions!$B$100</f>
         <v/>
       </c>
     </row>
@@ -6860,27 +6908,27 @@
         </is>
       </c>
       <c r="B53" s="19">
-        <f>B50*B52</f>
+        <f>B75*B52</f>
         <v/>
       </c>
       <c r="C53" s="19">
-        <f>C50*C52</f>
+        <f>C75*C52</f>
         <v/>
       </c>
       <c r="D53" s="19">
-        <f>D50*D52</f>
+        <f>D75*D52</f>
         <v/>
       </c>
       <c r="E53" s="19">
-        <f>E50*E52</f>
+        <f>E75*E52</f>
         <v/>
       </c>
       <c r="F53" s="19">
-        <f>F50*F52</f>
+        <f>F75*F52</f>
         <v/>
       </c>
       <c r="G53" s="19">
-        <f>G50*G52</f>
+        <f>G75*G52</f>
         <v/>
       </c>
     </row>
@@ -6891,27 +6939,27 @@
         </is>
       </c>
       <c r="B54" s="19">
-        <f>B50-B53</f>
+        <f>B75-B53</f>
         <v/>
       </c>
       <c r="C54" s="19">
-        <f>C50-C53</f>
+        <f>C75-C53</f>
         <v/>
       </c>
       <c r="D54" s="19">
-        <f>D50-D53</f>
+        <f>D75-D53</f>
         <v/>
       </c>
       <c r="E54" s="19">
-        <f>E50-E53</f>
+        <f>E75-E53</f>
         <v/>
       </c>
       <c r="F54" s="19">
-        <f>F50-F53</f>
+        <f>F75-F53</f>
         <v/>
       </c>
       <c r="G54" s="19">
-        <f>G50-G53</f>
+        <f>G75-G53</f>
         <v/>
       </c>
     </row>
@@ -6922,27 +6970,27 @@
         </is>
       </c>
       <c r="B55" s="21">
-        <f>B50+B48</f>
+        <f>B75+B48</f>
         <v/>
       </c>
       <c r="C55" s="21">
-        <f>C50+C48</f>
+        <f>C75+C48</f>
         <v/>
       </c>
       <c r="D55" s="21">
-        <f>D50+D48</f>
+        <f>D75+D48</f>
         <v/>
       </c>
       <c r="E55" s="21">
-        <f>E50+E48</f>
+        <f>E75+E48</f>
         <v/>
       </c>
       <c r="F55" s="21">
-        <f>F50+F48</f>
+        <f>F75+F48</f>
         <v/>
       </c>
       <c r="G55" s="21">
-        <f>G50+G48</f>
+        <f>G75+G48</f>
         <v/>
       </c>
     </row>
@@ -6953,27 +7001,27 @@
         </is>
       </c>
       <c r="B56" s="26">
-        <f>$B$22*Assumptions!$B$25</f>
+        <f>$B$22*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="C56" s="26">
-        <f>$B$22*Assumptions!$C$25</f>
+        <f>$B$22*Assumptions!$C$26</f>
         <v/>
       </c>
       <c r="D56" s="26">
-        <f>$B$22*Assumptions!$D$25</f>
+        <f>$B$22*Assumptions!$D$26</f>
         <v/>
       </c>
       <c r="E56" s="26">
-        <f>$B$22*Assumptions!$E$25</f>
+        <f>$B$22*Assumptions!$E$26</f>
         <v/>
       </c>
       <c r="F56" s="26">
-        <f>$B$22*Assumptions!$F$25</f>
+        <f>$B$22*Assumptions!$F$26</f>
         <v/>
       </c>
       <c r="G56" s="26">
-        <f>$B$22*Assumptions!$G$25</f>
+        <f>$B$22*Assumptions!$G$26</f>
         <v/>
       </c>
     </row>
@@ -6984,27 +7032,27 @@
         </is>
       </c>
       <c r="B57" s="26">
-        <f>$B$26*Assumptions!$B$26*Assumptions!$B$27</f>
+        <f>$B$26*Assumptions!$B$27*Assumptions!$B$28</f>
         <v/>
       </c>
       <c r="C57" s="26">
-        <f>$B$26*Assumptions!$C$26*Assumptions!$C$27</f>
+        <f>$B$26*Assumptions!$C$27*Assumptions!$C$28</f>
         <v/>
       </c>
       <c r="D57" s="26">
-        <f>$B$26*Assumptions!$D$26*Assumptions!$D$27</f>
+        <f>$B$26*Assumptions!$D$27*Assumptions!$D$28</f>
         <v/>
       </c>
       <c r="E57" s="26">
-        <f>$B$26*Assumptions!$E$26*Assumptions!$E$27</f>
+        <f>$B$26*Assumptions!$E$27*Assumptions!$E$28</f>
         <v/>
       </c>
       <c r="F57" s="26">
-        <f>$B$26*Assumptions!$F$26*Assumptions!$F$27</f>
+        <f>$B$26*Assumptions!$F$27*Assumptions!$F$28</f>
         <v/>
       </c>
       <c r="G57" s="26">
-        <f>$B$26*Assumptions!$G$26*Assumptions!$G$27</f>
+        <f>$B$26*Assumptions!$G$27*Assumptions!$G$28</f>
         <v/>
       </c>
     </row>
@@ -7232,27 +7280,27 @@
         </is>
       </c>
       <c r="B65" s="26">
-        <f>$B$35*Assumptions!$B$28*(1-Assumptions!$B$29)*B46</f>
+        <f>$B$35*Assumptions!$B$29*(1-Assumptions!$B$30)*B46</f>
         <v/>
       </c>
       <c r="C65" s="26">
-        <f>$B$35*Assumptions!$C$28*(1-Assumptions!$C$29)*C46</f>
+        <f>$B$35*Assumptions!$C$29*(1-Assumptions!$C$30)*C46</f>
         <v/>
       </c>
       <c r="D65" s="26">
-        <f>$B$35*Assumptions!$D$28*(1-Assumptions!$D$29)*D46</f>
+        <f>$B$35*Assumptions!$D$29*(1-Assumptions!$D$30)*D46</f>
         <v/>
       </c>
       <c r="E65" s="26">
-        <f>$B$35*Assumptions!$E$28*(1-Assumptions!$E$29)*E46</f>
+        <f>$B$35*Assumptions!$E$29*(1-Assumptions!$E$30)*E46</f>
         <v/>
       </c>
       <c r="F65" s="26">
-        <f>$B$35*Assumptions!$F$28*(1-Assumptions!$F$29)*F46</f>
+        <f>$B$35*Assumptions!$F$29*(1-Assumptions!$F$30)*F46</f>
         <v/>
       </c>
       <c r="G65" s="26">
-        <f>$B$35*Assumptions!$G$28*(1-Assumptions!$G$29)*G46</f>
+        <f>$B$35*Assumptions!$G$29*(1-Assumptions!$G$30)*G46</f>
         <v/>
       </c>
     </row>
@@ -7263,27 +7311,27 @@
         </is>
       </c>
       <c r="B66" s="26">
-        <f>$B$36*Assumptions!$B$28*B55</f>
+        <f>$B$36*Assumptions!$B$29*B55</f>
         <v/>
       </c>
       <c r="C66" s="26">
-        <f>$B$36*Assumptions!$C$28*C55</f>
+        <f>$B$36*Assumptions!$C$29*C55</f>
         <v/>
       </c>
       <c r="D66" s="26">
-        <f>$B$36*Assumptions!$D$28*D55</f>
+        <f>$B$36*Assumptions!$D$29*D55</f>
         <v/>
       </c>
       <c r="E66" s="26">
-        <f>$B$36*Assumptions!$E$28*E55</f>
+        <f>$B$36*Assumptions!$E$29*E55</f>
         <v/>
       </c>
       <c r="F66" s="26">
-        <f>$B$36*Assumptions!$F$28*F55</f>
+        <f>$B$36*Assumptions!$F$29*F55</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>$B$36*Assumptions!$G$28*G55</f>
+        <f>$B$36*Assumptions!$G$29*G55</f>
         <v/>
       </c>
     </row>
@@ -7294,27 +7342,27 @@
         </is>
       </c>
       <c r="B67" s="26">
-        <f>$B$37*Assumptions!$B$28*B55</f>
+        <f>$B$37*Assumptions!$B$29*B55</f>
         <v/>
       </c>
       <c r="C67" s="26">
-        <f>$B$37*Assumptions!$C$28*C55</f>
+        <f>$B$37*Assumptions!$C$29*C55</f>
         <v/>
       </c>
       <c r="D67" s="26">
-        <f>$B$37*Assumptions!$D$28*D55</f>
+        <f>$B$37*Assumptions!$D$29*D55</f>
         <v/>
       </c>
       <c r="E67" s="26">
-        <f>$B$37*Assumptions!$E$28*E55</f>
+        <f>$B$37*Assumptions!$E$29*E55</f>
         <v/>
       </c>
       <c r="F67" s="26">
-        <f>$B$37*Assumptions!$F$28*F55</f>
+        <f>$B$37*Assumptions!$F$29*F55</f>
         <v/>
       </c>
       <c r="G67" s="26">
-        <f>$B$37*Assumptions!$G$28*G55</f>
+        <f>$B$37*Assumptions!$G$29*G55</f>
         <v/>
       </c>
     </row>
@@ -7387,27 +7435,27 @@
         </is>
       </c>
       <c r="B70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*B63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*B63</f>
         <v/>
       </c>
       <c r="C70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*C63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*C63</f>
         <v/>
       </c>
       <c r="D70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*D63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*D63</f>
         <v/>
       </c>
       <c r="E70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*E63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*E63</f>
         <v/>
       </c>
       <c r="F70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*F63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*F63</f>
         <v/>
       </c>
       <c r="G70" s="26">
-        <f>(Assumptions!$B$63+Assumptions!$B$66)/Assumptions!$B$54*G63</f>
+        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*G63</f>
         <v/>
       </c>
     </row>
@@ -7504,18 +7552,67 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Draw from finished-goods stock (Mt)  (DRIVER)</t>
+        </is>
+      </c>
+      <c r="B74" s="20">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C74" s="20">
+        <f>Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D74" s="20">
+        <f>Assumptions!$D$25</f>
+        <v/>
+      </c>
+      <c r="E74" s="20">
+        <f>Assumptions!$E$25</f>
+        <v/>
+      </c>
+      <c r="F74" s="20">
+        <f>Assumptions!$F$25</f>
+        <v/>
+      </c>
+      <c r="G74" s="20">
+        <f>Assumptions!$G$25</f>
+        <v/>
+      </c>
+    </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>VALIDATION — AND A PRICE TEST THAT CAN ACTUALLY FAIL</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="n"/>
+      <c r="B75" s="27">
+        <f>B50+B74</f>
+        <v/>
+      </c>
+      <c r="C75" s="27">
+        <f>C50+C74</f>
+        <v/>
+      </c>
+      <c r="D75" s="27">
+        <f>D50+D74</f>
+        <v/>
+      </c>
+      <c r="E75" s="27">
+        <f>E50+E74</f>
+        <v/>
+      </c>
+      <c r="F75" s="27">
+        <f>F50+F74</f>
+        <v/>
+      </c>
+      <c r="G75" s="27">
+        <f>G50+G74</f>
+        <v/>
+      </c>
       <c r="H75" s="6" t="n"/>
       <c r="I75" s="6" t="n"/>
       <c r="J75" s="6" t="n"/>
@@ -7538,7 +7635,7 @@
         </is>
       </c>
       <c r="B77" s="23">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
     </row>
@@ -7610,7 +7707,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>local EGP 2,916/t, export cement USD 46.6/t, export clinker USD 30.3/t.</t>
+          <t>local EGP 2,856/t, export cement USD 46.2/t, export clinker USD 30.0/t.</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7776,7 @@
           <t>Peak kiln utilisation — must stay below 100%</t>
         </is>
       </c>
-      <c r="B94" s="27">
+      <c r="B94" s="28">
         <f>B93/B92</f>
         <v/>
       </c>
@@ -7723,7 +7820,7 @@
           <t>Peak mill utilisation — must stay below 100%</t>
         </is>
       </c>
-      <c r="B98" s="27">
+      <c r="B98" s="28">
         <f>B97/B96</f>
         <v/>
       </c>
@@ -7951,23 +8048,23 @@
         </is>
       </c>
       <c r="B8" s="26">
-        <f>B5*Assumptions!$B$32</f>
+        <f>B5*Assumptions!$B$33</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>C5*Assumptions!$C$32</f>
+        <f>C5*Assumptions!$C$33</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>D5*Assumptions!$D$32</f>
+        <f>D5*Assumptions!$D$33</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>E5*Assumptions!$E$32</f>
+        <f>E5*Assumptions!$E$33</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>F5*Assumptions!$F$32</f>
+        <f>F5*Assumptions!$F$33</f>
         <v/>
       </c>
     </row>
@@ -8086,23 +8183,23 @@
         </is>
       </c>
       <c r="B13" s="26">
-        <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$C$27</f>
+        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$C$28</f>
         <v/>
       </c>
       <c r="C13" s="26">
-        <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$D$27</f>
+        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$D$28</f>
         <v/>
       </c>
       <c r="D13" s="26">
-        <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$E$27</f>
+        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$E$28</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$F$27</f>
+        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$F$28</f>
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>-Assumptions!$B$13*Assumptions!$B$35*Assumptions!$G$27</f>
+        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$G$28</f>
         <v/>
       </c>
     </row>
@@ -8113,23 +8210,23 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>-(B5-Assumptions!$B$54)*Assumptions!$B$36</f>
+        <f>-(B5-Assumptions!$B$55)*Assumptions!$B$37</f>
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>-(C5-B5)*Assumptions!$B$36</f>
+        <f>-(C5-B5)*Assumptions!$B$37</f>
         <v/>
       </c>
       <c r="D14" s="26">
-        <f>-(D5-C5)*Assumptions!$B$36</f>
+        <f>-(D5-C5)*Assumptions!$B$37</f>
         <v/>
       </c>
       <c r="E14" s="26">
-        <f>-(E5-D5)*Assumptions!$B$36</f>
+        <f>-(E5-D5)*Assumptions!$B$37</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>-(F5-E5)*Assumptions!$B$36</f>
+        <f>-(F5-E5)*Assumptions!$B$37</f>
         <v/>
       </c>
     </row>
@@ -8140,7 +8237,7 @@
         </is>
       </c>
       <c r="B15" s="24">
-        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$50)</f>
+        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$51)</f>
         <v/>
       </c>
       <c r="C15" s="24">
@@ -8166,24 +8263,24 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="28">
-        <f>(Assumptions!$B$33-Assumptions!$B$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
-        <v/>
-      </c>
-      <c r="C16" s="28">
-        <f>(Assumptions!$B$33-Assumptions!$C$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
-        <v/>
-      </c>
-      <c r="D16" s="28">
-        <f>(Assumptions!$B$33-Assumptions!$D$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>(Assumptions!$B$33-Assumptions!$E$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>(Assumptions!$B$33-Assumptions!$F$33)/(Assumptions!$B$33-Assumptions!$F$33)</f>
+      <c r="B16" s="29">
+        <f>(Assumptions!$B$34-Assumptions!$B$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
+        <v/>
+      </c>
+      <c r="C16" s="29">
+        <f>(Assumptions!$B$34-Assumptions!$C$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
+        <v/>
+      </c>
+      <c r="D16" s="29">
+        <f>(Assumptions!$B$34-Assumptions!$D$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
+        <v/>
+      </c>
+      <c r="E16" s="29">
+        <f>(Assumptions!$B$34-Assumptions!$E$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>(Assumptions!$B$34-Assumptions!$F$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
         <v/>
       </c>
     </row>
@@ -8193,23 +8290,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>$C$40-($C$40-$C$50)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>$C$40-($C$40-$C$50)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>$C$40-($C$40-$C$50)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>$C$40-($C$40-$C$50)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>$C$40-($C$40-$C$50)*F16</f>
         <v/>
       </c>
@@ -8220,24 +8317,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="28">
-        <f>1/(1+B17)^((1-Assumptions!$B$50)/2)</f>
-        <v/>
-      </c>
-      <c r="C18" s="28">
-        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="28">
-        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="28">
-        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
+      <c r="B18" s="29">
+        <f>1/(1+B17)^((1-Assumptions!$B$51)/2)</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
     </row>
@@ -8289,7 +8386,7 @@
         </is>
       </c>
       <c r="B22" s="26">
-        <f>Assumptions!$B$13*Assumptions!$B$141*Assumptions!$B$11*Assumptions!$G$28</f>
+        <f>Assumptions!$B$13*Assumptions!$B$142*Assumptions!$B$11*Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
@@ -8300,7 +8397,7 @@
         </is>
       </c>
       <c r="B23" s="26">
-        <f>F11*(1+Assumptions!$B$49)</f>
+        <f>F11*(1+Assumptions!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -8322,7 +8419,7 @@
         </is>
       </c>
       <c r="B25" s="22">
-        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$114+$C$44)</f>
+        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$115+$C$44)</f>
         <v/>
       </c>
     </row>
@@ -8333,7 +8430,7 @@
         </is>
       </c>
       <c r="B26" s="22">
-        <f>Assumptions!$B$49/B24</f>
+        <f>Assumptions!$B$50/B24</f>
         <v/>
       </c>
     </row>
@@ -8344,7 +8441,7 @@
         </is>
       </c>
       <c r="B27" s="26">
-        <f>B23*(1-B26)/($C$50-Assumptions!$B$49)</f>
+        <f>B23*(1-B26)/($C$50-Assumptions!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -8365,8 +8462,8 @@
           <t>End-of-window discount factor  (t = 4.417y, not the year-5 mid-point)</t>
         </is>
       </c>
-      <c r="B29" s="28">
-        <f>1/((1+B17)^(1-Assumptions!$B$50)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
+      <c r="B29" s="29">
+        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
         <v/>
       </c>
     </row>
@@ -8423,7 +8520,7 @@
           <t>TERMINAL VALUE AS % OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="28">
         <f>B32/B33</f>
         <v/>
       </c>
@@ -8435,7 +8532,7 @@
         </is>
       </c>
       <c r="B35" s="26">
-        <f>Assumptions!$B$111</f>
+        <f>Assumptions!$B$112</f>
         <v/>
       </c>
       <c r="E35" t="inlineStr">
@@ -8451,11 +8548,11 @@
         </is>
       </c>
       <c r="B36" s="26">
-        <f>B15/(1-Assumptions!$B$50)*Assumptions!$B$50+Assumptions!$B$111*Assumptions!$B$34*Assumptions!$B$50*(1-Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C36" s="29">
-        <f>Assumptions!$B$39</f>
+        <f>B15/(1-Assumptions!$B$51)*Assumptions!$B$51+Assumptions!$B$112*Assumptions!$B$35*Assumptions!$B$51*(1-Assumptions!$B$9)</f>
+        <v/>
+      </c>
+      <c r="C36" s="30">
+        <f>Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -8471,11 +8568,11 @@
         </is>
       </c>
       <c r="B37" s="26">
-        <f>-Assumptions!$B$130</f>
-        <v/>
-      </c>
-      <c r="C37" s="29">
-        <f>-Assumptions!$B$40</f>
+        <f>-Assumptions!$B$131</f>
+        <v/>
+      </c>
+      <c r="C37" s="30">
+        <f>-Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -8494,7 +8591,7 @@
         <f>SUM(B35:B37)</f>
         <v/>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <f>C36+C37</f>
         <v/>
       </c>
@@ -8511,11 +8608,11 @@
         </is>
       </c>
       <c r="B39" s="26">
-        <f>-Assumptions!$B$137</f>
-        <v/>
-      </c>
-      <c r="C39" s="29">
-        <f>C38+Assumptions!$B$10*Assumptions!$B$41</f>
+        <f>-Assumptions!$B$138</f>
+        <v/>
+      </c>
+      <c r="C39" s="30">
+        <f>C38+Assumptions!$B$10*Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E39" t="inlineStr">
@@ -8534,7 +8631,7 @@
         <f>B38+B39</f>
         <v/>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="31">
         <f>(1-C43)*C39+C43*C42</f>
         <v/>
       </c>
@@ -8550,12 +8647,12 @@
           <t>Less non-controlling interests (audited note 24)</t>
         </is>
       </c>
-      <c r="B41" s="31">
-        <f>-Assumptions!$B$117</f>
-        <v/>
-      </c>
-      <c r="C41" s="30">
-        <f>(Assumptions!$B$119*Assumptions!$B$43+Assumptions!$B$120*(Assumptions!$B$42+0.03)+Assumptions!$B$121*(Assumptions!$B$42+0.0435)+Assumptions!$B$122*Assumptions!$B$43)/C44</f>
+      <c r="B41" s="32">
+        <f>-Assumptions!$B$118</f>
+        <v/>
+      </c>
+      <c r="C41" s="31">
+        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03)+Assumptions!$B$122*(Assumptions!$B$43+0.0435)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
         <v/>
       </c>
       <c r="E41" t="inlineStr">
@@ -8574,7 +8671,7 @@
         <f>B33+B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <f>C41*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
@@ -8590,11 +8687,11 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="32">
         <f>Assumptions!$B$6-Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <f>C44/(C44+C45)</f>
         <v/>
       </c>
@@ -8610,12 +8707,12 @@
           <t>FAIR VALUE PER SHARE (EGP)</t>
         </is>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <f>B42/B43</f>
         <v/>
       </c>
       <c r="C44" s="26">
-        <f>Assumptions!$B$119+Assumptions!$B$120+Assumptions!$B$121+Assumptions!$B$122</f>
+        <f>Assumptions!$B$120+Assumptions!$B$121+Assumptions!$B$122+Assumptions!$B$123</f>
         <v/>
       </c>
       <c r="E44" t="inlineStr">
@@ -8637,7 +8734,7 @@
     </row>
     <row r="46">
       <c r="C46" s="22">
-        <f>(Assumptions!$B$120+Assumptions!$B$121)/C44</f>
+        <f>(Assumptions!$B$121+Assumptions!$B$122)/C44</f>
         <v/>
       </c>
       <c r="E46" t="inlineStr">
@@ -8648,7 +8745,7 @@
     </row>
     <row r="47">
       <c r="C47" s="19">
-        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$48/(1-Assumptions!$B$48))</f>
+        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$49/(1-Assumptions!$B$49))</f>
         <v/>
       </c>
       <c r="E47" t="inlineStr">
@@ -8658,8 +8755,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="29">
-        <f>Assumptions!$B$46+C47*Assumptions!$B$47</f>
+      <c r="C48" s="30">
+        <f>Assumptions!$B$47+C47*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="E48" t="inlineStr">
@@ -8669,8 +8766,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="29">
-        <f>Assumptions!$B$45*(1-Assumptions!$B$8)</f>
+      <c r="C49" s="30">
+        <f>Assumptions!$B$46*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
       <c r="E49" t="inlineStr">
@@ -8680,8 +8777,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="30">
-        <f>(1-Assumptions!$B$48)*C48+Assumptions!$B$48*C49</f>
+      <c r="C50" s="31">
+        <f>(1-Assumptions!$B$49)*C48+Assumptions!$B$49*C49</f>
         <v/>
       </c>
       <c r="E50" t="inlineStr">
@@ -8691,8 +8788,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="29">
-        <f>Assumptions!$B$39+Assumptions!$B$10*Assumptions!$B$41</f>
+      <c r="C51" s="30">
+        <f>Assumptions!$B$40+Assumptions!$B$10*Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E51" t="inlineStr">
@@ -8743,8 +8840,8 @@
           <t>CIB facility rate — EGP corridor + 0.6%</t>
         </is>
       </c>
-      <c r="B56" s="29">
-        <f>Assumptions!$B$43</f>
+      <c r="B56" s="30">
+        <f>Assumptions!$B$44</f>
         <v/>
       </c>
     </row>
@@ -8754,8 +8851,8 @@
           <t>NBE/KfW facility rate — Euribor + 3.00%</t>
         </is>
       </c>
-      <c r="B57" s="29">
-        <f>Assumptions!$B$42+0.03</f>
+      <c r="B57" s="30">
+        <f>Assumptions!$B$43+0.03</f>
         <v/>
       </c>
     </row>
@@ -8765,8 +8862,8 @@
           <t>EBRD facility rate — Euribor + 4.35%</t>
         </is>
       </c>
-      <c r="B58" s="29">
-        <f>Assumptions!$B$42+0.0435</f>
+      <c r="B58" s="30">
+        <f>Assumptions!$B$43+0.0435</f>
         <v/>
       </c>
     </row>
@@ -8776,7 +8873,7 @@
           <t>ADOPTED blended cost of debt</t>
         </is>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="31">
         <f>C41</f>
         <v/>
       </c>
@@ -8787,8 +8884,8 @@
           <t>Effective rate computed FY2024 (interest / average debt)</t>
         </is>
       </c>
-      <c r="B60" s="29">
-        <f>(Assumptions!$B$127+Assumptions!$B$128)/((Assumptions!$B$124+Assumptions!$B$123)/2)</f>
+      <c r="B60" s="30">
+        <f>(Assumptions!$B$128+Assumptions!$B$129)/((Assumptions!$B$125+Assumptions!$B$124)/2)</f>
         <v/>
       </c>
     </row>
@@ -8798,8 +8895,8 @@
           <t>Effective rate computed FY2025</t>
         </is>
       </c>
-      <c r="B61" s="29">
-        <f>(Assumptions!$B$125+Assumptions!$B$126)/((Assumptions!$B$123+C44-Assumptions!$B$122)/2)</f>
+      <c r="B61" s="30">
+        <f>(Assumptions!$B$126+Assumptions!$B$127)/((Assumptions!$B$124+C44-Assumptions!$B$123)/2)</f>
         <v/>
       </c>
     </row>
@@ -8809,8 +8906,8 @@
           <t>Effective rate computed Q1-2026, annualised</t>
         </is>
       </c>
-      <c r="B62" s="29">
-        <f>Assumptions!$B$139*4/((C44+Assumptions!$B$137)/2)</f>
+      <c r="B62" s="30">
+        <f>Assumptions!$B$140*4/((C44+Assumptions!$B$138)/2)</f>
         <v/>
       </c>
     </row>
@@ -8820,8 +8917,8 @@
           <t>Pound-EQUIVALENT cost of debt under interest parity</t>
         </is>
       </c>
-      <c r="B63" s="30">
-        <f>(Assumptions!$B$119*Assumptions!$B$43+Assumptions!$B$120*(Assumptions!$B$42+0.03+Assumptions!$B$44)+Assumptions!$B$121*(Assumptions!$B$42+0.0435+Assumptions!$B$44)+Assumptions!$B$122*Assumptions!$B$43)/C44</f>
+      <c r="B63" s="31">
+        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03+Assumptions!$B$45)+Assumptions!$B$122*(Assumptions!$B$43+0.0435+Assumptions!$B$45)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
         <v/>
       </c>
     </row>
@@ -8932,7 +9029,7 @@
         <f>DCF!B31</f>
         <v/>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>B5/DCF!$B$43</f>
         <v/>
       </c>
@@ -8947,7 +9044,7 @@
         <f>DCF!B32</f>
         <v/>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>B6/DCF!$B$43</f>
         <v/>
       </c>
@@ -8958,11 +9055,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="35">
         <f>DCF!B33</f>
         <v/>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>B7/DCF!$B$43</f>
         <v/>
       </c>
@@ -8977,7 +9074,7 @@
         <f>DCF!B40</f>
         <v/>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>B8/DCF!$B$43</f>
         <v/>
       </c>
@@ -8992,7 +9089,7 @@
         <f>DCF!B41</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <f>B9/DCF!$B$43</f>
         <v/>
       </c>
@@ -9003,11 +9100,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>DCF!B42</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>B10/DCF!$B$43</f>
         <v/>
       </c>
@@ -9018,7 +9115,7 @@
           <t>TERMINAL VALUE AS % OF ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>DCF!B34</f>
         <v/>
       </c>
@@ -9029,7 +9126,7 @@
           <t>Memo: spot price</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -9040,7 +9137,7 @@
           <t>Fair value less spot</t>
         </is>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>C10-C13</f>
         <v/>
       </c>
@@ -9062,7 +9159,7 @@
           <t>Memo: enterprise value per annual tonne of capacity (USD)</t>
         </is>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <f>B7/Assumptions!$B$13/Assumptions!$B$11</f>
         <v/>
       </c>
@@ -9192,15 +9289,15 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>Assumptions!$B$52</f>
+        <f>Assumptions!$B$53</f>
         <v/>
       </c>
       <c r="C5" s="23">
-        <f>Assumptions!$B$53</f>
+        <f>Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="D5" s="23">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="E5" s="23">
@@ -9231,15 +9328,15 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>-Assumptions!$B$55</f>
+        <f>-Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="C6" s="23">
-        <f>-Assumptions!$B$56</f>
+        <f>-Assumptions!$B$57</f>
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>-Assumptions!$B$57</f>
+        <f>-Assumptions!$B$58</f>
         <v/>
       </c>
       <c r="E6" s="26" t="n"/>
@@ -9293,15 +9390,15 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>-Assumptions!$B$58</f>
+        <f>-Assumptions!$B$59</f>
         <v/>
       </c>
       <c r="C9" s="23">
-        <f>-Assumptions!$B$59</f>
+        <f>-Assumptions!$B$60</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>-Assumptions!$B$60</f>
+        <f>-Assumptions!$B$61</f>
         <v/>
       </c>
     </row>
@@ -9312,15 +9409,15 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>-Assumptions!$B$61-Assumptions!$B$64</f>
+        <f>-Assumptions!$B$62-Assumptions!$B$65</f>
         <v/>
       </c>
       <c r="C10" s="23">
-        <f>-Assumptions!$B$62-Assumptions!$B$65</f>
+        <f>-Assumptions!$B$63-Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>-Assumptions!$B$63-Assumptions!$B$66</f>
+        <f>-Assumptions!$B$64-Assumptions!$B$67</f>
         <v/>
       </c>
     </row>
@@ -9409,15 +9506,15 @@
         </is>
       </c>
       <c r="B13" s="23">
-        <f>Assumptions!$B$79</f>
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
       <c r="C13" s="23">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="E13" s="23">
@@ -9459,23 +9556,23 @@
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>DCF!B7</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>DCF!C7</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>DCF!D7</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="35">
         <f>DCF!E7</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="35">
         <f>DCF!F7</f>
         <v/>
       </c>
@@ -9526,35 +9623,35 @@
         </is>
       </c>
       <c r="B16" s="26">
-        <f>Assumptions!$B$67-B11</f>
+        <f>Assumptions!$B$68-B11</f>
         <v/>
       </c>
       <c r="C16" s="26">
-        <f>Assumptions!$B$68-C11</f>
+        <f>Assumptions!$B$69-C11</f>
         <v/>
       </c>
       <c r="D16" s="26">
-        <f>Assumptions!$B$85+Assumptions!$B$86-Assumptions!$B$87+Assumptions!$B$88+1.14</f>
+        <f>Assumptions!$B$86+Assumptions!$B$87-Assumptions!$B$88+Assumptions!$B$89+1.14</f>
         <v/>
       </c>
       <c r="E16" s="26">
-        <f>('Balance Sheet'!D9-Assumptions!$B$130)*Assumptions!$B$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
+        <f>('Balance Sheet'!D9-Assumptions!$B$131)*Assumptions!$B$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
         <v/>
       </c>
       <c r="F16" s="26">
-        <f>'Balance Sheet'!E9*Assumptions!$C$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
+        <f>'Balance Sheet'!E9*Assumptions!$C$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
         <v/>
       </c>
       <c r="G16" s="26">
-        <f>'Balance Sheet'!F9*Assumptions!$D$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
+        <f>'Balance Sheet'!F9*Assumptions!$D$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
         <v/>
       </c>
       <c r="H16" s="26">
-        <f>'Balance Sheet'!G9*Assumptions!$E$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
+        <f>'Balance Sheet'!G9*Assumptions!$E$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
         <v/>
       </c>
       <c r="I16" s="26">
-        <f>'Balance Sheet'!H9*Assumptions!$F$34-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$33-DCF!$C$44*DCF!$C$46*(Assumptions!$B$42+0.0435)</f>
+        <f>'Balance Sheet'!H9*Assumptions!$F$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
         <v/>
       </c>
     </row>
@@ -9565,15 +9662,15 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>Assumptions!$B$67</f>
+        <f>Assumptions!$B$68</f>
         <v/>
       </c>
       <c r="C17" s="23">
-        <f>Assumptions!$B$68</f>
+        <f>Assumptions!$B$69</f>
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>Assumptions!$B$69</f>
+        <f>Assumptions!$B$70</f>
         <v/>
       </c>
       <c r="E17" s="26">
@@ -9604,15 +9701,15 @@
         </is>
       </c>
       <c r="B18" s="23">
-        <f>-Assumptions!$B$70</f>
+        <f>-Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="C18" s="23">
-        <f>-Assumptions!$B$71</f>
+        <f>-Assumptions!$B$72</f>
         <v/>
       </c>
       <c r="D18" s="23">
-        <f>-Assumptions!$B$72</f>
+        <f>-Assumptions!$B$73</f>
         <v/>
       </c>
       <c r="E18" s="26">
@@ -9681,16 +9778,16 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B20" s="34">
-        <f>Assumptions!$B$73</f>
-        <v/>
-      </c>
-      <c r="C20" s="34">
+      <c r="B20" s="35">
         <f>Assumptions!$B$74</f>
         <v/>
       </c>
-      <c r="D20" s="34">
+      <c r="C20" s="35">
         <f>Assumptions!$B$75</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="E20" s="24">
@@ -9720,35 +9817,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B21" s="36">
-        <f>Assumptions!$B$76</f>
-        <v/>
-      </c>
-      <c r="C21" s="36">
+      <c r="B21" s="37">
         <f>Assumptions!$B$77</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="C21" s="37">
         <f>Assumptions!$B$78</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="D21" s="37">
+        <f>Assumptions!$B$79</f>
+        <v/>
+      </c>
+      <c r="E21" s="34">
         <f>E20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <f>F20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <f>G20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <f>H20/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <f>I20/DCF!$B$43</f>
         <v/>
       </c>
@@ -9760,31 +9857,31 @@
         </is>
       </c>
       <c r="C22" s="23">
+        <f>Assumptions!$B$132</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
         <f>Assumptions!$B$131</f>
         <v/>
       </c>
-      <c r="D22" s="23">
-        <f>Assumptions!$B$130</f>
-        <v/>
-      </c>
       <c r="E22" s="26">
-        <f>E20*Assumptions!$B$37</f>
+        <f>E20*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="F22" s="26">
-        <f>F20*Assumptions!$B$37</f>
+        <f>F20*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="G22" s="26">
-        <f>G20*Assumptions!$B$37</f>
+        <f>G20*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="H22" s="26">
-        <f>H20*Assumptions!$B$37</f>
+        <f>H20*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="I22" s="26">
-        <f>I20*Assumptions!$B$37</f>
+        <f>I20*Assumptions!$B$38</f>
         <v/>
       </c>
     </row>
@@ -9794,31 +9891,31 @@
           <t>Dividend per share (EGP)</t>
         </is>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="34">
         <f>C22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <f>D22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="34">
         <f>E22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>F22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="34">
         <f>G22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H23" s="33">
+      <c r="H23" s="34">
         <f>H22/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I23" s="33">
+      <c r="I23" s="34">
         <f>I22/DCF!$B$43</f>
         <v/>
       </c>
@@ -9829,7 +9926,7 @@
           <t>FY2025 check: components of non-operating income against the audited residual</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>D16-(D17-D11)</f>
         <v/>
       </c>
@@ -9967,7 +10064,7 @@
         </is>
       </c>
       <c r="D5" s="23">
-        <f>Assumptions!$B$105</f>
+        <f>Assumptions!$B$106</f>
         <v/>
       </c>
     </row>
@@ -9978,7 +10075,7 @@
         </is>
       </c>
       <c r="D6" s="23">
-        <f>Assumptions!$B$106</f>
+        <f>Assumptions!$B$107</f>
         <v/>
       </c>
     </row>
@@ -9989,7 +10086,7 @@
         </is>
       </c>
       <c r="D7" s="23">
-        <f>Assumptions!$B$107</f>
+        <f>Assumptions!$B$108</f>
         <v/>
       </c>
     </row>
@@ -10031,19 +10128,19 @@
         </is>
       </c>
       <c r="B9" s="23">
+        <f>Assumptions!$B$114</f>
+        <v/>
+      </c>
+      <c r="C9" s="23">
         <f>Assumptions!$B$113</f>
         <v/>
       </c>
-      <c r="C9" s="23">
+      <c r="D9" s="23">
         <f>Assumptions!$B$112</f>
         <v/>
       </c>
-      <c r="D9" s="23">
-        <f>Assumptions!$B$111</f>
-        <v/>
-      </c>
       <c r="E9" s="26">
-        <f>D9-Assumptions!$B$130+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
+        <f>D9-Assumptions!$B$131+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F9" s="26">
@@ -10070,7 +10167,7 @@
         </is>
       </c>
       <c r="D10" s="26">
-        <f>Assumptions!$B$108+Assumptions!$B$109+Assumptions!$B$110</f>
+        <f>Assumptions!$B$109+Assumptions!$B$110+Assumptions!$B$111</f>
         <v/>
       </c>
       <c r="E10" s="26">
@@ -10100,16 +10197,16 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
+        <f>Assumptions!$B$104</f>
+        <v/>
+      </c>
+      <c r="C11" s="35">
         <f>Assumptions!$B$103</f>
         <v/>
       </c>
-      <c r="C11" s="34">
+      <c r="D11" s="35">
         <f>Assumptions!$B$102</f>
-        <v/>
-      </c>
-      <c r="D11" s="34">
-        <f>Assumptions!$B$101</f>
         <v/>
       </c>
       <c r="E11" s="24">
@@ -10140,11 +10237,11 @@
         </is>
       </c>
       <c r="B12" s="23">
+        <f>Assumptions!$B$125</f>
+        <v/>
+      </c>
+      <c r="C12" s="23">
         <f>Assumptions!$B$124</f>
-        <v/>
-      </c>
-      <c r="C12" s="23">
-        <f>Assumptions!$B$123</f>
         <v/>
       </c>
       <c r="D12" s="23">
@@ -10210,7 +10307,7 @@
         </is>
       </c>
       <c r="D14" s="23">
-        <f>Assumptions!$B$104</f>
+        <f>Assumptions!$B$105</f>
         <v/>
       </c>
       <c r="E14" s="26">
@@ -10240,20 +10337,20 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
+        <f>Assumptions!$B$117</f>
+        <v/>
+      </c>
+      <c r="C15" s="35">
         <f>Assumptions!$B$116</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="D15" s="35">
         <f>Assumptions!$B$115</f>
         <v/>
       </c>
-      <c r="D15" s="34">
-        <f>Assumptions!$B$114</f>
-        <v/>
-      </c>
       <c r="E15" s="24">
-        <f>D15-Assumptions!$B$130+'Income Statement'!E20-'Income Statement'!E22</f>
+        <f>D15-Assumptions!$B$131+'Income Statement'!E20-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F15" s="24">
@@ -10318,35 +10415,35 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="34">
         <f>B15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <f>C15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <f>D15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>E15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="34">
         <f>F15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="34">
         <f>G15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="34">
         <f>H15/DCF!$B$43</f>
         <v/>
       </c>
-      <c r="I17" s="33">
+      <c r="I17" s="34">
         <f>I15/DCF!$B$43</f>
         <v/>
       </c>
@@ -10413,7 +10510,7 @@
         </is>
       </c>
       <c r="B21" s="26">
-        <f>Assumptions!$B$101</f>
+        <f>Assumptions!$B$102</f>
         <v/>
       </c>
     </row>
@@ -10424,7 +10521,7 @@
         </is>
       </c>
       <c r="B22" s="26">
-        <f>-Assumptions!$B$104</f>
+        <f>-Assumptions!$B$105</f>
         <v/>
       </c>
     </row>
@@ -10446,7 +10543,7 @@
         </is>
       </c>
       <c r="B24" s="26">
-        <f>Assumptions!$B$114+Assumptions!$B$117</f>
+        <f>Assumptions!$B$115+Assumptions!$B$118</f>
         <v/>
       </c>
     </row>
@@ -10456,7 +10553,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="39">
         <f>B23-B24</f>
         <v/>
       </c>
@@ -10603,7 +10700,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="C6" s="23">
@@ -10692,7 +10789,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>-Assumptions!$B$84</f>
+        <f>-Assumptions!$B$85</f>
         <v/>
       </c>
       <c r="C9" s="23">
@@ -10754,7 +10851,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>-Assumptions!$B$130</f>
+        <f>-Assumptions!$B$131</f>
         <v/>
       </c>
       <c r="C11" s="26">
@@ -10785,7 +10882,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>Assumptions!$B$111</f>
+        <f>Assumptions!$B$112</f>
         <v/>
       </c>
       <c r="C12" s="23">
@@ -11155,35 +11252,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>'Income Statement'!B21</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>'Income Statement'!C21</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>'Income Statement'!D21</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>'Income Statement'!E21</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>'Income Statement'!F21</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>'Income Statement'!G21</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>'Income Statement'!H21</f>
         <v/>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="37">
         <f>'Income Statement'!I21</f>
         <v/>
       </c>

--- a/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_06082026_public.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -943,52 +943,56 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Anything else pasted would be a defect.</t>
+          <t xml:space="preserve">  Anything else pasted would be a defect, and the claim is AUDITED rather than asserted. Of the 306 pasted</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cells: 136 are audited or disclosed history; 77 are genuine forecast drivers, which by definition have</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>HOW THE COMPANY IS VALUED. A single-segment cement operating company: two lines in Suez governorate, 4.2Mt of</t>
+          <t xml:space="preserve">  nothing to derive them from; 26 are the simulation ladder; 78 are whole-model re-runs. That is all 306, and</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>clinker capacity and 5.0Mt of cement, 60% owned by Aridos Jativa of Spain. No property leg, no lending book,</t>
+          <t xml:space="preserve">  ZERO are derivable-but-pasted. Two rounds of review found cells that were: revision 3 held two rounded</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>no concession. One operating-company lens, cross-read against relative multiples, normalised earnings power</t>
+          <t xml:space="preserve">  COPIES of figures derived elsewhere on the same sheet (the FY2025 utilisation and export share), and the</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>and replacement cost. Cash of EGP 3,459mn against interest-bearing debt of EGP 1,135mn makes it net cash;</t>
+          <t xml:space="preserve">  expert panel on the Summary sheet was nine typed numbers. The copies are gone because revision 4 inverted</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>that cash is stripped out of the discount rate and added back in the bridge, so it is priced once at face —</t>
+          <t xml:space="preserve">  the build so the quantities are no longer derived at all; the panel is now nine FORMULAS, which also</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>less the EGP 2,002mn FY2025 dividend that was declared and still unpaid at 31 March 2026.</t>
+          <t xml:space="preserve">  settles what it is — the same model at three parameter values, not three independent valuations.</t>
         </is>
       </c>
     </row>
@@ -998,42 +1002,42 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>TWO THINGS TO KNOW BEFORE READING ANY NUMBER.</t>
+          <t>HOW THE COMPANY IS VALUED. A single-segment cement operating company: two lines in Suez governorate, 4.2Mt of</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * FY2025 is a cyclical peak. The audited EBITDA margin went 22.0% to 23.1% to 39.2% across the three years,</t>
+          <t>clinker capacity and 5.0Mt of cement, 60% owned by Aridos Jativa of Spain. No property leg, no lending book,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    on the abolition of the production quota in May 2025. The forecast glides it down every year from there.</t>
+          <t>no concession. One operating-company lens, cross-read against relative multiples, normalised earnings power</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Book return on capital is 60.6% and replacement-cost return is 8.6%. The terminal block is struck on the</t>
+          <t>and replacement cost. Cash of EGP 3,459mn against interest-bearing debt of EGP 1,135mn makes it net cash;</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    REPLACEMENT figure. On the book number, growth would be free; it is not, and the difference is the single</t>
+          <t>that cash is stripped out of the discount rate and added back in the bridge, so it is priced once at face —</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    most consequential judgement in this model.</t>
+          <t>less the EGP 2,002mn FY2025 dividend that was declared and still unpaid at 31 March 2026.</t>
         </is>
       </c>
     </row>
@@ -1042,6 +1046,51 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TWO THINGS TO KNOW BEFORE READING ANY NUMBER.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * FY2025 is a cyclical peak. The audited EBITDA margin went 22.0% to 23.1% to 39.2% across the three years,</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    on the abolition of the production quota in May 2025. The forecast glides it down every year from there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Book return on capital is 60.6% and replacement-cost return is 8.6%. The terminal block is struck on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REPLACEMENT figure. On the book number, growth would be free; it is not, and the difference is the single</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    most consequential judgement in this model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>No rating and no price target. Fair-value ranges and distributions only.</t>
         </is>
@@ -2868,14 +2917,17 @@
           <t>Expert 1 — Replacement-cost industrialist</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>58.81090803276457</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>68.87446529898703</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>78.93802256520951</v>
+      <c r="B17" s="34">
+        <f>((Assumptions!$B$143-15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="C17" s="34">
+        <f>(Assumptions!$B$143*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="D17" s="34">
+        <f>((Assumptions!$B$143+15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
       </c>
       <c r="E17" s="22">
         <f>C17/Assumptions!$B$5-1</f>
@@ -2888,14 +2940,17 @@
           <t>Expert 2 — Mid-cycle earnings-power analyst</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>46.11694752434044</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>52.94667167624527</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>59.77639582815011</v>
+      <c r="B18" s="34">
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$145-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="C18" s="34">
+        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$145+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="D18" s="34">
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$145+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
       </c>
       <c r="E18" s="22">
         <f>C18/Assumptions!$B$5-1</f>
@@ -2908,14 +2963,17 @@
           <t>Expert 3 — Cash-return and distribution investor</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>46.44553116758097</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>52.3465209611052</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>60.21450735247083</v>
+      <c r="B19" s="34">
+        <f>(AVERAGE(DCF!C15:F15)/0.20+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="C19" s="34">
+        <f>(AVERAGE(DCF!C15:F15)/0.175+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
+      </c>
+      <c r="D19" s="34">
+        <f>(AVERAGE(DCF!C15:F15)/0.15+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <v/>
       </c>
       <c r="E19" s="22">
         <f>C19/Assumptions!$B$5-1</f>
